--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.65</v>
+        <v>5.03</v>
       </c>
       <c r="F14" t="n">
-        <v>11.26</v>
+        <v>11.84</v>
       </c>
       <c r="G14" t="n">
-        <v>352.5</v>
+        <v>338</v>
       </c>
       <c r="H14" t="n">
-        <v>76.2</v>
+        <v>74.2</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.64</v>
+        <v>571.35</v>
       </c>
       <c r="K14" t="n">
-        <v>123.61</v>
+        <v>-122.81</v>
       </c>
       <c r="L14" t="n">
-        <v>123.64</v>
+        <v>584.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:24:05</t>
+          <t>06:23:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.42</v>
+        <v>4.96</v>
       </c>
       <c r="F15" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>352</v>
+        <v>349.7</v>
       </c>
       <c r="H15" t="n">
-        <v>76.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>137.12</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>-226.63</v>
       </c>
       <c r="L15" t="n">
-        <v>137.23</v>
+        <v>242.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:25:13</t>
+          <t>06:24:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.88</v>
+        <v>4.39</v>
       </c>
       <c r="F16" t="n">
-        <v>12.17</v>
+        <v>11.72</v>
       </c>
       <c r="G16" t="n">
-        <v>344</v>
+        <v>353.2</v>
       </c>
       <c r="H16" t="n">
-        <v>72.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>62.64</v>
+        <v>80.34</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.22</v>
+        <v>156.82</v>
       </c>
       <c r="L16" t="n">
-        <v>62.72</v>
+        <v>176.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:29:18</t>
+          <t>06:28:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.68</v>
+        <v>4.41</v>
       </c>
       <c r="F17" t="n">
-        <v>12.13</v>
+        <v>12.08</v>
       </c>
       <c r="G17" t="n">
-        <v>349.4</v>
+        <v>358.9</v>
       </c>
       <c r="H17" t="n">
-        <v>80.2</v>
+        <v>73.2</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-9.84</v>
+        <v>364.96</v>
       </c>
       <c r="K17" t="n">
-        <v>-31.55</v>
+        <v>3.74</v>
       </c>
       <c r="L17" t="n">
-        <v>33.05</v>
+        <v>364.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:31:42</t>
+          <t>06:30:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.65</v>
+        <v>5.14</v>
       </c>
       <c r="F18" t="n">
-        <v>12.41</v>
+        <v>11.85</v>
       </c>
       <c r="G18" t="n">
-        <v>341.2</v>
+        <v>352.3</v>
       </c>
       <c r="H18" t="n">
-        <v>74.7</v>
+        <v>78.5</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-17.5</v>
+        <v>198.01</v>
       </c>
       <c r="K18" t="n">
-        <v>-105.82</v>
+        <v>-170.94</v>
       </c>
       <c r="L18" t="n">
-        <v>107.25</v>
+        <v>261.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:33:02</t>
+          <t>06:30:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.76</v>
+        <v>4.51</v>
       </c>
       <c r="F19" t="n">
-        <v>11.77</v>
+        <v>11.63</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>339.9</v>
       </c>
       <c r="H19" t="n">
-        <v>67.3</v>
+        <v>77.7</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-55.1</v>
+        <v>-13.32</v>
       </c>
       <c r="K19" t="n">
-        <v>-142.34</v>
+        <v>-258.12</v>
       </c>
       <c r="L19" t="n">
-        <v>152.63</v>
+        <v>258.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:36:59</t>
+          <t>06:34:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.11</v>
+        <v>4.92</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>12.61</v>
       </c>
       <c r="G20" t="n">
-        <v>350.3</v>
+        <v>356.1</v>
       </c>
       <c r="H20" t="n">
-        <v>75.3</v>
+        <v>72.8</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>194.93</v>
+        <v>-78.48</v>
       </c>
       <c r="K20" t="n">
-        <v>-182.76</v>
+        <v>-309.93</v>
       </c>
       <c r="L20" t="n">
-        <v>267.21</v>
+        <v>319.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:38:09</t>
+          <t>06:36:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="F21" t="n">
-        <v>11.94</v>
+        <v>12.27</v>
       </c>
       <c r="G21" t="n">
-        <v>342.7</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="n">
-        <v>70.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-224.56</v>
+        <v>323.29</v>
       </c>
       <c r="K21" t="n">
-        <v>-43.98</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>228.82</v>
+        <v>331.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:39:57</t>
+          <t>06:37:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.08</v>
+        <v>4.32</v>
       </c>
       <c r="F22" t="n">
-        <v>11.51</v>
+        <v>11.75</v>
       </c>
       <c r="G22" t="n">
-        <v>346.4</v>
+        <v>343.3</v>
       </c>
       <c r="H22" t="n">
-        <v>78.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>152.08</v>
+        <v>238.37</v>
       </c>
       <c r="K22" t="n">
-        <v>-73.72</v>
+        <v>-62.2</v>
       </c>
       <c r="L22" t="n">
-        <v>169.01</v>
+        <v>246.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:44:38</t>
+          <t>06:42:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.71</v>
+        <v>4.03</v>
       </c>
       <c r="F23" t="n">
-        <v>11.44</v>
+        <v>12.12</v>
       </c>
       <c r="G23" t="n">
-        <v>337.9</v>
+        <v>359.1</v>
       </c>
       <c r="H23" t="n">
-        <v>77.8</v>
+        <v>68.7</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>42.08</v>
+        <v>-471.93</v>
       </c>
       <c r="K23" t="n">
-        <v>19</v>
+        <v>17.12</v>
       </c>
       <c r="L23" t="n">
-        <v>46.17</v>
+        <v>472.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:46:25</t>
+          <t>06:44:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.55</v>
+        <v>4.19</v>
       </c>
       <c r="F24" t="n">
-        <v>11.83</v>
+        <v>11.94</v>
       </c>
       <c r="G24" t="n">
-        <v>348.5</v>
+        <v>352.1</v>
       </c>
       <c r="H24" t="n">
-        <v>74.8</v>
+        <v>74.2</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>441.26</v>
+        <v>18.65</v>
       </c>
       <c r="K24" t="n">
-        <v>105.59</v>
+        <v>542.5700000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>453.72</v>
+        <v>542.89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:47:28</t>
+          <t>06:46:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.27</v>
+        <v>3.9</v>
       </c>
       <c r="F25" t="n">
-        <v>12.05</v>
+        <v>12.11</v>
       </c>
       <c r="G25" t="n">
-        <v>353.3</v>
+        <v>356.2</v>
       </c>
       <c r="H25" t="n">
-        <v>79.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-200.72</v>
+        <v>100.51</v>
       </c>
       <c r="K25" t="n">
-        <v>205.25</v>
+        <v>205.1</v>
       </c>
       <c r="L25" t="n">
-        <v>287.08</v>
+        <v>228.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:51:48</t>
+          <t>06:50:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.95</v>
+        <v>3.82</v>
       </c>
       <c r="F26" t="n">
-        <v>11.66</v>
+        <v>12.04</v>
       </c>
       <c r="G26" t="n">
-        <v>351.1</v>
+        <v>338.4</v>
       </c>
       <c r="H26" t="n">
-        <v>71.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>325.98</v>
+        <v>606.5599999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-80.38</v>
+        <v>-110.14</v>
       </c>
       <c r="L26" t="n">
-        <v>335.74</v>
+        <v>616.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:54:21</t>
+          <t>06:53:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.61</v>
+        <v>4.8</v>
       </c>
       <c r="F27" t="n">
-        <v>12.63</v>
+        <v>10.86</v>
       </c>
       <c r="G27" t="n">
-        <v>352.7</v>
+        <v>350.4</v>
       </c>
       <c r="H27" t="n">
-        <v>75.5</v>
+        <v>72.5</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-775.13</v>
+        <v>32.55</v>
       </c>
       <c r="K27" t="n">
-        <v>41.11</v>
+        <v>219.43</v>
       </c>
       <c r="L27" t="n">
-        <v>776.22</v>
+        <v>221.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:56:19</t>
+          <t>06:53:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.14</v>
+        <v>5.01</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>11.82</v>
       </c>
       <c r="G28" t="n">
-        <v>356</v>
+        <v>356.6</v>
       </c>
       <c r="H28" t="n">
-        <v>79.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-42.69</v>
+        <v>27.97</v>
       </c>
       <c r="K28" t="n">
-        <v>-922.71</v>
+        <v>234.91</v>
       </c>
       <c r="L28" t="n">
-        <v>923.6900000000001</v>
+        <v>236.57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:05:19</t>
+          <t>07:02:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.85</v>
+        <v>5.13</v>
       </c>
       <c r="F29" t="n">
-        <v>11.9</v>
+        <v>11.92</v>
       </c>
       <c r="G29" t="n">
-        <v>350.3</v>
+        <v>1.2</v>
       </c>
       <c r="H29" t="n">
-        <v>80.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-192.43</v>
+        <v>305.28</v>
       </c>
       <c r="K29" t="n">
-        <v>72.81999999999999</v>
+        <v>-140.16</v>
       </c>
       <c r="L29" t="n">
-        <v>205.75</v>
+        <v>335.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:07:37</t>
+          <t>07:05:02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="F30" t="n">
-        <v>12.16</v>
+        <v>11.98</v>
       </c>
       <c r="G30" t="n">
-        <v>353</v>
+        <v>338.5</v>
       </c>
       <c r="H30" t="n">
-        <v>73.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>22.37</v>
+        <v>-193.46</v>
       </c>
       <c r="K30" t="n">
-        <v>38.59</v>
+        <v>-180.19</v>
       </c>
       <c r="L30" t="n">
-        <v>44.61</v>
+        <v>264.38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:09:02</t>
+          <t>07:06:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.88</v>
+        <v>4.98</v>
       </c>
       <c r="F31" t="n">
-        <v>12.01</v>
+        <v>11.89</v>
       </c>
       <c r="G31" t="n">
-        <v>350.7</v>
+        <v>344.9</v>
       </c>
       <c r="H31" t="n">
-        <v>67.5</v>
+        <v>75.2</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.71</v>
+        <v>-50.37</v>
       </c>
       <c r="K31" t="n">
-        <v>-119.57</v>
+        <v>466.09</v>
       </c>
       <c r="L31" t="n">
-        <v>119.63</v>
+        <v>468.81</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:13:43</t>
+          <t>07:11:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.68</v>
+        <v>4.88</v>
       </c>
       <c r="F32" t="n">
-        <v>12.15</v>
+        <v>12.07</v>
       </c>
       <c r="G32" t="n">
-        <v>348.2</v>
+        <v>358.7</v>
       </c>
       <c r="H32" t="n">
-        <v>79.5</v>
+        <v>76.5</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>18.35</v>
+        <v>-202.11</v>
       </c>
       <c r="K32" t="n">
-        <v>140.75</v>
+        <v>-183.19</v>
       </c>
       <c r="L32" t="n">
-        <v>141.94</v>
+        <v>272.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:15:21</t>
+          <t>07:13:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.54</v>
+        <v>4.77</v>
       </c>
       <c r="F33" t="n">
-        <v>12.39</v>
+        <v>12.31</v>
       </c>
       <c r="G33" t="n">
-        <v>359.5</v>
+        <v>357.1</v>
       </c>
       <c r="H33" t="n">
-        <v>75.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>91.95999999999999</v>
+        <v>-206.75</v>
       </c>
       <c r="K33" t="n">
-        <v>56.31</v>
+        <v>30.44</v>
       </c>
       <c r="L33" t="n">
-        <v>107.83</v>
+        <v>208.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:16:52</t>
+          <t>07:15:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.77</v>
+        <v>5.01</v>
       </c>
       <c r="F34" t="n">
-        <v>11.68</v>
+        <v>11.71</v>
       </c>
       <c r="G34" t="n">
-        <v>336.9</v>
+        <v>2.4</v>
       </c>
       <c r="H34" t="n">
-        <v>58.3</v>
+        <v>75.3</v>
       </c>
       <c r="I34" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>229.59</v>
+        <v>138.59</v>
       </c>
       <c r="K34" t="n">
-        <v>-74.13</v>
+        <v>41.78</v>
       </c>
       <c r="L34" t="n">
-        <v>241.26</v>
+        <v>144.75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:21:24</t>
+          <t>07:19:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.15</v>
+        <v>5.17</v>
       </c>
       <c r="F35" t="n">
-        <v>11.57</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>357.8</v>
+        <v>336.6</v>
       </c>
       <c r="H35" t="n">
-        <v>74</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.15</v>
+        <v>455.88</v>
       </c>
       <c r="K35" t="n">
-        <v>115.84</v>
+        <v>-86.81999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>116.28</v>
+        <v>464.07</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:23:30</t>
+          <t>07:21:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.11</v>
+        <v>5.44</v>
       </c>
       <c r="F36" t="n">
-        <v>11.79</v>
+        <v>11.92</v>
       </c>
       <c r="G36" t="n">
-        <v>351.6</v>
+        <v>356.6</v>
       </c>
       <c r="H36" t="n">
-        <v>73.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>304.6</v>
+        <v>-157.82</v>
       </c>
       <c r="K36" t="n">
-        <v>-144.37</v>
+        <v>-99.92</v>
       </c>
       <c r="L36" t="n">
-        <v>337.08</v>
+        <v>186.79</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:24:23</t>
+          <t>07:23:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.78</v>
+        <v>5.79</v>
       </c>
       <c r="F37" t="n">
-        <v>11.33</v>
+        <v>11.43</v>
       </c>
       <c r="G37" t="n">
-        <v>349.6</v>
+        <v>358.5</v>
       </c>
       <c r="H37" t="n">
-        <v>68.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-24.71</v>
+        <v>428.04</v>
       </c>
       <c r="K37" t="n">
-        <v>-15</v>
+        <v>-305.13</v>
       </c>
       <c r="L37" t="n">
-        <v>28.91</v>
+        <v>525.66</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:27:35</t>
+          <t>07:28:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.14</v>
+        <v>4.74</v>
       </c>
       <c r="F38" t="n">
-        <v>11.69</v>
+        <v>11.81</v>
       </c>
       <c r="G38" t="n">
-        <v>340.9</v>
+        <v>357.1</v>
       </c>
       <c r="H38" t="n">
-        <v>66</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>327.62</v>
+        <v>-324.38</v>
       </c>
       <c r="K38" t="n">
-        <v>112.71</v>
+        <v>594.7</v>
       </c>
       <c r="L38" t="n">
-        <v>346.46</v>
+        <v>677.42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:29:12</t>
+          <t>07:29:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="F39" t="n">
-        <v>11.76</v>
+        <v>12.23</v>
       </c>
       <c r="G39" t="n">
-        <v>352.7</v>
+        <v>355.7</v>
       </c>
       <c r="H39" t="n">
-        <v>74.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>94.03</v>
+        <v>-716.88</v>
       </c>
       <c r="K39" t="n">
-        <v>363.06</v>
+        <v>-1116.41</v>
       </c>
       <c r="L39" t="n">
-        <v>375.04</v>
+        <v>1326.76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:31:35</t>
+          <t>07:30:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.26</v>
+        <v>5.18</v>
       </c>
       <c r="F40" t="n">
-        <v>11.58</v>
+        <v>11.62</v>
       </c>
       <c r="G40" t="n">
-        <v>343.1</v>
+        <v>350.6</v>
       </c>
       <c r="H40" t="n">
-        <v>63.7</v>
+        <v>68.2</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>182.29</v>
+        <v>-55.37</v>
       </c>
       <c r="K40" t="n">
-        <v>177.26</v>
+        <v>366.68</v>
       </c>
       <c r="L40" t="n">
-        <v>254.27</v>
+        <v>370.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:35:01</t>
+          <t>07:35:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.03</v>
+        <v>5.81</v>
       </c>
       <c r="F41" t="n">
-        <v>11.55</v>
+        <v>11.65</v>
       </c>
       <c r="G41" t="n">
-        <v>350.7</v>
+        <v>351.6</v>
       </c>
       <c r="H41" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-59.91</v>
+        <v>-517.58</v>
       </c>
       <c r="K41" t="n">
-        <v>-849.52</v>
+        <v>-30.47</v>
       </c>
       <c r="L41" t="n">
-        <v>851.63</v>
+        <v>518.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:37:06</t>
+          <t>07:36:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>5.32</v>
       </c>
       <c r="F42" t="n">
-        <v>11.75</v>
+        <v>11.42</v>
       </c>
       <c r="G42" t="n">
-        <v>347.9</v>
+        <v>337.2</v>
       </c>
       <c r="H42" t="n">
-        <v>76.2</v>
+        <v>79.2</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-257.28</v>
+        <v>647.5599999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-212.58</v>
+        <v>-396.09</v>
       </c>
       <c r="L42" t="n">
-        <v>333.74</v>
+        <v>759.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:38:26</t>
+          <t>07:38:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.77</v>
+        <v>5.05</v>
       </c>
       <c r="F43" t="n">
-        <v>11.2</v>
+        <v>11.32</v>
       </c>
       <c r="G43" t="n">
-        <v>335.5</v>
+        <v>351.2</v>
       </c>
       <c r="H43" t="n">
-        <v>75.7</v>
+        <v>71.3</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-17.4</v>
+        <v>1483.47</v>
       </c>
       <c r="K43" t="n">
-        <v>253.83</v>
+        <v>152.71</v>
       </c>
       <c r="L43" t="n">
-        <v>254.42</v>
+        <v>1491.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:46:35</t>
+          <t>07:46:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.27</v>
+        <v>5.83</v>
       </c>
       <c r="F44" t="n">
-        <v>11.92</v>
+        <v>11.28</v>
       </c>
       <c r="G44" t="n">
-        <v>347</v>
+        <v>352.6</v>
       </c>
       <c r="H44" t="n">
-        <v>71.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-32.69</v>
+        <v>-384.79</v>
       </c>
       <c r="K44" t="n">
-        <v>153.02</v>
+        <v>-311.73</v>
       </c>
       <c r="L44" t="n">
-        <v>156.48</v>
+        <v>495.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:48:46</t>
+          <t>07:48:42</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.97</v>
+        <v>4.71</v>
       </c>
       <c r="F45" t="n">
-        <v>12.22</v>
+        <v>12.25</v>
       </c>
       <c r="G45" t="n">
-        <v>352.5</v>
+        <v>350.9</v>
       </c>
       <c r="H45" t="n">
-        <v>67.2</v>
+        <v>69.8</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-27.42</v>
+        <v>-16.47</v>
       </c>
       <c r="K45" t="n">
-        <v>-233.12</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>234.72</v>
+        <v>86.59</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:50:24</t>
+          <t>07:50:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37</v>
+        <v>4.5</v>
       </c>
       <c r="F46" t="n">
-        <v>11.78</v>
+        <v>12.11</v>
       </c>
       <c r="G46" t="n">
-        <v>345.4</v>
+        <v>2.1</v>
       </c>
       <c r="H46" t="n">
-        <v>78.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-219.1</v>
+        <v>115.82</v>
       </c>
       <c r="K46" t="n">
-        <v>-149.6</v>
+        <v>6.03</v>
       </c>
       <c r="L46" t="n">
-        <v>265.3</v>
+        <v>115.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:55:21</t>
+          <t>07:56:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.33</v>
+        <v>4.78</v>
       </c>
       <c r="F47" t="n">
-        <v>11.38</v>
+        <v>12.01</v>
       </c>
       <c r="G47" t="n">
-        <v>351.7</v>
+        <v>340.8</v>
       </c>
       <c r="H47" t="n">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-34.46</v>
+        <v>-76.7</v>
       </c>
       <c r="K47" t="n">
-        <v>287.86</v>
+        <v>-185.31</v>
       </c>
       <c r="L47" t="n">
-        <v>289.92</v>
+        <v>200.55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:56:21</t>
+          <t>07:58:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.62</v>
+        <v>5.36</v>
       </c>
       <c r="F48" t="n">
-        <v>11.59</v>
+        <v>11.49</v>
       </c>
       <c r="G48" t="n">
-        <v>348.6</v>
+        <v>350.3</v>
       </c>
       <c r="H48" t="n">
-        <v>80.5</v>
+        <v>75.2</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.5</v>
+        <v>-152.47</v>
       </c>
       <c r="K48" t="n">
-        <v>-149.64</v>
+        <v>-285.07</v>
       </c>
       <c r="L48" t="n">
-        <v>149.74</v>
+        <v>323.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:58:34</t>
+          <t>07:59:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.22</v>
+        <v>5.51</v>
       </c>
       <c r="F49" t="n">
-        <v>11.23</v>
+        <v>11.64</v>
       </c>
       <c r="G49" t="n">
-        <v>349.1</v>
+        <v>335.7</v>
       </c>
       <c r="H49" t="n">
-        <v>74.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-258.78</v>
+        <v>-172.94</v>
       </c>
       <c r="K49" t="n">
-        <v>94.54000000000001</v>
+        <v>525.9</v>
       </c>
       <c r="L49" t="n">
-        <v>275.51</v>
+        <v>553.61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:02:59</t>
+          <t>08:02:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="F50" t="n">
-        <v>10.92</v>
+        <v>12.23</v>
       </c>
       <c r="G50" t="n">
-        <v>351</v>
+        <v>344.5</v>
       </c>
       <c r="H50" t="n">
-        <v>71.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>193.41</v>
+        <v>214.19</v>
       </c>
       <c r="K50" t="n">
-        <v>-117.27</v>
+        <v>-179.72</v>
       </c>
       <c r="L50" t="n">
-        <v>226.19</v>
+        <v>279.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:05:04</t>
+          <t>08:04:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.51</v>
+        <v>5.28</v>
       </c>
       <c r="F51" t="n">
-        <v>12.42</v>
+        <v>11.94</v>
       </c>
       <c r="G51" t="n">
-        <v>353.2</v>
+        <v>6</v>
       </c>
       <c r="H51" t="n">
-        <v>75.8</v>
+        <v>71.7</v>
       </c>
       <c r="I51" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>55.97</v>
+        <v>-100.56</v>
       </c>
       <c r="K51" t="n">
-        <v>52.05</v>
+        <v>53.85</v>
       </c>
       <c r="L51" t="n">
-        <v>76.43000000000001</v>
+        <v>114.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:06:32</t>
+          <t>08:05:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.01</v>
+        <v>4.88</v>
       </c>
       <c r="F52" t="n">
-        <v>11.23</v>
+        <v>11.63</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="H52" t="n">
-        <v>71.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-131.78</v>
+        <v>-149.68</v>
       </c>
       <c r="K52" t="n">
-        <v>92.26000000000001</v>
+        <v>702.99</v>
       </c>
       <c r="L52" t="n">
-        <v>160.87</v>
+        <v>718.75</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:10:01</t>
+          <t>08:10:22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
       <c r="F53" t="n">
-        <v>11.63</v>
+        <v>11.43</v>
       </c>
       <c r="G53" t="n">
-        <v>352.3</v>
+        <v>10.8</v>
       </c>
       <c r="H53" t="n">
-        <v>80</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-94.45</v>
+        <v>644.05</v>
       </c>
       <c r="K53" t="n">
-        <v>411.15</v>
+        <v>-78.16</v>
       </c>
       <c r="L53" t="n">
-        <v>421.86</v>
+        <v>648.78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:11:35</t>
+          <t>08:11:34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.06</v>
+        <v>5.2</v>
       </c>
       <c r="F54" t="n">
-        <v>12.01</v>
+        <v>11.63</v>
       </c>
       <c r="G54" t="n">
-        <v>350</v>
+        <v>358.4</v>
       </c>
       <c r="H54" t="n">
-        <v>74.3</v>
+        <v>73.7</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>201.96</v>
+        <v>-23.25</v>
       </c>
       <c r="K54" t="n">
-        <v>501.3</v>
+        <v>154.64</v>
       </c>
       <c r="L54" t="n">
-        <v>540.45</v>
+        <v>156.38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:13:28</t>
+          <t>08:13:22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
       <c r="F55" t="n">
-        <v>11.32</v>
+        <v>11.78</v>
       </c>
       <c r="G55" t="n">
-        <v>334.7</v>
+        <v>3.8</v>
       </c>
       <c r="H55" t="n">
-        <v>83.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>188.26</v>
+        <v>-455.65</v>
       </c>
       <c r="K55" t="n">
-        <v>-131.72</v>
+        <v>-44.07</v>
       </c>
       <c r="L55" t="n">
-        <v>229.77</v>
+        <v>457.78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:18:32</t>
+          <t>08:17:49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="F56" t="n">
-        <v>11.28</v>
+        <v>11.94</v>
       </c>
       <c r="G56" t="n">
-        <v>2.3</v>
+        <v>352.7</v>
       </c>
       <c r="H56" t="n">
-        <v>71</v>
+        <v>67.7</v>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-95.34999999999999</v>
+        <v>-1135.83</v>
       </c>
       <c r="K56" t="n">
-        <v>303.26</v>
+        <v>-855.39</v>
       </c>
       <c r="L56" t="n">
-        <v>317.9</v>
+        <v>1421.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:20:52</t>
+          <t>08:19:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.09</v>
+        <v>5.23</v>
       </c>
       <c r="F57" t="n">
-        <v>12.11</v>
+        <v>11.31</v>
       </c>
       <c r="G57" t="n">
-        <v>343.3</v>
+        <v>341.3</v>
       </c>
       <c r="H57" t="n">
-        <v>75.2</v>
+        <v>72.2</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-571.74</v>
+        <v>-995.8</v>
       </c>
       <c r="K57" t="n">
-        <v>75.97</v>
+        <v>-134.86</v>
       </c>
       <c r="L57" t="n">
-        <v>576.77</v>
+        <v>1004.89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:22:03</t>
+          <t>08:21:52</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.39</v>
+        <v>4.95</v>
       </c>
       <c r="F58" t="n">
-        <v>12.1</v>
+        <v>11.96</v>
       </c>
       <c r="G58" t="n">
-        <v>350.8</v>
+        <v>341.8</v>
       </c>
       <c r="H58" t="n">
-        <v>76.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-541.29</v>
+        <v>367.67</v>
       </c>
       <c r="K58" t="n">
-        <v>10.99</v>
+        <v>415.96</v>
       </c>
       <c r="L58" t="n">
-        <v>541.4</v>
+        <v>555.16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:34:01</t>
+          <t>08:34:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.52</v>
+        <v>5.18</v>
       </c>
       <c r="F59" t="n">
-        <v>12.73</v>
+        <v>11.84</v>
       </c>
       <c r="G59" t="n">
-        <v>333.3</v>
+        <v>338.4</v>
       </c>
       <c r="H59" t="n">
-        <v>75.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.78</v>
+        <v>-178.34</v>
       </c>
       <c r="K59" t="n">
-        <v>-93.62</v>
+        <v>-120.33</v>
       </c>
       <c r="L59" t="n">
-        <v>93.69</v>
+        <v>215.14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:36:20</t>
+          <t>08:35:18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.09</v>
+        <v>5.24</v>
       </c>
       <c r="F60" t="n">
-        <v>11.6</v>
+        <v>11.92</v>
       </c>
       <c r="G60" t="n">
-        <v>356</v>
+        <v>357.2</v>
       </c>
       <c r="H60" t="n">
-        <v>70.7</v>
+        <v>77.8</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-70.45</v>
+        <v>-83.31999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-27.95</v>
+        <v>-53.34</v>
       </c>
       <c r="L60" t="n">
-        <v>75.79000000000001</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:38:30</t>
+          <t>08:37:53</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.41</v>
+        <v>4.98</v>
       </c>
       <c r="F61" t="n">
-        <v>12.67</v>
+        <v>11.48</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8</v>
+        <v>348.5</v>
       </c>
       <c r="H61" t="n">
-        <v>71.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-74.37</v>
+        <v>-357.54</v>
       </c>
       <c r="K61" t="n">
-        <v>54.43</v>
+        <v>191.99</v>
       </c>
       <c r="L61" t="n">
-        <v>92.15000000000001</v>
+        <v>405.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:42:56</t>
+          <t>08:41:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="F62" t="n">
-        <v>11.96</v>
+        <v>12.63</v>
       </c>
       <c r="G62" t="n">
-        <v>341.1</v>
+        <v>352.3</v>
       </c>
       <c r="H62" t="n">
-        <v>71.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>53.23</v>
+        <v>-213.51</v>
       </c>
       <c r="K62" t="n">
-        <v>31.44</v>
+        <v>28.83</v>
       </c>
       <c r="L62" t="n">
-        <v>61.82</v>
+        <v>215.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:43:50</t>
+          <t>08:43:59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.93</v>
+        <v>5.88</v>
       </c>
       <c r="F63" t="n">
-        <v>11.2</v>
+        <v>11.87</v>
       </c>
       <c r="G63" t="n">
-        <v>356.6</v>
+        <v>341.7</v>
       </c>
       <c r="H63" t="n">
-        <v>63</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-125.54</v>
+        <v>336.47</v>
       </c>
       <c r="K63" t="n">
-        <v>71.25</v>
+        <v>224.37</v>
       </c>
       <c r="L63" t="n">
-        <v>144.35</v>
+        <v>404.42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:46:07</t>
+          <t>08:45:35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.84</v>
+        <v>4.81</v>
       </c>
       <c r="F64" t="n">
-        <v>12.14</v>
+        <v>11.37</v>
       </c>
       <c r="G64" t="n">
-        <v>359.2</v>
+        <v>341.8</v>
       </c>
       <c r="H64" t="n">
-        <v>64.5</v>
+        <v>76</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>152.9</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>354.87</v>
+        <v>246.04</v>
       </c>
       <c r="L64" t="n">
-        <v>386.4</v>
+        <v>256.74</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:50:49</t>
+          <t>08:50:24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.23</v>
+        <v>5.42</v>
       </c>
       <c r="F65" t="n">
-        <v>11.96</v>
+        <v>12.44</v>
       </c>
       <c r="G65" t="n">
-        <v>357.3</v>
+        <v>340.8</v>
       </c>
       <c r="H65" t="n">
-        <v>77.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-49.12</v>
+        <v>199.49</v>
       </c>
       <c r="K65" t="n">
-        <v>245.83</v>
+        <v>-481.17</v>
       </c>
       <c r="L65" t="n">
-        <v>250.69</v>
+        <v>520.88</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:53:14</t>
+          <t>08:52:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.77</v>
+        <v>5.6</v>
       </c>
       <c r="F66" t="n">
-        <v>11.67</v>
+        <v>11.91</v>
       </c>
       <c r="G66" t="n">
-        <v>354.1</v>
+        <v>338.1</v>
       </c>
       <c r="H66" t="n">
-        <v>75</v>
+        <v>75.7</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-128.17</v>
+        <v>-285.33</v>
       </c>
       <c r="K66" t="n">
-        <v>201.5</v>
+        <v>247.8</v>
       </c>
       <c r="L66" t="n">
-        <v>238.81</v>
+        <v>377.91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:54:44</t>
+          <t>08:54:11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.31</v>
+        <v>5.33</v>
       </c>
       <c r="F67" t="n">
-        <v>11.68</v>
+        <v>11.08</v>
       </c>
       <c r="G67" t="n">
-        <v>344.7</v>
+        <v>351.9</v>
       </c>
       <c r="H67" t="n">
-        <v>77.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-131.36</v>
+        <v>16.59</v>
       </c>
       <c r="K67" t="n">
-        <v>13.33</v>
+        <v>380.33</v>
       </c>
       <c r="L67" t="n">
-        <v>132.04</v>
+        <v>380.69</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:00:14</t>
+          <t>08:58:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="F68" t="n">
-        <v>12</v>
+        <v>12.05</v>
       </c>
       <c r="G68" t="n">
-        <v>339.1</v>
+        <v>357.4</v>
       </c>
       <c r="H68" t="n">
-        <v>73.2</v>
+        <v>73.7</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-181.69</v>
+        <v>195.29</v>
       </c>
       <c r="K68" t="n">
-        <v>-100.95</v>
+        <v>-597.6799999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>207.85</v>
+        <v>628.77</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:01:40</t>
+          <t>09:00:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.87</v>
+        <v>5.54</v>
       </c>
       <c r="F69" t="n">
-        <v>11.92</v>
+        <v>12.37</v>
       </c>
       <c r="G69" t="n">
-        <v>347.5</v>
+        <v>352</v>
       </c>
       <c r="H69" t="n">
-        <v>71.7</v>
+        <v>75.2</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>519.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-52.09</v>
+        <v>842.7</v>
       </c>
       <c r="L69" t="n">
-        <v>522.36</v>
+        <v>847.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:03:02</t>
+          <t>09:01:49</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="F70" t="n">
-        <v>12.18</v>
+        <v>11.98</v>
       </c>
       <c r="G70" t="n">
-        <v>1.2</v>
+        <v>346</v>
       </c>
       <c r="H70" t="n">
-        <v>81.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>235.2</v>
+        <v>-818.05</v>
       </c>
       <c r="K70" t="n">
-        <v>234.35</v>
+        <v>608.45</v>
       </c>
       <c r="L70" t="n">
-        <v>332.03</v>
+        <v>1019.52</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:06:25</t>
+          <t>09:06:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.72</v>
+        <v>5.7</v>
       </c>
       <c r="F71" t="n">
-        <v>11.92</v>
+        <v>12.2</v>
       </c>
       <c r="G71" t="n">
-        <v>357.7</v>
+        <v>351.8</v>
       </c>
       <c r="H71" t="n">
-        <v>71.3</v>
+        <v>74.7</v>
       </c>
       <c r="I71" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>330.56</v>
+        <v>-290.4</v>
       </c>
       <c r="K71" t="n">
-        <v>-219.74</v>
+        <v>140.75</v>
       </c>
       <c r="L71" t="n">
-        <v>396.93</v>
+        <v>322.71</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:08:34</t>
+          <t>09:07:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.24</v>
+        <v>5.75</v>
       </c>
       <c r="F72" t="n">
-        <v>11.24</v>
+        <v>11.99</v>
       </c>
       <c r="G72" t="n">
-        <v>349.2</v>
+        <v>346.3</v>
       </c>
       <c r="H72" t="n">
-        <v>74.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>275.2</v>
+        <v>-198.06</v>
       </c>
       <c r="K72" t="n">
-        <v>407.78</v>
+        <v>150.07</v>
       </c>
       <c r="L72" t="n">
-        <v>491.95</v>
+        <v>248.49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:09:37</t>
+          <t>09:08:56</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.34</v>
+        <v>4.86</v>
       </c>
       <c r="F73" t="n">
-        <v>12.45</v>
+        <v>11.61</v>
       </c>
       <c r="G73" t="n">
-        <v>356.1</v>
+        <v>349.9</v>
       </c>
       <c r="H73" t="n">
-        <v>76</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>-101.76</v>
+        <v>185.22</v>
       </c>
       <c r="K73" t="n">
-        <v>-209.14</v>
+        <v>323.11</v>
       </c>
       <c r="L73" t="n">
-        <v>232.58</v>
+        <v>372.43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:22:10</t>
+          <t>09:18:25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.41</v>
+        <v>5.59</v>
       </c>
       <c r="F74" t="n">
-        <v>11.69</v>
+        <v>11.67</v>
       </c>
       <c r="G74" t="n">
-        <v>1.5</v>
+        <v>346.3</v>
       </c>
       <c r="H74" t="n">
-        <v>76.8</v>
+        <v>69.8</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>86.79000000000001</v>
+        <v>-88.13</v>
       </c>
       <c r="K74" t="n">
-        <v>-121.91</v>
+        <v>-172.87</v>
       </c>
       <c r="L74" t="n">
-        <v>149.65</v>
+        <v>194.04</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:23:35</t>
+          <t>09:19:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.7</v>
+        <v>5.41</v>
       </c>
       <c r="F75" t="n">
-        <v>12.21</v>
+        <v>11.44</v>
       </c>
       <c r="G75" t="n">
-        <v>342.7</v>
+        <v>344.2</v>
       </c>
       <c r="H75" t="n">
-        <v>71.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-28.77</v>
+        <v>526.46</v>
       </c>
       <c r="K75" t="n">
-        <v>47.85</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>55.83</v>
+        <v>533.5700000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:25:17</t>
+          <t>09:20:31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="F76" t="n">
-        <v>11.56</v>
+        <v>12.03</v>
       </c>
       <c r="G76" t="n">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="H76" t="n">
-        <v>73.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>75.95999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="K76" t="n">
-        <v>29.04</v>
+        <v>-97.39</v>
       </c>
       <c r="L76" t="n">
-        <v>81.31999999999999</v>
+        <v>97.48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:28:55</t>
+          <t>09:25:43</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.27</v>
+        <v>5.64</v>
       </c>
       <c r="F77" t="n">
-        <v>11.73</v>
+        <v>11.33</v>
       </c>
       <c r="G77" t="n">
-        <v>347</v>
+        <v>344.3</v>
       </c>
       <c r="H77" t="n">
-        <v>68.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>18.92</v>
+        <v>-283.07</v>
       </c>
       <c r="K77" t="n">
-        <v>-118.36</v>
+        <v>-100.56</v>
       </c>
       <c r="L77" t="n">
-        <v>119.87</v>
+        <v>300.41</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:30:47</t>
+          <t>09:27:48</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.83</v>
+        <v>5.12</v>
       </c>
       <c r="F78" t="n">
-        <v>11.77</v>
+        <v>11.72</v>
       </c>
       <c r="G78" t="n">
-        <v>337</v>
+        <v>350.9</v>
       </c>
       <c r="H78" t="n">
-        <v>74.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-56.86</v>
+        <v>294.23</v>
       </c>
       <c r="K78" t="n">
-        <v>-65.42</v>
+        <v>113.6</v>
       </c>
       <c r="L78" t="n">
-        <v>86.68000000000001</v>
+        <v>315.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:33:01</t>
+          <t>09:29:36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.79</v>
+        <v>5.28</v>
       </c>
       <c r="F79" t="n">
-        <v>11.68</v>
+        <v>12.18</v>
       </c>
       <c r="G79" t="n">
-        <v>343.4</v>
+        <v>358.1</v>
       </c>
       <c r="H79" t="n">
-        <v>76.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-16.15</v>
+        <v>335.64</v>
       </c>
       <c r="K79" t="n">
-        <v>250.64</v>
+        <v>167.75</v>
       </c>
       <c r="L79" t="n">
-        <v>251.16</v>
+        <v>375.23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:39:07</t>
+          <t>09:35:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.89</v>
+        <v>5.59</v>
       </c>
       <c r="F80" t="n">
-        <v>11.99</v>
+        <v>11.7</v>
       </c>
       <c r="G80" t="n">
-        <v>353.4</v>
+        <v>350.9</v>
       </c>
       <c r="H80" t="n">
-        <v>73.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-338.7</v>
+        <v>-551.6799999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-133.68</v>
+        <v>-225.06</v>
       </c>
       <c r="L80" t="n">
-        <v>364.12</v>
+        <v>595.83</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:40:09</t>
+          <t>09:36:31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.83</v>
+        <v>6.2</v>
       </c>
       <c r="F81" t="n">
-        <v>11.17</v>
+        <v>11.92</v>
       </c>
       <c r="G81" t="n">
-        <v>342.7</v>
+        <v>351.7</v>
       </c>
       <c r="H81" t="n">
-        <v>72.7</v>
+        <v>77.5</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>282.15</v>
+        <v>303.74</v>
       </c>
       <c r="K81" t="n">
-        <v>19.84</v>
+        <v>574.4</v>
       </c>
       <c r="L81" t="n">
-        <v>282.85</v>
+        <v>649.76</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:42:00</t>
+          <t>09:38:28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.74</v>
+        <v>5.33</v>
       </c>
       <c r="F82" t="n">
-        <v>11.73</v>
+        <v>12.4</v>
       </c>
       <c r="G82" t="n">
-        <v>353.1</v>
+        <v>345.1</v>
       </c>
       <c r="H82" t="n">
-        <v>83</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>59.33</v>
+        <v>-384.2</v>
       </c>
       <c r="K82" t="n">
-        <v>210.04</v>
+        <v>518.52</v>
       </c>
       <c r="L82" t="n">
-        <v>218.25</v>
+        <v>645.34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:48:11</t>
+          <t>09:43:55</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.97</v>
+        <v>5.09</v>
       </c>
       <c r="F83" t="n">
-        <v>11.79</v>
+        <v>11.55</v>
       </c>
       <c r="G83" t="n">
-        <v>344.8</v>
+        <v>350.5</v>
       </c>
       <c r="H83" t="n">
-        <v>70</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>219.19</v>
+        <v>-188.67</v>
       </c>
       <c r="K83" t="n">
-        <v>-500.17</v>
+        <v>472.97</v>
       </c>
       <c r="L83" t="n">
-        <v>546.1</v>
+        <v>509.21</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:49:55</t>
+          <t>09:46:11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3568,31 +3568,31 @@
         <v>5.4</v>
       </c>
       <c r="F84" t="n">
-        <v>11.62</v>
+        <v>11.75</v>
       </c>
       <c r="G84" t="n">
-        <v>354.3</v>
+        <v>344.9</v>
       </c>
       <c r="H84" t="n">
-        <v>71.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>108.68</v>
+        <v>-814.03</v>
       </c>
       <c r="K84" t="n">
-        <v>-33.98</v>
+        <v>531.22</v>
       </c>
       <c r="L84" t="n">
-        <v>113.87</v>
+        <v>972.03</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:52:12</t>
+          <t>09:47:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="F85" t="n">
-        <v>12.18</v>
+        <v>12</v>
       </c>
       <c r="G85" t="n">
-        <v>5.8</v>
+        <v>357.9</v>
       </c>
       <c r="H85" t="n">
-        <v>70.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I85" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-84.56999999999999</v>
+        <v>396.79</v>
       </c>
       <c r="K85" t="n">
-        <v>-274.4</v>
+        <v>-69.41</v>
       </c>
       <c r="L85" t="n">
-        <v>287.14</v>
+        <v>402.82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:55:36</t>
+          <t>09:53:05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.42</v>
+        <v>5.17</v>
       </c>
       <c r="F86" t="n">
-        <v>11.89</v>
+        <v>11.48</v>
       </c>
       <c r="G86" t="n">
-        <v>340.7</v>
+        <v>340.9</v>
       </c>
       <c r="H86" t="n">
-        <v>70.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="I86" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>252.15</v>
+        <v>732.87</v>
       </c>
       <c r="K86" t="n">
-        <v>-669.73</v>
+        <v>-709.63</v>
       </c>
       <c r="L86" t="n">
-        <v>715.62</v>
+        <v>1020.13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:57:13</t>
+          <t>09:54:10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.91</v>
+        <v>5.59</v>
       </c>
       <c r="F87" t="n">
-        <v>11.21</v>
+        <v>11.69</v>
       </c>
       <c r="G87" t="n">
-        <v>347.8</v>
+        <v>342.9</v>
       </c>
       <c r="H87" t="n">
-        <v>73.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>432.66</v>
+        <v>426.8</v>
       </c>
       <c r="K87" t="n">
-        <v>-143.67</v>
+        <v>-210.08</v>
       </c>
       <c r="L87" t="n">
-        <v>455.89</v>
+        <v>475.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:59:19</t>
+          <t>09:56:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.34</v>
+        <v>6.06</v>
       </c>
       <c r="F88" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="G88" t="n">
-        <v>6</v>
+        <v>348.2</v>
       </c>
       <c r="H88" t="n">
-        <v>75.2</v>
+        <v>75.8</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>664.29</v>
+        <v>-276.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-62.02</v>
+        <v>192.09</v>
       </c>
       <c r="L88" t="n">
-        <v>667.1799999999999</v>
+        <v>336.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>571.35</v>
+        <v>532.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-122.81</v>
+        <v>-114.54</v>
       </c>
       <c r="L14" t="n">
-        <v>584.4</v>
+        <v>545.04</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-85.59999999999999</v>
+        <v>-120.2</v>
       </c>
       <c r="K15" t="n">
-        <v>-226.63</v>
+        <v>-318.24</v>
       </c>
       <c r="L15" t="n">
-        <v>242.26</v>
+        <v>340.18</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>80.34</v>
+        <v>117.57</v>
       </c>
       <c r="K16" t="n">
-        <v>156.82</v>
+        <v>229.49</v>
       </c>
       <c r="L16" t="n">
-        <v>176.21</v>
+        <v>257.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>364.96</v>
+        <v>424.92</v>
       </c>
       <c r="K17" t="n">
-        <v>3.74</v>
+        <v>4.36</v>
       </c>
       <c r="L17" t="n">
-        <v>364.98</v>
+        <v>424.95</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>198.01</v>
+        <v>276.29</v>
       </c>
       <c r="K18" t="n">
-        <v>-170.94</v>
+        <v>-238.52</v>
       </c>
       <c r="L18" t="n">
-        <v>261.59</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-13.32</v>
+        <v>-18.78</v>
       </c>
       <c r="K19" t="n">
-        <v>-258.12</v>
+        <v>-363.91</v>
       </c>
       <c r="L19" t="n">
-        <v>258.47</v>
+        <v>364.39</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-78.48</v>
+        <v>-122.22</v>
       </c>
       <c r="K20" t="n">
-        <v>-309.93</v>
+        <v>-482.69</v>
       </c>
       <c r="L20" t="n">
-        <v>319.71</v>
+        <v>497.92</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>323.29</v>
+        <v>485.77</v>
       </c>
       <c r="K21" t="n">
-        <v>71.29000000000001</v>
+        <v>107.13</v>
       </c>
       <c r="L21" t="n">
-        <v>331.06</v>
+        <v>497.44</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>238.37</v>
+        <v>402.91</v>
       </c>
       <c r="K22" t="n">
-        <v>-62.2</v>
+        <v>-105.13</v>
       </c>
       <c r="L22" t="n">
-        <v>246.35</v>
+        <v>416.4</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-471.93</v>
+        <v>-715.79</v>
       </c>
       <c r="K23" t="n">
-        <v>17.12</v>
+        <v>25.97</v>
       </c>
       <c r="L23" t="n">
-        <v>472.24</v>
+        <v>716.26</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>18.65</v>
+        <v>27.64</v>
       </c>
       <c r="K24" t="n">
-        <v>542.5700000000001</v>
+        <v>803.97</v>
       </c>
       <c r="L24" t="n">
-        <v>542.89</v>
+        <v>804.4400000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>100.51</v>
+        <v>193.46</v>
       </c>
       <c r="K25" t="n">
-        <v>205.1</v>
+        <v>394.75</v>
       </c>
       <c r="L25" t="n">
-        <v>228.4</v>
+        <v>439.6</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>606.5599999999999</v>
+        <v>906.33</v>
       </c>
       <c r="K26" t="n">
-        <v>-110.14</v>
+        <v>-164.58</v>
       </c>
       <c r="L26" t="n">
-        <v>616.48</v>
+        <v>921.15</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>32.55</v>
+        <v>86.52</v>
       </c>
       <c r="K27" t="n">
-        <v>219.43</v>
+        <v>583.28</v>
       </c>
       <c r="L27" t="n">
-        <v>221.83</v>
+        <v>589.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>27.97</v>
+        <v>78.84</v>
       </c>
       <c r="K28" t="n">
-        <v>234.91</v>
+        <v>662.05</v>
       </c>
       <c r="L28" t="n">
-        <v>236.57</v>
+        <v>666.73</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>305.28</v>
+        <v>391.62</v>
       </c>
       <c r="K29" t="n">
-        <v>-140.16</v>
+        <v>-179.8</v>
       </c>
       <c r="L29" t="n">
-        <v>335.92</v>
+        <v>430.92</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-193.46</v>
+        <v>-235.89</v>
       </c>
       <c r="K30" t="n">
-        <v>-180.19</v>
+        <v>-219.7</v>
       </c>
       <c r="L30" t="n">
-        <v>264.38</v>
+        <v>322.36</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-50.37</v>
+        <v>-58.36</v>
       </c>
       <c r="K31" t="n">
-        <v>466.09</v>
+        <v>539.97</v>
       </c>
       <c r="L31" t="n">
-        <v>468.81</v>
+        <v>543.12</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-202.11</v>
+        <v>-276.35</v>
       </c>
       <c r="K32" t="n">
-        <v>-183.19</v>
+        <v>-250.49</v>
       </c>
       <c r="L32" t="n">
-        <v>272.78</v>
+        <v>372.98</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-206.75</v>
+        <v>-309.38</v>
       </c>
       <c r="K33" t="n">
-        <v>30.44</v>
+        <v>45.55</v>
       </c>
       <c r="L33" t="n">
-        <v>208.98</v>
+        <v>312.71</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>138.59</v>
+        <v>260.15</v>
       </c>
       <c r="K34" t="n">
-        <v>41.78</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>144.75</v>
+        <v>271.71</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>455.88</v>
+        <v>651.49</v>
       </c>
       <c r="K35" t="n">
-        <v>-86.81999999999999</v>
+        <v>-124.08</v>
       </c>
       <c r="L35" t="n">
-        <v>464.07</v>
+        <v>663.21</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-157.82</v>
+        <v>-333.83</v>
       </c>
       <c r="K36" t="n">
-        <v>-99.92</v>
+        <v>-211.36</v>
       </c>
       <c r="L36" t="n">
-        <v>186.79</v>
+        <v>395.12</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>428.04</v>
+        <v>621.72</v>
       </c>
       <c r="K37" t="n">
-        <v>-305.13</v>
+        <v>-443.19</v>
       </c>
       <c r="L37" t="n">
-        <v>525.66</v>
+        <v>763.51</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-324.38</v>
+        <v>-477.72</v>
       </c>
       <c r="K38" t="n">
-        <v>594.7</v>
+        <v>875.83</v>
       </c>
       <c r="L38" t="n">
-        <v>677.42</v>
+        <v>997.64</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-716.88</v>
+        <v>-874.45</v>
       </c>
       <c r="K39" t="n">
-        <v>-1116.41</v>
+        <v>-1361.79</v>
       </c>
       <c r="L39" t="n">
-        <v>1326.76</v>
+        <v>1618.37</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-55.37</v>
+        <v>-106.99</v>
       </c>
       <c r="K40" t="n">
-        <v>366.68</v>
+        <v>708.5599999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>370.83</v>
+        <v>716.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-517.58</v>
+        <v>-1063.96</v>
       </c>
       <c r="K41" t="n">
-        <v>-30.47</v>
+        <v>-62.63</v>
       </c>
       <c r="L41" t="n">
-        <v>518.47</v>
+        <v>1065.8</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>647.5599999999999</v>
+        <v>1035.93</v>
       </c>
       <c r="K42" t="n">
-        <v>-396.09</v>
+        <v>-633.64</v>
       </c>
       <c r="L42" t="n">
-        <v>759.09</v>
+        <v>1214.35</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>1483.47</v>
+        <v>1941.21</v>
       </c>
       <c r="K43" t="n">
-        <v>152.71</v>
+        <v>199.83</v>
       </c>
       <c r="L43" t="n">
-        <v>1491.31</v>
+        <v>1951.47</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-384.79</v>
+        <v>-465.11</v>
       </c>
       <c r="K44" t="n">
-        <v>-311.73</v>
+        <v>-376.8</v>
       </c>
       <c r="L44" t="n">
-        <v>495.22</v>
+        <v>598.59</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-16.47</v>
+        <v>-34.64</v>
       </c>
       <c r="K45" t="n">
-        <v>85.01000000000001</v>
+        <v>178.86</v>
       </c>
       <c r="L45" t="n">
-        <v>86.59</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>115.82</v>
+        <v>200.36</v>
       </c>
       <c r="K46" t="n">
-        <v>6.03</v>
+        <v>10.43</v>
       </c>
       <c r="L46" t="n">
-        <v>115.98</v>
+        <v>200.63</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-76.7</v>
+        <v>-118.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-185.31</v>
+        <v>-286.98</v>
       </c>
       <c r="L47" t="n">
-        <v>200.55</v>
+        <v>310.59</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-152.47</v>
+        <v>-214.84</v>
       </c>
       <c r="K48" t="n">
-        <v>-285.07</v>
+        <v>-401.69</v>
       </c>
       <c r="L48" t="n">
-        <v>323.28</v>
+        <v>455.53</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-172.94</v>
+        <v>-212.39</v>
       </c>
       <c r="K49" t="n">
-        <v>525.9</v>
+        <v>645.85</v>
       </c>
       <c r="L49" t="n">
-        <v>553.61</v>
+        <v>679.87</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>214.19</v>
+        <v>344.28</v>
       </c>
       <c r="K50" t="n">
-        <v>-179.72</v>
+        <v>-288.87</v>
       </c>
       <c r="L50" t="n">
-        <v>279.6</v>
+        <v>449.42</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-100.56</v>
+        <v>-274.29</v>
       </c>
       <c r="K51" t="n">
-        <v>53.85</v>
+        <v>146.87</v>
       </c>
       <c r="L51" t="n">
-        <v>114.07</v>
+        <v>311.13</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-149.68</v>
+        <v>-191.11</v>
       </c>
       <c r="K52" t="n">
-        <v>702.99</v>
+        <v>897.58</v>
       </c>
       <c r="L52" t="n">
-        <v>718.75</v>
+        <v>917.7</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>644.05</v>
+        <v>943.9299999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-78.16</v>
+        <v>-114.55</v>
       </c>
       <c r="L53" t="n">
-        <v>648.78</v>
+        <v>950.85</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-23.25</v>
+        <v>-67.52</v>
       </c>
       <c r="K54" t="n">
-        <v>154.64</v>
+        <v>449.13</v>
       </c>
       <c r="L54" t="n">
-        <v>156.38</v>
+        <v>454.18</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-455.65</v>
+        <v>-802.65</v>
       </c>
       <c r="K55" t="n">
-        <v>-44.07</v>
+        <v>-77.63</v>
       </c>
       <c r="L55" t="n">
-        <v>457.78</v>
+        <v>806.39</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-1135.83</v>
+        <v>-1549.11</v>
       </c>
       <c r="K56" t="n">
-        <v>-855.39</v>
+        <v>-1166.64</v>
       </c>
       <c r="L56" t="n">
-        <v>1421.9</v>
+        <v>1939.27</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-995.8</v>
+        <v>-1482.94</v>
       </c>
       <c r="K57" t="n">
-        <v>-134.86</v>
+        <v>-200.84</v>
       </c>
       <c r="L57" t="n">
-        <v>1004.89</v>
+        <v>1496.47</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>367.67</v>
+        <v>655.51</v>
       </c>
       <c r="K58" t="n">
-        <v>415.96</v>
+        <v>741.6</v>
       </c>
       <c r="L58" t="n">
-        <v>555.16</v>
+        <v>989.78</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-178.34</v>
+        <v>-261.15</v>
       </c>
       <c r="K59" t="n">
-        <v>-120.33</v>
+        <v>-176.21</v>
       </c>
       <c r="L59" t="n">
-        <v>215.14</v>
+        <v>315.04</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-83.31999999999999</v>
+        <v>-179.14</v>
       </c>
       <c r="K60" t="n">
-        <v>-53.34</v>
+        <v>-114.68</v>
       </c>
       <c r="L60" t="n">
-        <v>98.93000000000001</v>
+        <v>212.7</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-357.54</v>
+        <v>-410.8</v>
       </c>
       <c r="K61" t="n">
-        <v>191.99</v>
+        <v>220.59</v>
       </c>
       <c r="L61" t="n">
-        <v>405.82</v>
+        <v>466.28</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-213.51</v>
+        <v>-305.77</v>
       </c>
       <c r="K62" t="n">
-        <v>28.83</v>
+        <v>41.28</v>
       </c>
       <c r="L62" t="n">
-        <v>215.45</v>
+        <v>308.55</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>336.47</v>
+        <v>464.38</v>
       </c>
       <c r="K63" t="n">
-        <v>224.37</v>
+        <v>309.66</v>
       </c>
       <c r="L63" t="n">
-        <v>404.42</v>
+        <v>558.15</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>73.34999999999999</v>
+        <v>106.41</v>
       </c>
       <c r="K64" t="n">
-        <v>246.04</v>
+        <v>356.94</v>
       </c>
       <c r="L64" t="n">
-        <v>256.74</v>
+        <v>372.46</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>199.49</v>
+        <v>268.42</v>
       </c>
       <c r="K65" t="n">
-        <v>-481.17</v>
+        <v>-647.4299999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>520.88</v>
+        <v>700.86</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-285.33</v>
+        <v>-465.8</v>
       </c>
       <c r="K66" t="n">
-        <v>247.8</v>
+        <v>404.52</v>
       </c>
       <c r="L66" t="n">
-        <v>377.91</v>
+        <v>616.9299999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>16.59</v>
+        <v>26.3</v>
       </c>
       <c r="K67" t="n">
-        <v>380.33</v>
+        <v>603.05</v>
       </c>
       <c r="L67" t="n">
-        <v>380.69</v>
+        <v>603.62</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>195.29</v>
+        <v>307.16</v>
       </c>
       <c r="K68" t="n">
-        <v>-597.6799999999999</v>
+        <v>-940.05</v>
       </c>
       <c r="L68" t="n">
-        <v>628.77</v>
+        <v>988.96</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>88.23999999999999</v>
+        <v>128.55</v>
       </c>
       <c r="K69" t="n">
-        <v>842.7</v>
+        <v>1227.69</v>
       </c>
       <c r="L69" t="n">
-        <v>847.3</v>
+        <v>1234.4</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-818.05</v>
+        <v>-1134.38</v>
       </c>
       <c r="K70" t="n">
-        <v>608.45</v>
+        <v>843.73</v>
       </c>
       <c r="L70" t="n">
-        <v>1019.52</v>
+        <v>1413.76</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-290.4</v>
+        <v>-764.3200000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>140.75</v>
+        <v>370.45</v>
       </c>
       <c r="L71" t="n">
-        <v>322.71</v>
+        <v>849.36</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-198.06</v>
+        <v>-613.23</v>
       </c>
       <c r="K72" t="n">
-        <v>150.07</v>
+        <v>464.65</v>
       </c>
       <c r="L72" t="n">
-        <v>248.49</v>
+        <v>769.38</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>185.22</v>
+        <v>379.92</v>
       </c>
       <c r="K73" t="n">
-        <v>323.11</v>
+        <v>662.73</v>
       </c>
       <c r="L73" t="n">
-        <v>372.43</v>
+        <v>763.9</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-88.13</v>
+        <v>-138.97</v>
       </c>
       <c r="K74" t="n">
-        <v>-172.87</v>
+        <v>-272.62</v>
       </c>
       <c r="L74" t="n">
-        <v>194.04</v>
+        <v>306</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>526.46</v>
+        <v>617.24</v>
       </c>
       <c r="K75" t="n">
-        <v>86.79000000000001</v>
+        <v>101.76</v>
       </c>
       <c r="L75" t="n">
-        <v>533.5700000000001</v>
+        <v>625.5700000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>4.14</v>
+        <v>10.01</v>
       </c>
       <c r="K76" t="n">
-        <v>-97.39</v>
+        <v>-235.48</v>
       </c>
       <c r="L76" t="n">
-        <v>97.48</v>
+        <v>235.69</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-283.07</v>
+        <v>-405.45</v>
       </c>
       <c r="K77" t="n">
-        <v>-100.56</v>
+        <v>-144.03</v>
       </c>
       <c r="L77" t="n">
-        <v>300.41</v>
+        <v>430.27</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>294.23</v>
+        <v>411.19</v>
       </c>
       <c r="K78" t="n">
-        <v>113.6</v>
+        <v>158.76</v>
       </c>
       <c r="L78" t="n">
-        <v>315.4</v>
+        <v>440.78</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>335.64</v>
+        <v>450.37</v>
       </c>
       <c r="K79" t="n">
-        <v>167.75</v>
+        <v>225.09</v>
       </c>
       <c r="L79" t="n">
-        <v>375.23</v>
+        <v>503.49</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-551.6799999999999</v>
+        <v>-777.33</v>
       </c>
       <c r="K80" t="n">
-        <v>-225.06</v>
+        <v>-317.12</v>
       </c>
       <c r="L80" t="n">
-        <v>595.83</v>
+        <v>839.52</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>303.74</v>
+        <v>409.45</v>
       </c>
       <c r="K81" t="n">
-        <v>574.4</v>
+        <v>774.3200000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>649.76</v>
+        <v>875.91</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-384.2</v>
+        <v>-485.37</v>
       </c>
       <c r="K82" t="n">
-        <v>518.52</v>
+        <v>655.0599999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>645.34</v>
+        <v>815.28</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-188.67</v>
+        <v>-317.7</v>
       </c>
       <c r="K83" t="n">
-        <v>472.97</v>
+        <v>796.45</v>
       </c>
       <c r="L83" t="n">
-        <v>509.21</v>
+        <v>857.48</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-814.03</v>
+        <v>-1154.89</v>
       </c>
       <c r="K84" t="n">
-        <v>531.22</v>
+        <v>753.65</v>
       </c>
       <c r="L84" t="n">
-        <v>972.03</v>
+        <v>1379.05</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>396.79</v>
+        <v>687.98</v>
       </c>
       <c r="K85" t="n">
-        <v>-69.41</v>
+        <v>-120.35</v>
       </c>
       <c r="L85" t="n">
-        <v>402.82</v>
+        <v>698.42</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>732.87</v>
+        <v>1132.64</v>
       </c>
       <c r="K86" t="n">
-        <v>-709.63</v>
+        <v>-1096.72</v>
       </c>
       <c r="L86" t="n">
-        <v>1020.13</v>
+        <v>1576.6</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>426.8</v>
+        <v>916.99</v>
       </c>
       <c r="K87" t="n">
-        <v>-210.08</v>
+        <v>-451.35</v>
       </c>
       <c r="L87" t="n">
-        <v>475.7</v>
+        <v>1022.05</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-276.11</v>
+        <v>-753.8200000000001</v>
       </c>
       <c r="K88" t="n">
-        <v>192.09</v>
+        <v>524.45</v>
       </c>
       <c r="L88" t="n">
-        <v>336.35</v>
+        <v>918.3099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>532.87</v>
+        <v>312.77</v>
       </c>
       <c r="K14" t="n">
-        <v>-114.54</v>
+        <v>-67.23</v>
       </c>
       <c r="L14" t="n">
-        <v>545.04</v>
+        <v>319.91</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-120.2</v>
+        <v>-70.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-318.24</v>
+        <v>-187.18</v>
       </c>
       <c r="L15" t="n">
-        <v>340.18</v>
+        <v>200.08</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>117.57</v>
+        <v>70.58</v>
       </c>
       <c r="K16" t="n">
-        <v>229.49</v>
+        <v>137.77</v>
       </c>
       <c r="L16" t="n">
-        <v>257.86</v>
+        <v>154.8</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>424.92</v>
+        <v>260.63</v>
       </c>
       <c r="K17" t="n">
-        <v>4.36</v>
+        <v>2.67</v>
       </c>
       <c r="L17" t="n">
-        <v>424.95</v>
+        <v>260.65</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>276.29</v>
+        <v>167.2</v>
       </c>
       <c r="K18" t="n">
-        <v>-238.52</v>
+        <v>-144.34</v>
       </c>
       <c r="L18" t="n">
-        <v>365</v>
+        <v>220.88</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-18.78</v>
+        <v>-10.69</v>
       </c>
       <c r="K19" t="n">
-        <v>-363.91</v>
+        <v>-207.22</v>
       </c>
       <c r="L19" t="n">
-        <v>364.39</v>
+        <v>207.5</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-122.22</v>
+        <v>-63.12</v>
       </c>
       <c r="K20" t="n">
-        <v>-482.69</v>
+        <v>-249.26</v>
       </c>
       <c r="L20" t="n">
-        <v>497.92</v>
+        <v>257.13</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>485.77</v>
+        <v>252.26</v>
       </c>
       <c r="K21" t="n">
-        <v>107.13</v>
+        <v>55.63</v>
       </c>
       <c r="L21" t="n">
-        <v>497.44</v>
+        <v>258.32</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>402.91</v>
+        <v>202.46</v>
       </c>
       <c r="K22" t="n">
-        <v>-105.13</v>
+        <v>-52.83</v>
       </c>
       <c r="L22" t="n">
-        <v>416.4</v>
+        <v>209.24</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-715.79</v>
+        <v>-321.23</v>
       </c>
       <c r="K23" t="n">
-        <v>25.97</v>
+        <v>11.65</v>
       </c>
       <c r="L23" t="n">
-        <v>716.26</v>
+        <v>321.44</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>27.64</v>
+        <v>12.32</v>
       </c>
       <c r="K24" t="n">
-        <v>803.97</v>
+        <v>358.42</v>
       </c>
       <c r="L24" t="n">
-        <v>804.4400000000001</v>
+        <v>358.64</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>193.46</v>
+        <v>91.52</v>
       </c>
       <c r="K25" t="n">
-        <v>394.75</v>
+        <v>186.74</v>
       </c>
       <c r="L25" t="n">
-        <v>439.6</v>
+        <v>207.96</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>906.33</v>
+        <v>386.67</v>
       </c>
       <c r="K26" t="n">
-        <v>-164.58</v>
+        <v>-70.20999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>921.15</v>
+        <v>392.99</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>86.52</v>
+        <v>37.08</v>
       </c>
       <c r="K27" t="n">
-        <v>583.28</v>
+        <v>249.98</v>
       </c>
       <c r="L27" t="n">
-        <v>589.66</v>
+        <v>252.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>78.84</v>
+        <v>31.97</v>
       </c>
       <c r="K28" t="n">
-        <v>662.05</v>
+        <v>268.43</v>
       </c>
       <c r="L28" t="n">
-        <v>666.73</v>
+        <v>270.33</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>391.62</v>
+        <v>229.21</v>
       </c>
       <c r="K29" t="n">
-        <v>-179.8</v>
+        <v>-105.23</v>
       </c>
       <c r="L29" t="n">
-        <v>430.92</v>
+        <v>252.22</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-235.89</v>
+        <v>-147.84</v>
       </c>
       <c r="K30" t="n">
-        <v>-219.7</v>
+        <v>-137.69</v>
       </c>
       <c r="L30" t="n">
-        <v>322.36</v>
+        <v>202.03</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-58.36</v>
+        <v>-34.3</v>
       </c>
       <c r="K31" t="n">
-        <v>539.97</v>
+        <v>317.41</v>
       </c>
       <c r="L31" t="n">
-        <v>543.12</v>
+        <v>319.25</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-276.35</v>
+        <v>-164.25</v>
       </c>
       <c r="K32" t="n">
-        <v>-250.49</v>
+        <v>-148.88</v>
       </c>
       <c r="L32" t="n">
-        <v>372.98</v>
+        <v>221.68</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-309.38</v>
+        <v>-184.5</v>
       </c>
       <c r="K33" t="n">
-        <v>45.55</v>
+        <v>27.16</v>
       </c>
       <c r="L33" t="n">
-        <v>312.71</v>
+        <v>186.49</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>260.15</v>
+        <v>150.37</v>
       </c>
       <c r="K34" t="n">
-        <v>78.43000000000001</v>
+        <v>45.33</v>
       </c>
       <c r="L34" t="n">
-        <v>271.71</v>
+        <v>157.06</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>651.49</v>
+        <v>326.24</v>
       </c>
       <c r="K35" t="n">
-        <v>-124.08</v>
+        <v>-62.13</v>
       </c>
       <c r="L35" t="n">
-        <v>663.21</v>
+        <v>332.11</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-333.83</v>
+        <v>-170.12</v>
       </c>
       <c r="K36" t="n">
-        <v>-211.36</v>
+        <v>-107.71</v>
       </c>
       <c r="L36" t="n">
-        <v>395.12</v>
+        <v>201.35</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>621.72</v>
+        <v>306.94</v>
       </c>
       <c r="K37" t="n">
-        <v>-443.19</v>
+        <v>-218.8</v>
       </c>
       <c r="L37" t="n">
-        <v>763.51</v>
+        <v>376.94</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-477.72</v>
+        <v>-209.99</v>
       </c>
       <c r="K38" t="n">
-        <v>875.83</v>
+        <v>384.99</v>
       </c>
       <c r="L38" t="n">
-        <v>997.64</v>
+        <v>438.54</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-874.45</v>
+        <v>-401.87</v>
       </c>
       <c r="K39" t="n">
-        <v>-1361.79</v>
+        <v>-625.84</v>
       </c>
       <c r="L39" t="n">
-        <v>1618.37</v>
+        <v>743.76</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-106.99</v>
+        <v>-46.48</v>
       </c>
       <c r="K40" t="n">
-        <v>708.5599999999999</v>
+        <v>307.8</v>
       </c>
       <c r="L40" t="n">
-        <v>716.59</v>
+        <v>311.29</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-1063.96</v>
+        <v>-423.25</v>
       </c>
       <c r="K41" t="n">
-        <v>-62.63</v>
+        <v>-24.91</v>
       </c>
       <c r="L41" t="n">
-        <v>1065.8</v>
+        <v>423.99</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>1035.93</v>
+        <v>437.78</v>
       </c>
       <c r="K42" t="n">
-        <v>-633.64</v>
+        <v>-267.77</v>
       </c>
       <c r="L42" t="n">
-        <v>1214.35</v>
+        <v>513.1799999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>1941.21</v>
+        <v>826.0700000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>199.83</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>1951.47</v>
+        <v>830.4400000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-465.11</v>
+        <v>-273.88</v>
       </c>
       <c r="K44" t="n">
-        <v>-376.8</v>
+        <v>-221.88</v>
       </c>
       <c r="L44" t="n">
-        <v>598.59</v>
+        <v>352.48</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.64</v>
+        <v>-21.02</v>
       </c>
       <c r="K45" t="n">
-        <v>178.86</v>
+        <v>108.51</v>
       </c>
       <c r="L45" t="n">
-        <v>182.19</v>
+        <v>110.52</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>200.36</v>
+        <v>122.53</v>
       </c>
       <c r="K46" t="n">
-        <v>10.43</v>
+        <v>6.38</v>
       </c>
       <c r="L46" t="n">
-        <v>200.63</v>
+        <v>122.7</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-118.78</v>
+        <v>-69.13</v>
       </c>
       <c r="K47" t="n">
-        <v>-286.98</v>
+        <v>-167.02</v>
       </c>
       <c r="L47" t="n">
-        <v>310.59</v>
+        <v>180.76</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-214.84</v>
+        <v>-120.26</v>
       </c>
       <c r="K48" t="n">
-        <v>-401.69</v>
+        <v>-224.85</v>
       </c>
       <c r="L48" t="n">
-        <v>455.53</v>
+        <v>254.99</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-212.39</v>
+        <v>-118.46</v>
       </c>
       <c r="K49" t="n">
-        <v>645.85</v>
+        <v>360.23</v>
       </c>
       <c r="L49" t="n">
-        <v>679.87</v>
+        <v>379.21</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>344.28</v>
+        <v>181.61</v>
       </c>
       <c r="K50" t="n">
-        <v>-288.87</v>
+        <v>-152.38</v>
       </c>
       <c r="L50" t="n">
-        <v>449.42</v>
+        <v>237.07</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-274.29</v>
+        <v>-140.31</v>
       </c>
       <c r="K51" t="n">
-        <v>146.87</v>
+        <v>75.13</v>
       </c>
       <c r="L51" t="n">
-        <v>311.13</v>
+        <v>159.16</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-191.11</v>
+        <v>-94.27</v>
       </c>
       <c r="K52" t="n">
-        <v>897.58</v>
+        <v>442.75</v>
       </c>
       <c r="L52" t="n">
-        <v>917.7</v>
+        <v>452.67</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>943.9299999999999</v>
+        <v>415.74</v>
       </c>
       <c r="K53" t="n">
-        <v>-114.55</v>
+        <v>-50.45</v>
       </c>
       <c r="L53" t="n">
-        <v>950.85</v>
+        <v>418.79</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-67.52</v>
+        <v>-30.73</v>
       </c>
       <c r="K54" t="n">
-        <v>449.13</v>
+        <v>204.38</v>
       </c>
       <c r="L54" t="n">
-        <v>454.18</v>
+        <v>206.68</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-802.65</v>
+        <v>-348.23</v>
       </c>
       <c r="K55" t="n">
-        <v>-77.63</v>
+        <v>-33.68</v>
       </c>
       <c r="L55" t="n">
-        <v>806.39</v>
+        <v>349.86</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-1549.11</v>
+        <v>-617.6</v>
       </c>
       <c r="K56" t="n">
-        <v>-1166.64</v>
+        <v>-465.12</v>
       </c>
       <c r="L56" t="n">
-        <v>1939.27</v>
+        <v>773.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-1482.94</v>
+        <v>-612.35</v>
       </c>
       <c r="K57" t="n">
-        <v>-200.84</v>
+        <v>-82.93000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>1496.47</v>
+        <v>617.9400000000001</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>655.51</v>
+        <v>266.23</v>
       </c>
       <c r="K58" t="n">
-        <v>741.6</v>
+        <v>301.19</v>
       </c>
       <c r="L58" t="n">
-        <v>989.78</v>
+        <v>401.99</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-261.15</v>
+        <v>-156.17</v>
       </c>
       <c r="K59" t="n">
-        <v>-176.21</v>
+        <v>-105.38</v>
       </c>
       <c r="L59" t="n">
-        <v>315.04</v>
+        <v>188.4</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-179.14</v>
+        <v>-106.95</v>
       </c>
       <c r="K60" t="n">
-        <v>-114.68</v>
+        <v>-68.47</v>
       </c>
       <c r="L60" t="n">
-        <v>212.7</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-410.8</v>
+        <v>-253.08</v>
       </c>
       <c r="K61" t="n">
-        <v>220.59</v>
+        <v>135.9</v>
       </c>
       <c r="L61" t="n">
-        <v>466.28</v>
+        <v>287.26</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-305.77</v>
+        <v>-187.15</v>
       </c>
       <c r="K62" t="n">
-        <v>41.28</v>
+        <v>25.27</v>
       </c>
       <c r="L62" t="n">
-        <v>308.55</v>
+        <v>188.85</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>464.38</v>
+        <v>256.94</v>
       </c>
       <c r="K63" t="n">
-        <v>309.66</v>
+        <v>171.34</v>
       </c>
       <c r="L63" t="n">
-        <v>558.15</v>
+        <v>308.83</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>106.41</v>
+        <v>60.47</v>
       </c>
       <c r="K64" t="n">
-        <v>356.94</v>
+        <v>202.84</v>
       </c>
       <c r="L64" t="n">
-        <v>372.46</v>
+        <v>211.67</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>268.42</v>
+        <v>140.36</v>
       </c>
       <c r="K65" t="n">
-        <v>-647.4299999999999</v>
+        <v>-338.56</v>
       </c>
       <c r="L65" t="n">
-        <v>700.86</v>
+        <v>366.51</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-465.8</v>
+        <v>-225.67</v>
       </c>
       <c r="K66" t="n">
-        <v>404.52</v>
+        <v>195.98</v>
       </c>
       <c r="L66" t="n">
-        <v>616.9299999999999</v>
+        <v>298.89</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>26.3</v>
+        <v>12.82</v>
       </c>
       <c r="K67" t="n">
-        <v>603.05</v>
+        <v>293.98</v>
       </c>
       <c r="L67" t="n">
-        <v>603.62</v>
+        <v>294.26</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>307.16</v>
+        <v>135.73</v>
       </c>
       <c r="K68" t="n">
-        <v>-940.05</v>
+        <v>-415.4</v>
       </c>
       <c r="L68" t="n">
-        <v>988.96</v>
+        <v>437.01</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>128.55</v>
+        <v>58.03</v>
       </c>
       <c r="K69" t="n">
-        <v>1227.69</v>
+        <v>554.21</v>
       </c>
       <c r="L69" t="n">
-        <v>1234.4</v>
+        <v>557.24</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-1134.38</v>
+        <v>-519.3099999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>843.73</v>
+        <v>386.26</v>
       </c>
       <c r="L70" t="n">
-        <v>1413.76</v>
+        <v>647.21</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-764.3200000000001</v>
+        <v>-297.86</v>
       </c>
       <c r="K71" t="n">
-        <v>370.45</v>
+        <v>144.37</v>
       </c>
       <c r="L71" t="n">
-        <v>849.36</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-613.23</v>
+        <v>-238.73</v>
       </c>
       <c r="K72" t="n">
-        <v>464.65</v>
+        <v>180.88</v>
       </c>
       <c r="L72" t="n">
-        <v>769.38</v>
+        <v>299.52</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>379.92</v>
+        <v>158.47</v>
       </c>
       <c r="K73" t="n">
-        <v>662.73</v>
+        <v>276.43</v>
       </c>
       <c r="L73" t="n">
-        <v>763.9</v>
+        <v>318.63</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-138.97</v>
+        <v>-84.27</v>
       </c>
       <c r="K74" t="n">
-        <v>-272.62</v>
+        <v>-165.31</v>
       </c>
       <c r="L74" t="n">
-        <v>306</v>
+        <v>185.55</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>617.24</v>
+        <v>358.63</v>
       </c>
       <c r="K75" t="n">
-        <v>101.76</v>
+        <v>59.12</v>
       </c>
       <c r="L75" t="n">
-        <v>625.5700000000001</v>
+        <v>363.47</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>10.01</v>
+        <v>5.78</v>
       </c>
       <c r="K76" t="n">
-        <v>-235.48</v>
+        <v>-135.96</v>
       </c>
       <c r="L76" t="n">
-        <v>235.69</v>
+        <v>136.08</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-405.45</v>
+        <v>-236.32</v>
       </c>
       <c r="K77" t="n">
-        <v>-144.03</v>
+        <v>-83.95</v>
       </c>
       <c r="L77" t="n">
-        <v>430.27</v>
+        <v>250.79</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>411.19</v>
+        <v>231.6</v>
       </c>
       <c r="K78" t="n">
-        <v>158.76</v>
+        <v>89.42</v>
       </c>
       <c r="L78" t="n">
-        <v>440.78</v>
+        <v>248.26</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>450.37</v>
+        <v>252.61</v>
       </c>
       <c r="K79" t="n">
-        <v>225.09</v>
+        <v>126.25</v>
       </c>
       <c r="L79" t="n">
-        <v>503.49</v>
+        <v>282.4</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-777.33</v>
+        <v>-376.68</v>
       </c>
       <c r="K80" t="n">
-        <v>-317.12</v>
+        <v>-153.67</v>
       </c>
       <c r="L80" t="n">
-        <v>839.52</v>
+        <v>406.82</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>409.45</v>
+        <v>210.71</v>
       </c>
       <c r="K81" t="n">
-        <v>774.3200000000001</v>
+        <v>398.49</v>
       </c>
       <c r="L81" t="n">
-        <v>875.91</v>
+        <v>450.77</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-485.37</v>
+        <v>-254.36</v>
       </c>
       <c r="K82" t="n">
-        <v>655.0599999999999</v>
+        <v>343.28</v>
       </c>
       <c r="L82" t="n">
-        <v>815.28</v>
+        <v>427.25</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-317.7</v>
+        <v>-138.33</v>
       </c>
       <c r="K83" t="n">
-        <v>796.45</v>
+        <v>346.77</v>
       </c>
       <c r="L83" t="n">
-        <v>857.48</v>
+        <v>373.34</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-1154.89</v>
+        <v>-499.02</v>
       </c>
       <c r="K84" t="n">
-        <v>753.65</v>
+        <v>325.65</v>
       </c>
       <c r="L84" t="n">
-        <v>1379.05</v>
+        <v>595.88</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>687.98</v>
+        <v>321.27</v>
       </c>
       <c r="K85" t="n">
-        <v>-120.35</v>
+        <v>-56.2</v>
       </c>
       <c r="L85" t="n">
-        <v>698.42</v>
+        <v>326.15</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>1132.64</v>
+        <v>446.94</v>
       </c>
       <c r="K86" t="n">
-        <v>-1096.72</v>
+        <v>-432.76</v>
       </c>
       <c r="L86" t="n">
-        <v>1576.6</v>
+        <v>622.12</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>916.99</v>
+        <v>358.21</v>
       </c>
       <c r="K87" t="n">
-        <v>-451.35</v>
+        <v>-176.32</v>
       </c>
       <c r="L87" t="n">
-        <v>1022.05</v>
+        <v>399.26</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-753.8200000000001</v>
+        <v>-291.65</v>
       </c>
       <c r="K88" t="n">
-        <v>524.45</v>
+        <v>202.91</v>
       </c>
       <c r="L88" t="n">
-        <v>918.3099999999999</v>
+        <v>355.29</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>312.77</v>
+        <v>341.05</v>
       </c>
       <c r="K14" t="n">
-        <v>-67.23</v>
+        <v>-73.31</v>
       </c>
       <c r="L14" t="n">
-        <v>319.91</v>
+        <v>348.84</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-70.7</v>
+        <v>-77.05</v>
       </c>
       <c r="K15" t="n">
-        <v>-187.18</v>
+        <v>-203.99</v>
       </c>
       <c r="L15" t="n">
-        <v>200.08</v>
+        <v>218.06</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>70.58</v>
+        <v>76.34</v>
       </c>
       <c r="K16" t="n">
-        <v>137.77</v>
+        <v>149</v>
       </c>
       <c r="L16" t="n">
-        <v>154.8</v>
+        <v>167.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>260.63</v>
+        <v>280.78</v>
       </c>
       <c r="K17" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="L17" t="n">
-        <v>260.65</v>
+        <v>280.8</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>167.2</v>
+        <v>181.75</v>
       </c>
       <c r="K18" t="n">
-        <v>-144.34</v>
+        <v>-156.91</v>
       </c>
       <c r="L18" t="n">
-        <v>220.88</v>
+        <v>240.11</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.69</v>
+        <v>-11.73</v>
       </c>
       <c r="K19" t="n">
-        <v>-207.22</v>
+        <v>-227.19</v>
       </c>
       <c r="L19" t="n">
-        <v>207.5</v>
+        <v>227.49</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-63.12</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-249.26</v>
+        <v>-280.22</v>
       </c>
       <c r="L20" t="n">
-        <v>257.13</v>
+        <v>289.07</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>252.26</v>
+        <v>284.01</v>
       </c>
       <c r="K21" t="n">
-        <v>55.63</v>
+        <v>62.63</v>
       </c>
       <c r="L21" t="n">
-        <v>258.32</v>
+        <v>290.83</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>202.46</v>
+        <v>230.28</v>
       </c>
       <c r="K22" t="n">
-        <v>-52.83</v>
+        <v>-60.09</v>
       </c>
       <c r="L22" t="n">
-        <v>209.24</v>
+        <v>237.99</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-321.23</v>
+        <v>-371.61</v>
       </c>
       <c r="K23" t="n">
-        <v>11.65</v>
+        <v>13.48</v>
       </c>
       <c r="L23" t="n">
-        <v>321.44</v>
+        <v>371.86</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>12.32</v>
+        <v>14.38</v>
       </c>
       <c r="K24" t="n">
-        <v>358.42</v>
+        <v>418.22</v>
       </c>
       <c r="L24" t="n">
-        <v>358.64</v>
+        <v>418.47</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>91.52</v>
+        <v>106.46</v>
       </c>
       <c r="K25" t="n">
-        <v>186.74</v>
+        <v>217.24</v>
       </c>
       <c r="L25" t="n">
-        <v>207.96</v>
+        <v>241.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>386.67</v>
+        <v>458.09</v>
       </c>
       <c r="K26" t="n">
-        <v>-70.20999999999999</v>
+        <v>-83.18000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>392.99</v>
+        <v>465.59</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>37.08</v>
+        <v>43.97</v>
       </c>
       <c r="K27" t="n">
-        <v>249.98</v>
+        <v>296.42</v>
       </c>
       <c r="L27" t="n">
-        <v>252.72</v>
+        <v>299.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>31.97</v>
+        <v>38.19</v>
       </c>
       <c r="K28" t="n">
-        <v>268.43</v>
+        <v>320.71</v>
       </c>
       <c r="L28" t="n">
-        <v>270.33</v>
+        <v>322.97</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>229.21</v>
+        <v>248.81</v>
       </c>
       <c r="K29" t="n">
-        <v>-105.23</v>
+        <v>-114.23</v>
       </c>
       <c r="L29" t="n">
-        <v>252.22</v>
+        <v>273.78</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-147.84</v>
+        <v>-159.27</v>
       </c>
       <c r="K30" t="n">
-        <v>-137.69</v>
+        <v>-148.34</v>
       </c>
       <c r="L30" t="n">
-        <v>202.03</v>
+        <v>217.65</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-34.3</v>
+        <v>-37.43</v>
       </c>
       <c r="K31" t="n">
-        <v>317.41</v>
+        <v>346.37</v>
       </c>
       <c r="L31" t="n">
-        <v>319.25</v>
+        <v>348.39</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-164.25</v>
+        <v>-178.37</v>
       </c>
       <c r="K32" t="n">
-        <v>-148.88</v>
+        <v>-161.67</v>
       </c>
       <c r="L32" t="n">
-        <v>221.68</v>
+        <v>240.74</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>-184.5</v>
+        <v>-200.75</v>
       </c>
       <c r="K33" t="n">
-        <v>27.16</v>
+        <v>29.56</v>
       </c>
       <c r="L33" t="n">
-        <v>186.49</v>
+        <v>202.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>17</v>
       </c>
       <c r="J34" t="n">
-        <v>150.37</v>
+        <v>163.9</v>
       </c>
       <c r="K34" t="n">
-        <v>45.33</v>
+        <v>49.41</v>
       </c>
       <c r="L34" t="n">
-        <v>157.06</v>
+        <v>171.19</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>17</v>
       </c>
       <c r="J35" t="n">
-        <v>326.24</v>
+        <v>369.63</v>
       </c>
       <c r="K35" t="n">
-        <v>-62.13</v>
+        <v>-70.40000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>332.11</v>
+        <v>376.28</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-170.12</v>
+        <v>-191.28</v>
       </c>
       <c r="K36" t="n">
-        <v>-107.71</v>
+        <v>-121.1</v>
       </c>
       <c r="L36" t="n">
-        <v>201.35</v>
+        <v>226.39</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>306.94</v>
+        <v>349.16</v>
       </c>
       <c r="K37" t="n">
-        <v>-218.8</v>
+        <v>-248.9</v>
       </c>
       <c r="L37" t="n">
-        <v>376.94</v>
+        <v>428.79</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-209.99</v>
+        <v>-244.35</v>
       </c>
       <c r="K38" t="n">
-        <v>384.99</v>
+        <v>447.98</v>
       </c>
       <c r="L38" t="n">
-        <v>438.54</v>
+        <v>510.29</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-401.87</v>
+        <v>-462</v>
       </c>
       <c r="K39" t="n">
-        <v>-625.84</v>
+        <v>-719.47</v>
       </c>
       <c r="L39" t="n">
-        <v>743.76</v>
+        <v>855.04</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-46.48</v>
+        <v>-53.83</v>
       </c>
       <c r="K40" t="n">
-        <v>307.8</v>
+        <v>356.48</v>
       </c>
       <c r="L40" t="n">
-        <v>311.29</v>
+        <v>360.52</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-423.25</v>
+        <v>-500.86</v>
       </c>
       <c r="K41" t="n">
-        <v>-24.91</v>
+        <v>-29.48</v>
       </c>
       <c r="L41" t="n">
-        <v>423.99</v>
+        <v>501.73</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>437.78</v>
+        <v>520.34</v>
       </c>
       <c r="K42" t="n">
-        <v>-267.77</v>
+        <v>-318.27</v>
       </c>
       <c r="L42" t="n">
-        <v>513.1799999999999</v>
+        <v>609.96</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>826.0700000000001</v>
+        <v>974.6900000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>85.04000000000001</v>
+        <v>100.34</v>
       </c>
       <c r="L43" t="n">
-        <v>830.4400000000001</v>
+        <v>979.84</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-273.88</v>
+        <v>-297.11</v>
       </c>
       <c r="K44" t="n">
-        <v>-221.88</v>
+        <v>-240.7</v>
       </c>
       <c r="L44" t="n">
-        <v>352.48</v>
+        <v>382.38</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>-21.02</v>
+        <v>-22.6</v>
       </c>
       <c r="K45" t="n">
-        <v>108.51</v>
+        <v>116.69</v>
       </c>
       <c r="L45" t="n">
-        <v>110.52</v>
+        <v>118.86</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>122.53</v>
+        <v>131.26</v>
       </c>
       <c r="K46" t="n">
-        <v>6.38</v>
+        <v>6.84</v>
       </c>
       <c r="L46" t="n">
-        <v>122.7</v>
+        <v>131.44</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-69.13</v>
+        <v>-75.06999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-167.02</v>
+        <v>-181.39</v>
       </c>
       <c r="L47" t="n">
-        <v>180.76</v>
+        <v>196.31</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-120.26</v>
+        <v>-131.99</v>
       </c>
       <c r="K48" t="n">
-        <v>-224.85</v>
+        <v>-246.78</v>
       </c>
       <c r="L48" t="n">
-        <v>254.99</v>
+        <v>279.87</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-118.46</v>
+        <v>-130.86</v>
       </c>
       <c r="K49" t="n">
-        <v>360.23</v>
+        <v>397.93</v>
       </c>
       <c r="L49" t="n">
-        <v>379.21</v>
+        <v>418.89</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>181.61</v>
+        <v>204.5</v>
       </c>
       <c r="K50" t="n">
-        <v>-152.38</v>
+        <v>-171.59</v>
       </c>
       <c r="L50" t="n">
-        <v>237.07</v>
+        <v>266.95</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>18</v>
       </c>
       <c r="J51" t="n">
-        <v>-140.31</v>
+        <v>-157.5</v>
       </c>
       <c r="K51" t="n">
-        <v>75.13</v>
+        <v>84.34</v>
       </c>
       <c r="L51" t="n">
-        <v>159.16</v>
+        <v>178.66</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-94.27</v>
+        <v>-106.98</v>
       </c>
       <c r="K52" t="n">
-        <v>442.75</v>
+        <v>502.45</v>
       </c>
       <c r="L52" t="n">
-        <v>452.67</v>
+        <v>513.71</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>415.74</v>
+        <v>483.24</v>
       </c>
       <c r="K53" t="n">
-        <v>-50.45</v>
+        <v>-58.64</v>
       </c>
       <c r="L53" t="n">
-        <v>418.79</v>
+        <v>486.79</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-30.73</v>
+        <v>-35.56</v>
       </c>
       <c r="K54" t="n">
-        <v>204.38</v>
+        <v>236.55</v>
       </c>
       <c r="L54" t="n">
-        <v>206.68</v>
+        <v>239.21</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-348.23</v>
+        <v>-405.76</v>
       </c>
       <c r="K55" t="n">
-        <v>-33.68</v>
+        <v>-39.24</v>
       </c>
       <c r="L55" t="n">
-        <v>349.86</v>
+        <v>407.65</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-617.6</v>
+        <v>-736.4400000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-465.12</v>
+        <v>-554.62</v>
       </c>
       <c r="L56" t="n">
-        <v>773.16</v>
+        <v>921.9299999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-612.35</v>
+        <v>-724.8200000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>-82.93000000000001</v>
+        <v>-98.16</v>
       </c>
       <c r="L57" t="n">
-        <v>617.9400000000001</v>
+        <v>731.4299999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>266.23</v>
+        <v>322.3</v>
       </c>
       <c r="K58" t="n">
-        <v>301.19</v>
+        <v>364.63</v>
       </c>
       <c r="L58" t="n">
-        <v>401.99</v>
+        <v>486.65</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-156.17</v>
+        <v>-170.49</v>
       </c>
       <c r="K59" t="n">
-        <v>-105.38</v>
+        <v>-115.04</v>
       </c>
       <c r="L59" t="n">
-        <v>188.4</v>
+        <v>205.67</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-106.95</v>
+        <v>-117.01</v>
       </c>
       <c r="K60" t="n">
-        <v>-68.47</v>
+        <v>-74.91</v>
       </c>
       <c r="L60" t="n">
-        <v>127</v>
+        <v>138.93</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-253.08</v>
+        <v>-275.8</v>
       </c>
       <c r="K61" t="n">
-        <v>135.9</v>
+        <v>148.1</v>
       </c>
       <c r="L61" t="n">
-        <v>287.26</v>
+        <v>313.04</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-187.15</v>
+        <v>-200.9</v>
       </c>
       <c r="K62" t="n">
-        <v>25.27</v>
+        <v>27.12</v>
       </c>
       <c r="L62" t="n">
-        <v>188.85</v>
+        <v>202.72</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>256.94</v>
+        <v>282.9</v>
       </c>
       <c r="K63" t="n">
-        <v>171.34</v>
+        <v>188.65</v>
       </c>
       <c r="L63" t="n">
-        <v>308.83</v>
+        <v>340.03</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>60.47</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>202.84</v>
+        <v>221.73</v>
       </c>
       <c r="L64" t="n">
-        <v>211.67</v>
+        <v>231.37</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>140.36</v>
+        <v>158.01</v>
       </c>
       <c r="K65" t="n">
-        <v>-338.56</v>
+        <v>-381.12</v>
       </c>
       <c r="L65" t="n">
-        <v>366.51</v>
+        <v>412.58</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-225.67</v>
+        <v>-256.72</v>
       </c>
       <c r="K66" t="n">
-        <v>195.98</v>
+        <v>222.94</v>
       </c>
       <c r="L66" t="n">
-        <v>298.89</v>
+        <v>340.01</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>12.82</v>
+        <v>14.7</v>
       </c>
       <c r="K67" t="n">
-        <v>293.98</v>
+        <v>337.03</v>
       </c>
       <c r="L67" t="n">
-        <v>294.26</v>
+        <v>337.35</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>135.73</v>
+        <v>157.53</v>
       </c>
       <c r="K68" t="n">
-        <v>-415.4</v>
+        <v>-482.11</v>
       </c>
       <c r="L68" t="n">
-        <v>437.01</v>
+        <v>507.19</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>58.03</v>
+        <v>67.17</v>
       </c>
       <c r="K69" t="n">
-        <v>554.21</v>
+        <v>641.48</v>
       </c>
       <c r="L69" t="n">
-        <v>557.24</v>
+        <v>644.99</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-519.3099999999999</v>
+        <v>-594.25</v>
       </c>
       <c r="K70" t="n">
-        <v>386.26</v>
+        <v>441.99</v>
       </c>
       <c r="L70" t="n">
-        <v>647.21</v>
+        <v>740.6</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-297.86</v>
+        <v>-354.73</v>
       </c>
       <c r="K71" t="n">
-        <v>144.37</v>
+        <v>171.93</v>
       </c>
       <c r="L71" t="n">
-        <v>331</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-238.73</v>
+        <v>-282.79</v>
       </c>
       <c r="K72" t="n">
-        <v>180.88</v>
+        <v>214.27</v>
       </c>
       <c r="L72" t="n">
-        <v>299.52</v>
+        <v>354.79</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>158.47</v>
+        <v>189.06</v>
       </c>
       <c r="K73" t="n">
-        <v>276.43</v>
+        <v>329.81</v>
       </c>
       <c r="L73" t="n">
-        <v>318.63</v>
+        <v>380.15</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-84.27</v>
+        <v>-91.15000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-165.31</v>
+        <v>-178.81</v>
       </c>
       <c r="L74" t="n">
-        <v>185.55</v>
+        <v>200.7</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>358.63</v>
+        <v>391.72</v>
       </c>
       <c r="K75" t="n">
-        <v>59.12</v>
+        <v>64.58</v>
       </c>
       <c r="L75" t="n">
-        <v>363.47</v>
+        <v>397</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>5.78</v>
+        <v>6.34</v>
       </c>
       <c r="K76" t="n">
-        <v>-135.96</v>
+        <v>-149.28</v>
       </c>
       <c r="L76" t="n">
-        <v>136.08</v>
+        <v>149.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-236.32</v>
+        <v>-258.9</v>
       </c>
       <c r="K77" t="n">
-        <v>-83.95</v>
+        <v>-91.97</v>
       </c>
       <c r="L77" t="n">
-        <v>250.79</v>
+        <v>274.75</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>231.6</v>
+        <v>252.77</v>
       </c>
       <c r="K78" t="n">
-        <v>89.42</v>
+        <v>97.59</v>
       </c>
       <c r="L78" t="n">
-        <v>248.26</v>
+        <v>270.96</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>252.61</v>
+        <v>274.27</v>
       </c>
       <c r="K79" t="n">
-        <v>126.25</v>
+        <v>137.07</v>
       </c>
       <c r="L79" t="n">
-        <v>282.4</v>
+        <v>306.62</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-376.68</v>
+        <v>-428.91</v>
       </c>
       <c r="K80" t="n">
-        <v>-153.67</v>
+        <v>-174.98</v>
       </c>
       <c r="L80" t="n">
-        <v>406.82</v>
+        <v>463.23</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>210.71</v>
+        <v>237.4</v>
       </c>
       <c r="K81" t="n">
-        <v>398.49</v>
+        <v>448.94</v>
       </c>
       <c r="L81" t="n">
-        <v>450.77</v>
+        <v>507.84</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-254.36</v>
+        <v>-286.91</v>
       </c>
       <c r="K82" t="n">
-        <v>343.28</v>
+        <v>387.22</v>
       </c>
       <c r="L82" t="n">
-        <v>427.25</v>
+        <v>481.93</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-138.33</v>
+        <v>-162.45</v>
       </c>
       <c r="K83" t="n">
-        <v>346.77</v>
+        <v>407.24</v>
       </c>
       <c r="L83" t="n">
-        <v>373.34</v>
+        <v>438.44</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-499.02</v>
+        <v>-577.03</v>
       </c>
       <c r="K84" t="n">
-        <v>325.65</v>
+        <v>376.56</v>
       </c>
       <c r="L84" t="n">
-        <v>595.88</v>
+        <v>689.03</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>321.27</v>
+        <v>372.14</v>
       </c>
       <c r="K85" t="n">
-        <v>-56.2</v>
+        <v>-65.09999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>326.15</v>
+        <v>377.79</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>446.94</v>
+        <v>534.41</v>
       </c>
       <c r="K86" t="n">
-        <v>-432.76</v>
+        <v>-517.47</v>
       </c>
       <c r="L86" t="n">
-        <v>622.12</v>
+        <v>743.89</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>358.21</v>
+        <v>428.76</v>
       </c>
       <c r="K87" t="n">
-        <v>-176.32</v>
+        <v>-211.04</v>
       </c>
       <c r="L87" t="n">
-        <v>399.26</v>
+        <v>477.88</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-291.65</v>
+        <v>-346.63</v>
       </c>
       <c r="K88" t="n">
-        <v>202.91</v>
+        <v>241.16</v>
       </c>
       <c r="L88" t="n">
-        <v>355.29</v>
+        <v>422.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.03</v>
+        <v>4.58</v>
       </c>
       <c r="F14" t="n">
-        <v>11.84</v>
+        <v>11.99</v>
       </c>
       <c r="G14" t="n">
-        <v>338</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>74.2</v>
+        <v>71.3</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>341.05</v>
+        <v>64.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-73.31</v>
+        <v>27.38</v>
       </c>
       <c r="L14" t="n">
-        <v>348.84</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:23:37</t>
+          <t>06:23:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.96</v>
+        <v>4.16</v>
       </c>
       <c r="F15" t="n">
-        <v>11.5</v>
+        <v>12.52</v>
       </c>
       <c r="G15" t="n">
-        <v>349.7</v>
+        <v>350.3</v>
       </c>
       <c r="H15" t="n">
-        <v>74.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-77.05</v>
+        <v>-120.47</v>
       </c>
       <c r="K15" t="n">
-        <v>-203.99</v>
+        <v>-84.86</v>
       </c>
       <c r="L15" t="n">
-        <v>218.06</v>
+        <v>147.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:24:55</t>
+          <t>06:24:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="F16" t="n">
-        <v>11.72</v>
+        <v>10.78</v>
       </c>
       <c r="G16" t="n">
-        <v>353.2</v>
+        <v>356.4</v>
       </c>
       <c r="H16" t="n">
-        <v>74.5</v>
+        <v>79.5</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>76.34</v>
+        <v>-25.44</v>
       </c>
       <c r="K16" t="n">
-        <v>149</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>167.42</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:28:57</t>
+          <t>06:28:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.41</v>
+        <v>4.8</v>
       </c>
       <c r="F17" t="n">
-        <v>12.08</v>
+        <v>11.73</v>
       </c>
       <c r="G17" t="n">
-        <v>358.9</v>
+        <v>339.4</v>
       </c>
       <c r="H17" t="n">
-        <v>73.2</v>
+        <v>69.5</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>280.78</v>
+        <v>121.05</v>
       </c>
       <c r="K17" t="n">
-        <v>2.88</v>
+        <v>11.33</v>
       </c>
       <c r="L17" t="n">
-        <v>280.8</v>
+        <v>121.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:30:00</t>
+          <t>06:30:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.14</v>
+        <v>5.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.85</v>
+        <v>11.7</v>
       </c>
       <c r="G18" t="n">
-        <v>352.3</v>
+        <v>354.4</v>
       </c>
       <c r="H18" t="n">
-        <v>78.5</v>
+        <v>71.5</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>181.75</v>
+        <v>120.19</v>
       </c>
       <c r="K18" t="n">
-        <v>-156.91</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>240.11</v>
+        <v>154.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:30:56</t>
+          <t>06:31:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.51</v>
+        <v>5.13</v>
       </c>
       <c r="F19" t="n">
-        <v>11.63</v>
+        <v>11.55</v>
       </c>
       <c r="G19" t="n">
-        <v>339.9</v>
+        <v>355.3</v>
       </c>
       <c r="H19" t="n">
-        <v>77.7</v>
+        <v>78.5</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-11.73</v>
+        <v>-8.57</v>
       </c>
       <c r="K19" t="n">
-        <v>-227.19</v>
+        <v>103.79</v>
       </c>
       <c r="L19" t="n">
-        <v>227.49</v>
+        <v>104.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:34:16</t>
+          <t>06:36:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.92</v>
+        <v>4.69</v>
       </c>
       <c r="F20" t="n">
-        <v>12.61</v>
+        <v>11.33</v>
       </c>
       <c r="G20" t="n">
-        <v>356.1</v>
+        <v>346.9</v>
       </c>
       <c r="H20" t="n">
-        <v>72.8</v>
+        <v>73.3</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-70.95999999999999</v>
+        <v>-141.01</v>
       </c>
       <c r="K20" t="n">
-        <v>-280.22</v>
+        <v>24.33</v>
       </c>
       <c r="L20" t="n">
-        <v>289.07</v>
+        <v>143.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:36:52</t>
+          <t>06:39:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="F21" t="n">
-        <v>12.27</v>
+        <v>11.47</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>357.6</v>
       </c>
       <c r="H21" t="n">
-        <v>73.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>284.01</v>
+        <v>-10.58</v>
       </c>
       <c r="K21" t="n">
-        <v>62.63</v>
+        <v>147</v>
       </c>
       <c r="L21" t="n">
-        <v>290.83</v>
+        <v>147.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:37:37</t>
+          <t>06:41:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="F22" t="n">
-        <v>11.75</v>
+        <v>11.77</v>
       </c>
       <c r="G22" t="n">
-        <v>343.3</v>
+        <v>350.8</v>
       </c>
       <c r="H22" t="n">
-        <v>75.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>230.28</v>
+        <v>-65.69</v>
       </c>
       <c r="K22" t="n">
-        <v>-60.09</v>
+        <v>142.18</v>
       </c>
       <c r="L22" t="n">
-        <v>237.99</v>
+        <v>156.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:42:31</t>
+          <t>06:46:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.03</v>
+        <v>5.3</v>
       </c>
       <c r="F23" t="n">
-        <v>12.12</v>
+        <v>12.51</v>
       </c>
       <c r="G23" t="n">
-        <v>359.1</v>
+        <v>348.7</v>
       </c>
       <c r="H23" t="n">
-        <v>68.7</v>
+        <v>73.7</v>
       </c>
       <c r="I23" t="n">
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-371.61</v>
+        <v>229.81</v>
       </c>
       <c r="K23" t="n">
-        <v>13.48</v>
+        <v>51.85</v>
       </c>
       <c r="L23" t="n">
-        <v>371.86</v>
+        <v>235.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:44:54</t>
+          <t>06:48:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.19</v>
+        <v>4.73</v>
       </c>
       <c r="F24" t="n">
-        <v>11.94</v>
+        <v>11.51</v>
       </c>
       <c r="G24" t="n">
-        <v>352.1</v>
+        <v>356.8</v>
       </c>
       <c r="H24" t="n">
-        <v>74.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>14.38</v>
+        <v>206.75</v>
       </c>
       <c r="K24" t="n">
-        <v>418.22</v>
+        <v>-60.31</v>
       </c>
       <c r="L24" t="n">
-        <v>418.47</v>
+        <v>215.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:46:10</t>
+          <t>06:49:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.9</v>
+        <v>5.17</v>
       </c>
       <c r="F25" t="n">
-        <v>12.11</v>
+        <v>11.75</v>
       </c>
       <c r="G25" t="n">
-        <v>356.2</v>
+        <v>348.7</v>
       </c>
       <c r="H25" t="n">
-        <v>79.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>106.46</v>
+        <v>-10.78</v>
       </c>
       <c r="K25" t="n">
-        <v>217.24</v>
+        <v>0.89</v>
       </c>
       <c r="L25" t="n">
-        <v>241.93</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:50:30</t>
+          <t>06:53:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="F26" t="n">
-        <v>12.04</v>
+        <v>11.23</v>
       </c>
       <c r="G26" t="n">
-        <v>338.4</v>
+        <v>352.6</v>
       </c>
       <c r="H26" t="n">
-        <v>76.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>458.09</v>
+        <v>-296.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-83.18000000000001</v>
+        <v>252.93</v>
       </c>
       <c r="L26" t="n">
-        <v>465.59</v>
+        <v>389.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:53:03</t>
+          <t>06:55:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="F27" t="n">
-        <v>10.86</v>
+        <v>11.83</v>
       </c>
       <c r="G27" t="n">
-        <v>350.4</v>
+        <v>1.7</v>
       </c>
       <c r="H27" t="n">
-        <v>72.5</v>
+        <v>78.5</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>43.97</v>
+        <v>134.89</v>
       </c>
       <c r="K27" t="n">
-        <v>296.42</v>
+        <v>234.09</v>
       </c>
       <c r="L27" t="n">
-        <v>299.66</v>
+        <v>270.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:53:52</t>
+          <t>06:56:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.01</v>
+        <v>5.08</v>
       </c>
       <c r="F28" t="n">
-        <v>11.82</v>
+        <v>12.16</v>
       </c>
       <c r="G28" t="n">
-        <v>356.6</v>
+        <v>344.2</v>
       </c>
       <c r="H28" t="n">
-        <v>74.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>38.19</v>
+        <v>-508.68</v>
       </c>
       <c r="K28" t="n">
-        <v>320.71</v>
+        <v>-43.89</v>
       </c>
       <c r="L28" t="n">
-        <v>322.97</v>
+        <v>510.57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:02:59</t>
+          <t>07:09:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.13</v>
+        <v>4.62</v>
       </c>
       <c r="F29" t="n">
-        <v>11.92</v>
+        <v>11.88</v>
       </c>
       <c r="G29" t="n">
-        <v>1.2</v>
+        <v>356.4</v>
       </c>
       <c r="H29" t="n">
-        <v>70</v>
+        <v>84.2</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>248.81</v>
+        <v>-29.06</v>
       </c>
       <c r="K29" t="n">
-        <v>-114.23</v>
+        <v>-107.69</v>
       </c>
       <c r="L29" t="n">
-        <v>273.78</v>
+        <v>111.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:05:02</t>
+          <t>07:11:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.49</v>
+        <v>4.94</v>
       </c>
       <c r="F30" t="n">
-        <v>11.98</v>
+        <v>11.49</v>
       </c>
       <c r="G30" t="n">
-        <v>338.5</v>
+        <v>347.3</v>
       </c>
       <c r="H30" t="n">
-        <v>76.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-159.27</v>
+        <v>101.12</v>
       </c>
       <c r="K30" t="n">
-        <v>-148.34</v>
+        <v>10.68</v>
       </c>
       <c r="L30" t="n">
-        <v>217.65</v>
+        <v>101.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:06:40</t>
+          <t>07:13:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.98</v>
+        <v>4.75</v>
       </c>
       <c r="F31" t="n">
-        <v>11.89</v>
+        <v>11.27</v>
       </c>
       <c r="G31" t="n">
-        <v>344.9</v>
+        <v>339.9</v>
       </c>
       <c r="H31" t="n">
-        <v>75.2</v>
+        <v>72.7</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-37.43</v>
+        <v>-87.56999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>346.37</v>
+        <v>-60.32</v>
       </c>
       <c r="L31" t="n">
-        <v>348.39</v>
+        <v>106.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:11:15</t>
+          <t>07:17:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="F32" t="n">
-        <v>12.07</v>
+        <v>11.8</v>
       </c>
       <c r="G32" t="n">
-        <v>358.7</v>
+        <v>355</v>
       </c>
       <c r="H32" t="n">
-        <v>76.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-178.37</v>
+        <v>27.53</v>
       </c>
       <c r="K32" t="n">
-        <v>-161.67</v>
+        <v>132.17</v>
       </c>
       <c r="L32" t="n">
-        <v>240.74</v>
+        <v>135.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:13:13</t>
+          <t>07:18:10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.77</v>
+        <v>4.93</v>
       </c>
       <c r="F33" t="n">
-        <v>12.31</v>
+        <v>11.49</v>
       </c>
       <c r="G33" t="n">
-        <v>357.1</v>
+        <v>354.1</v>
       </c>
       <c r="H33" t="n">
-        <v>78.8</v>
+        <v>72.8</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-200.75</v>
+        <v>62.72</v>
       </c>
       <c r="K33" t="n">
-        <v>29.56</v>
+        <v>45.14</v>
       </c>
       <c r="L33" t="n">
-        <v>202.91</v>
+        <v>77.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:15:00</t>
+          <t>07:19:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.01</v>
+        <v>4.47</v>
       </c>
       <c r="F34" t="n">
-        <v>11.71</v>
+        <v>11.53</v>
       </c>
       <c r="G34" t="n">
-        <v>2.4</v>
+        <v>349.1</v>
       </c>
       <c r="H34" t="n">
-        <v>75.3</v>
+        <v>71.8</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>163.9</v>
+        <v>12.15</v>
       </c>
       <c r="K34" t="n">
-        <v>49.41</v>
+        <v>-107.68</v>
       </c>
       <c r="L34" t="n">
-        <v>171.19</v>
+        <v>108.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:19:43</t>
+          <t>07:24:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.17</v>
+        <v>4.41</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>11.74</v>
       </c>
       <c r="G35" t="n">
-        <v>336.6</v>
+        <v>358.7</v>
       </c>
       <c r="H35" t="n">
-        <v>75.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>369.63</v>
+        <v>-122.38</v>
       </c>
       <c r="K35" t="n">
-        <v>-70.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="L35" t="n">
-        <v>376.28</v>
+        <v>146.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:21:41</t>
+          <t>07:26:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.44</v>
+        <v>5.69</v>
       </c>
       <c r="F36" t="n">
-        <v>11.92</v>
+        <v>11.82</v>
       </c>
       <c r="G36" t="n">
-        <v>356.6</v>
+        <v>347.9</v>
       </c>
       <c r="H36" t="n">
-        <v>72.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-191.28</v>
+        <v>-1.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-121.1</v>
+        <v>128.7</v>
       </c>
       <c r="L36" t="n">
-        <v>226.39</v>
+        <v>128.71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:23:11</t>
+          <t>07:28:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.79</v>
+        <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>11.43</v>
+        <v>11.81</v>
       </c>
       <c r="G37" t="n">
-        <v>358.5</v>
+        <v>0.9</v>
       </c>
       <c r="H37" t="n">
-        <v>78.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>349.16</v>
+        <v>-211.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-248.9</v>
+        <v>34.02</v>
       </c>
       <c r="L37" t="n">
-        <v>428.79</v>
+        <v>214.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:28:40</t>
+          <t>07:33:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.74</v>
+        <v>5.78</v>
       </c>
       <c r="F38" t="n">
-        <v>11.81</v>
+        <v>12.49</v>
       </c>
       <c r="G38" t="n">
-        <v>357.1</v>
+        <v>352.9</v>
       </c>
       <c r="H38" t="n">
-        <v>69.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-244.35</v>
+        <v>219.77</v>
       </c>
       <c r="K38" t="n">
-        <v>447.98</v>
+        <v>225.14</v>
       </c>
       <c r="L38" t="n">
-        <v>510.29</v>
+        <v>314.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:29:40</t>
+          <t>07:35:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="F39" t="n">
-        <v>12.23</v>
+        <v>11.82</v>
       </c>
       <c r="G39" t="n">
-        <v>355.7</v>
+        <v>3.8</v>
       </c>
       <c r="H39" t="n">
-        <v>66.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-462</v>
+        <v>-172.95</v>
       </c>
       <c r="K39" t="n">
-        <v>-719.47</v>
+        <v>130.04</v>
       </c>
       <c r="L39" t="n">
-        <v>855.04</v>
+        <v>216.38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:30:34</t>
+          <t>07:36:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.18</v>
+        <v>4.82</v>
       </c>
       <c r="F40" t="n">
-        <v>11.62</v>
+        <v>12.18</v>
       </c>
       <c r="G40" t="n">
-        <v>350.6</v>
+        <v>0.4</v>
       </c>
       <c r="H40" t="n">
-        <v>68.2</v>
+        <v>71.2</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>-53.83</v>
+        <v>179.79</v>
       </c>
       <c r="K40" t="n">
-        <v>356.48</v>
+        <v>168.1</v>
       </c>
       <c r="L40" t="n">
-        <v>360.52</v>
+        <v>246.13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:35:17</t>
+          <t>07:41:39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.81</v>
+        <v>5.18</v>
       </c>
       <c r="F41" t="n">
-        <v>11.65</v>
+        <v>11.82</v>
       </c>
       <c r="G41" t="n">
-        <v>351.6</v>
+        <v>350.2</v>
       </c>
       <c r="H41" t="n">
-        <v>73.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-500.86</v>
+        <v>-25.55</v>
       </c>
       <c r="K41" t="n">
-        <v>-29.48</v>
+        <v>-217.71</v>
       </c>
       <c r="L41" t="n">
-        <v>501.73</v>
+        <v>219.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:36:26</t>
+          <t>07:43:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.32</v>
+        <v>4.44</v>
       </c>
       <c r="F42" t="n">
-        <v>11.42</v>
+        <v>12.09</v>
       </c>
       <c r="G42" t="n">
-        <v>337.2</v>
+        <v>330.3</v>
       </c>
       <c r="H42" t="n">
-        <v>79.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>520.34</v>
+        <v>-83.22</v>
       </c>
       <c r="K42" t="n">
-        <v>-318.27</v>
+        <v>246.28</v>
       </c>
       <c r="L42" t="n">
-        <v>609.96</v>
+        <v>259.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:38:23</t>
+          <t>07:44:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="F43" t="n">
-        <v>11.32</v>
+        <v>11.97</v>
       </c>
       <c r="G43" t="n">
-        <v>351.2</v>
+        <v>347.8</v>
       </c>
       <c r="H43" t="n">
-        <v>71.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>974.6900000000001</v>
+        <v>-86.43000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>100.34</v>
+        <v>182.76</v>
       </c>
       <c r="L43" t="n">
-        <v>979.84</v>
+        <v>202.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:46:45</t>
+          <t>07:55:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.83</v>
+        <v>5.37</v>
       </c>
       <c r="F44" t="n">
-        <v>11.28</v>
+        <v>11.14</v>
       </c>
       <c r="G44" t="n">
-        <v>352.6</v>
+        <v>340.7</v>
       </c>
       <c r="H44" t="n">
-        <v>67.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>-297.11</v>
+        <v>70.5</v>
       </c>
       <c r="K44" t="n">
-        <v>-240.7</v>
+        <v>-62.35</v>
       </c>
       <c r="L44" t="n">
-        <v>382.38</v>
+        <v>94.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:48:42</t>
+          <t>07:57:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.71</v>
+        <v>5.33</v>
       </c>
       <c r="F45" t="n">
-        <v>12.25</v>
+        <v>11.6</v>
       </c>
       <c r="G45" t="n">
-        <v>350.9</v>
+        <v>344.4</v>
       </c>
       <c r="H45" t="n">
-        <v>69.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-22.6</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>116.69</v>
+        <v>-8.18</v>
       </c>
       <c r="L45" t="n">
-        <v>118.86</v>
+        <v>84.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:50:48</t>
+          <t>07:59:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="F46" t="n">
-        <v>12.11</v>
+        <v>11.42</v>
       </c>
       <c r="G46" t="n">
-        <v>2.1</v>
+        <v>345.6</v>
       </c>
       <c r="H46" t="n">
-        <v>69.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>131.26</v>
+        <v>83.09</v>
       </c>
       <c r="K46" t="n">
-        <v>6.84</v>
+        <v>79.75</v>
       </c>
       <c r="L46" t="n">
-        <v>131.44</v>
+        <v>115.17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:56:33</t>
+          <t>08:04:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.78</v>
+        <v>5.62</v>
       </c>
       <c r="F47" t="n">
-        <v>12.01</v>
+        <v>11.63</v>
       </c>
       <c r="G47" t="n">
-        <v>340.8</v>
+        <v>337.4</v>
       </c>
       <c r="H47" t="n">
-        <v>74.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-75.06999999999999</v>
+        <v>-87.31999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-181.39</v>
+        <v>27.41</v>
       </c>
       <c r="L47" t="n">
-        <v>196.31</v>
+        <v>91.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:58:27</t>
+          <t>08:06:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="F48" t="n">
-        <v>11.49</v>
+        <v>11.51</v>
       </c>
       <c r="G48" t="n">
-        <v>350.3</v>
+        <v>348.3</v>
       </c>
       <c r="H48" t="n">
-        <v>75.2</v>
+        <v>76.5</v>
       </c>
       <c r="I48" t="n">
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-131.99</v>
+        <v>-69.01000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-246.78</v>
+        <v>-128.15</v>
       </c>
       <c r="L48" t="n">
-        <v>279.87</v>
+        <v>145.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:59:19</t>
+          <t>08:07:56</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.51</v>
+        <v>5.1</v>
       </c>
       <c r="F49" t="n">
-        <v>11.64</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>335.7</v>
+        <v>337.6</v>
       </c>
       <c r="H49" t="n">
-        <v>79.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-130.86</v>
+        <v>-23.21</v>
       </c>
       <c r="K49" t="n">
-        <v>397.93</v>
+        <v>-83.83</v>
       </c>
       <c r="L49" t="n">
-        <v>418.89</v>
+        <v>86.98999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:02:57</t>
+          <t>08:11:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.07</v>
+        <v>4.81</v>
       </c>
       <c r="F50" t="n">
-        <v>12.23</v>
+        <v>11.36</v>
       </c>
       <c r="G50" t="n">
-        <v>344.5</v>
+        <v>354.1</v>
       </c>
       <c r="H50" t="n">
-        <v>77.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>204.5</v>
+        <v>142.22</v>
       </c>
       <c r="K50" t="n">
-        <v>-171.59</v>
+        <v>-13.68</v>
       </c>
       <c r="L50" t="n">
-        <v>266.95</v>
+        <v>142.88</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:04:11</t>
+          <t>08:12:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.28</v>
+        <v>5.29</v>
       </c>
       <c r="F51" t="n">
-        <v>11.94</v>
+        <v>11.62</v>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>358.9</v>
       </c>
       <c r="H51" t="n">
-        <v>71.7</v>
+        <v>63.9</v>
       </c>
       <c r="I51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-157.5</v>
+        <v>-154.71</v>
       </c>
       <c r="K51" t="n">
-        <v>84.34</v>
+        <v>-19.38</v>
       </c>
       <c r="L51" t="n">
-        <v>178.66</v>
+        <v>155.92</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:05:21</t>
+          <t>08:13:39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="F52" t="n">
-        <v>11.63</v>
+        <v>11.59</v>
       </c>
       <c r="G52" t="n">
-        <v>5.2</v>
+        <v>356.7</v>
       </c>
       <c r="H52" t="n">
-        <v>73.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-106.98</v>
+        <v>-38.61</v>
       </c>
       <c r="K52" t="n">
-        <v>502.45</v>
+        <v>130.38</v>
       </c>
       <c r="L52" t="n">
-        <v>513.71</v>
+        <v>135.98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:10:22</t>
+          <t>08:19:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.6</v>
+        <v>5.17</v>
       </c>
       <c r="F53" t="n">
-        <v>11.43</v>
+        <v>11.95</v>
       </c>
       <c r="G53" t="n">
-        <v>10.8</v>
+        <v>358.1</v>
       </c>
       <c r="H53" t="n">
-        <v>69.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="I53" t="n">
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>483.24</v>
+        <v>331.45</v>
       </c>
       <c r="K53" t="n">
-        <v>-58.64</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>486.79</v>
+        <v>344.52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:11:34</t>
+          <t>08:20:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.2</v>
+        <v>5.68</v>
       </c>
       <c r="F54" t="n">
-        <v>11.63</v>
+        <v>11.29</v>
       </c>
       <c r="G54" t="n">
-        <v>358.4</v>
+        <v>357.9</v>
       </c>
       <c r="H54" t="n">
-        <v>73.7</v>
+        <v>61.7</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-35.56</v>
+        <v>-259.09</v>
       </c>
       <c r="K54" t="n">
-        <v>236.55</v>
+        <v>-96.95</v>
       </c>
       <c r="L54" t="n">
-        <v>239.21</v>
+        <v>276.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:13:22</t>
+          <t>08:22:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.23</v>
+        <v>5.07</v>
       </c>
       <c r="F55" t="n">
-        <v>11.78</v>
+        <v>11.71</v>
       </c>
       <c r="G55" t="n">
-        <v>3.8</v>
+        <v>350.5</v>
       </c>
       <c r="H55" t="n">
-        <v>72.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-405.76</v>
+        <v>-158.18</v>
       </c>
       <c r="K55" t="n">
-        <v>-39.24</v>
+        <v>-139.63</v>
       </c>
       <c r="L55" t="n">
-        <v>407.65</v>
+        <v>210.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:17:49</t>
+          <t>08:27:10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.8</v>
+        <v>5.86</v>
       </c>
       <c r="F56" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="G56" t="n">
-        <v>352.7</v>
+        <v>351.6</v>
       </c>
       <c r="H56" t="n">
-        <v>67.7</v>
+        <v>78.2</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-736.4400000000001</v>
+        <v>-258.3</v>
       </c>
       <c r="K56" t="n">
-        <v>-554.62</v>
+        <v>-172.47</v>
       </c>
       <c r="L56" t="n">
-        <v>921.9299999999999</v>
+        <v>310.59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:19:23</t>
+          <t>08:28:51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.23</v>
+        <v>5.16</v>
       </c>
       <c r="F57" t="n">
-        <v>11.31</v>
+        <v>12.68</v>
       </c>
       <c r="G57" t="n">
-        <v>341.3</v>
+        <v>343.8</v>
       </c>
       <c r="H57" t="n">
-        <v>72.2</v>
+        <v>74.3</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-724.8200000000001</v>
+        <v>-222.24</v>
       </c>
       <c r="K57" t="n">
-        <v>-98.16</v>
+        <v>-374.38</v>
       </c>
       <c r="L57" t="n">
-        <v>731.4299999999999</v>
+        <v>435.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:21:52</t>
+          <t>08:30:56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.95</v>
+        <v>5.28</v>
       </c>
       <c r="F58" t="n">
-        <v>11.96</v>
+        <v>11.83</v>
       </c>
       <c r="G58" t="n">
-        <v>341.8</v>
+        <v>354.7</v>
       </c>
       <c r="H58" t="n">
-        <v>83.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="I58" t="n">
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>322.3</v>
+        <v>236.1</v>
       </c>
       <c r="K58" t="n">
-        <v>364.63</v>
+        <v>-6.32</v>
       </c>
       <c r="L58" t="n">
-        <v>486.65</v>
+        <v>236.18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:34:06</t>
+          <t>08:39:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.18</v>
+        <v>4.86</v>
       </c>
       <c r="F59" t="n">
-        <v>11.84</v>
+        <v>11.88</v>
       </c>
       <c r="G59" t="n">
-        <v>338.4</v>
+        <v>352</v>
       </c>
       <c r="H59" t="n">
-        <v>76.7</v>
+        <v>69.3</v>
       </c>
       <c r="I59" t="n">
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-170.49</v>
+        <v>-56.27</v>
       </c>
       <c r="K59" t="n">
-        <v>-115.04</v>
+        <v>-12.2</v>
       </c>
       <c r="L59" t="n">
-        <v>205.67</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:35:18</t>
+          <t>08:42:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.24</v>
+        <v>5.65</v>
       </c>
       <c r="F60" t="n">
-        <v>11.92</v>
+        <v>11.06</v>
       </c>
       <c r="G60" t="n">
-        <v>357.2</v>
+        <v>332.6</v>
       </c>
       <c r="H60" t="n">
-        <v>77.8</v>
+        <v>66.2</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-117.01</v>
+        <v>-69.73999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-74.91</v>
+        <v>-37.43</v>
       </c>
       <c r="L60" t="n">
-        <v>138.93</v>
+        <v>79.15000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:37:53</t>
+          <t>08:44:06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.98</v>
+        <v>5.28</v>
       </c>
       <c r="F61" t="n">
-        <v>11.48</v>
+        <v>11.93</v>
       </c>
       <c r="G61" t="n">
-        <v>348.5</v>
+        <v>336.3</v>
       </c>
       <c r="H61" t="n">
-        <v>80.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-275.8</v>
+        <v>-87.02</v>
       </c>
       <c r="K61" t="n">
-        <v>148.1</v>
+        <v>38.77</v>
       </c>
       <c r="L61" t="n">
-        <v>313.04</v>
+        <v>95.27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:41:56</t>
+          <t>08:47:04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.75</v>
+        <v>5.46</v>
       </c>
       <c r="F62" t="n">
-        <v>12.63</v>
+        <v>11.89</v>
       </c>
       <c r="G62" t="n">
-        <v>352.3</v>
+        <v>357.4</v>
       </c>
       <c r="H62" t="n">
-        <v>72</v>
+        <v>64.2</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-200.9</v>
+        <v>-228.62</v>
       </c>
       <c r="K62" t="n">
-        <v>27.12</v>
+        <v>-31.28</v>
       </c>
       <c r="L62" t="n">
-        <v>202.72</v>
+        <v>230.76</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:43:59</t>
+          <t>08:49:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.88</v>
+        <v>4.78</v>
       </c>
       <c r="F63" t="n">
-        <v>11.87</v>
+        <v>11.89</v>
       </c>
       <c r="G63" t="n">
-        <v>341.7</v>
+        <v>357.3</v>
       </c>
       <c r="H63" t="n">
-        <v>74.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="I63" t="n">
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>282.9</v>
+        <v>-80.97</v>
       </c>
       <c r="K63" t="n">
-        <v>188.65</v>
+        <v>-60.4</v>
       </c>
       <c r="L63" t="n">
-        <v>340.03</v>
+        <v>101.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:45:35</t>
+          <t>08:50:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.81</v>
+        <v>5.68</v>
       </c>
       <c r="F64" t="n">
-        <v>11.37</v>
+        <v>11.45</v>
       </c>
       <c r="G64" t="n">
-        <v>341.8</v>
+        <v>347.1</v>
       </c>
       <c r="H64" t="n">
-        <v>76</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>66.09999999999999</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>221.73</v>
+        <v>-59.59</v>
       </c>
       <c r="L64" t="n">
-        <v>231.37</v>
+        <v>107.23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:50:24</t>
+          <t>08:55:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.42</v>
+        <v>4.98</v>
       </c>
       <c r="F65" t="n">
-        <v>12.44</v>
+        <v>11.23</v>
       </c>
       <c r="G65" t="n">
-        <v>340.8</v>
+        <v>342.1</v>
       </c>
       <c r="H65" t="n">
-        <v>76.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>158.01</v>
+        <v>58.25</v>
       </c>
       <c r="K65" t="n">
-        <v>-381.12</v>
+        <v>-74.09</v>
       </c>
       <c r="L65" t="n">
-        <v>412.58</v>
+        <v>94.25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:52:32</t>
+          <t>08:58:06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.6</v>
+        <v>5.74</v>
       </c>
       <c r="F66" t="n">
-        <v>11.91</v>
+        <v>11.24</v>
       </c>
       <c r="G66" t="n">
-        <v>338.1</v>
+        <v>353.8</v>
       </c>
       <c r="H66" t="n">
-        <v>75.7</v>
+        <v>74.8</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>-256.72</v>
+        <v>-156.92</v>
       </c>
       <c r="K66" t="n">
-        <v>222.94</v>
+        <v>78.03</v>
       </c>
       <c r="L66" t="n">
-        <v>340.01</v>
+        <v>175.25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:54:11</t>
+          <t>08:58:49</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.33</v>
+        <v>4.98</v>
       </c>
       <c r="F67" t="n">
-        <v>11.08</v>
+        <v>11.98</v>
       </c>
       <c r="G67" t="n">
-        <v>351.9</v>
+        <v>340.1</v>
       </c>
       <c r="H67" t="n">
-        <v>81.5</v>
+        <v>76.3</v>
       </c>
       <c r="I67" t="n">
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>14.7</v>
+        <v>-144.43</v>
       </c>
       <c r="K67" t="n">
-        <v>337.03</v>
+        <v>-3.92</v>
       </c>
       <c r="L67" t="n">
-        <v>337.35</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:58:19</t>
+          <t>09:04:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.42</v>
+        <v>5.84</v>
       </c>
       <c r="F68" t="n">
-        <v>12.05</v>
+        <v>11.65</v>
       </c>
       <c r="G68" t="n">
-        <v>357.4</v>
+        <v>342.1</v>
       </c>
       <c r="H68" t="n">
-        <v>73.7</v>
+        <v>66.8</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>157.53</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-482.11</v>
+        <v>-143.54</v>
       </c>
       <c r="L68" t="n">
-        <v>507.19</v>
+        <v>166.49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:00:07</t>
+          <t>09:04:54</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.54</v>
+        <v>5.34</v>
       </c>
       <c r="F69" t="n">
-        <v>12.37</v>
+        <v>11.71</v>
       </c>
       <c r="G69" t="n">
-        <v>352</v>
+        <v>347.8</v>
       </c>
       <c r="H69" t="n">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>67.17</v>
+        <v>148.15</v>
       </c>
       <c r="K69" t="n">
-        <v>641.48</v>
+        <v>-75.31999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>644.99</v>
+        <v>166.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:01:49</t>
+          <t>09:06:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.1</v>
+        <v>5.73</v>
       </c>
       <c r="F70" t="n">
-        <v>11.98</v>
+        <v>11.24</v>
       </c>
       <c r="G70" t="n">
-        <v>346</v>
+        <v>347.9</v>
       </c>
       <c r="H70" t="n">
-        <v>71.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-594.25</v>
+        <v>-145.65</v>
       </c>
       <c r="K70" t="n">
-        <v>441.99</v>
+        <v>-116.89</v>
       </c>
       <c r="L70" t="n">
-        <v>740.6</v>
+        <v>186.75</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:06:00</t>
+          <t>09:11:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.7</v>
+        <v>5.33</v>
       </c>
       <c r="F71" t="n">
-        <v>12.2</v>
+        <v>12.48</v>
       </c>
       <c r="G71" t="n">
-        <v>351.8</v>
+        <v>342</v>
       </c>
       <c r="H71" t="n">
-        <v>74.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I71" t="n">
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-354.73</v>
+        <v>-231.39</v>
       </c>
       <c r="K71" t="n">
-        <v>171.93</v>
+        <v>341.34</v>
       </c>
       <c r="L71" t="n">
-        <v>394.2</v>
+        <v>412.38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:07:00</t>
+          <t>09:12:23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.75</v>
+        <v>5.33</v>
       </c>
       <c r="F72" t="n">
-        <v>11.99</v>
+        <v>12.13</v>
       </c>
       <c r="G72" t="n">
-        <v>346.3</v>
+        <v>354.2</v>
       </c>
       <c r="H72" t="n">
-        <v>71.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I72" t="n">
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-282.79</v>
+        <v>-107.45</v>
       </c>
       <c r="K72" t="n">
-        <v>214.27</v>
+        <v>381.49</v>
       </c>
       <c r="L72" t="n">
-        <v>354.79</v>
+        <v>396.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:08:56</t>
+          <t>09:14:39</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.86</v>
+        <v>5.2</v>
       </c>
       <c r="F73" t="n">
-        <v>11.61</v>
+        <v>12.46</v>
       </c>
       <c r="G73" t="n">
-        <v>349.9</v>
+        <v>347.1</v>
       </c>
       <c r="H73" t="n">
-        <v>74.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>189.06</v>
+        <v>-5.17</v>
       </c>
       <c r="K73" t="n">
-        <v>329.81</v>
+        <v>-230.2</v>
       </c>
       <c r="L73" t="n">
-        <v>380.15</v>
+        <v>230.26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:18:25</t>
+          <t>09:25:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.59</v>
+        <v>5.85</v>
       </c>
       <c r="F74" t="n">
-        <v>11.67</v>
+        <v>12.3</v>
       </c>
       <c r="G74" t="n">
-        <v>346.3</v>
+        <v>343.1</v>
       </c>
       <c r="H74" t="n">
-        <v>69.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-91.15000000000001</v>
+        <v>-75.38</v>
       </c>
       <c r="K74" t="n">
-        <v>-178.81</v>
+        <v>53.57</v>
       </c>
       <c r="L74" t="n">
-        <v>200.7</v>
+        <v>92.48</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:19:21</t>
+          <t>09:28:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.41</v>
+        <v>5.71</v>
       </c>
       <c r="F75" t="n">
-        <v>11.44</v>
+        <v>11.66</v>
       </c>
       <c r="G75" t="n">
-        <v>344.2</v>
+        <v>357.8</v>
       </c>
       <c r="H75" t="n">
-        <v>72.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>391.72</v>
+        <v>-110.35</v>
       </c>
       <c r="K75" t="n">
-        <v>64.58</v>
+        <v>23.81</v>
       </c>
       <c r="L75" t="n">
-        <v>397</v>
+        <v>112.89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:20:31</t>
+          <t>09:29:38</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.68</v>
+        <v>5.8</v>
       </c>
       <c r="F76" t="n">
-        <v>12.03</v>
+        <v>10.96</v>
       </c>
       <c r="G76" t="n">
-        <v>356</v>
+        <v>4</v>
       </c>
       <c r="H76" t="n">
-        <v>74.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="I76" t="n">
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>6.34</v>
+        <v>30.33</v>
       </c>
       <c r="K76" t="n">
-        <v>-149.28</v>
+        <v>70.59</v>
       </c>
       <c r="L76" t="n">
-        <v>149.42</v>
+        <v>76.83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:25:43</t>
+          <t>09:32:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.64</v>
+        <v>5.21</v>
       </c>
       <c r="F77" t="n">
-        <v>11.33</v>
+        <v>12.49</v>
       </c>
       <c r="G77" t="n">
-        <v>344.3</v>
+        <v>335.3</v>
       </c>
       <c r="H77" t="n">
-        <v>78.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>-258.9</v>
+        <v>1.59</v>
       </c>
       <c r="K77" t="n">
-        <v>-91.97</v>
+        <v>32.16</v>
       </c>
       <c r="L77" t="n">
-        <v>274.75</v>
+        <v>32.19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:27:48</t>
+          <t>09:34:54</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.12</v>
+        <v>6.15</v>
       </c>
       <c r="F78" t="n">
-        <v>11.72</v>
+        <v>11.99</v>
       </c>
       <c r="G78" t="n">
-        <v>350.9</v>
+        <v>356.5</v>
       </c>
       <c r="H78" t="n">
-        <v>72.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>252.77</v>
+        <v>119.17</v>
       </c>
       <c r="K78" t="n">
-        <v>97.59</v>
+        <v>40.73</v>
       </c>
       <c r="L78" t="n">
-        <v>270.96</v>
+        <v>125.94</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:29:36</t>
+          <t>09:36:28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.28</v>
+        <v>5.18</v>
       </c>
       <c r="F79" t="n">
-        <v>12.18</v>
+        <v>12.05</v>
       </c>
       <c r="G79" t="n">
-        <v>358.1</v>
+        <v>352.8</v>
       </c>
       <c r="H79" t="n">
-        <v>67.7</v>
+        <v>73.5</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>274.27</v>
+        <v>22.84</v>
       </c>
       <c r="K79" t="n">
-        <v>137.07</v>
+        <v>-47.7</v>
       </c>
       <c r="L79" t="n">
-        <v>306.62</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:35:33</t>
+          <t>09:41:16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,13 +3397,13 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.59</v>
+        <v>5.62</v>
       </c>
       <c r="F80" t="n">
-        <v>11.7</v>
+        <v>11.82</v>
       </c>
       <c r="G80" t="n">
-        <v>350.9</v>
+        <v>347.1</v>
       </c>
       <c r="H80" t="n">
         <v>76.40000000000001</v>
@@ -3412,19 +3412,19 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-428.91</v>
+        <v>136.8</v>
       </c>
       <c r="K80" t="n">
-        <v>-174.98</v>
+        <v>54.59</v>
       </c>
       <c r="L80" t="n">
-        <v>463.23</v>
+        <v>147.29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:36:31</t>
+          <t>09:42:35</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.2</v>
+        <v>5.97</v>
       </c>
       <c r="F81" t="n">
-        <v>11.92</v>
+        <v>12.45</v>
       </c>
       <c r="G81" t="n">
-        <v>351.7</v>
+        <v>354.9</v>
       </c>
       <c r="H81" t="n">
-        <v>77.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I81" t="n">
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>237.4</v>
+        <v>-70.93000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>448.94</v>
+        <v>189.41</v>
       </c>
       <c r="L81" t="n">
-        <v>507.84</v>
+        <v>202.25</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:38:28</t>
+          <t>09:44:38</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.33</v>
+        <v>4.85</v>
       </c>
       <c r="F82" t="n">
-        <v>12.4</v>
+        <v>10.96</v>
       </c>
       <c r="G82" t="n">
-        <v>345.1</v>
+        <v>354.2</v>
       </c>
       <c r="H82" t="n">
-        <v>78.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-286.91</v>
+        <v>-22.23</v>
       </c>
       <c r="K82" t="n">
-        <v>387.22</v>
+        <v>104.38</v>
       </c>
       <c r="L82" t="n">
-        <v>481.93</v>
+        <v>106.73</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:43:55</t>
+          <t>09:49:49</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.09</v>
+        <v>5.76</v>
       </c>
       <c r="F83" t="n">
-        <v>11.55</v>
+        <v>12.02</v>
       </c>
       <c r="G83" t="n">
-        <v>350.5</v>
+        <v>348.7</v>
       </c>
       <c r="H83" t="n">
-        <v>78.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-162.45</v>
+        <v>129.97</v>
       </c>
       <c r="K83" t="n">
-        <v>407.24</v>
+        <v>-139.4</v>
       </c>
       <c r="L83" t="n">
-        <v>438.44</v>
+        <v>190.59</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:46:11</t>
+          <t>09:52:27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.4</v>
+        <v>5.76</v>
       </c>
       <c r="F84" t="n">
-        <v>11.75</v>
+        <v>12.42</v>
       </c>
       <c r="G84" t="n">
-        <v>344.9</v>
+        <v>354.8</v>
       </c>
       <c r="H84" t="n">
-        <v>68</v>
+        <v>72.7</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-577.03</v>
+        <v>155.3</v>
       </c>
       <c r="K84" t="n">
-        <v>376.56</v>
+        <v>215.67</v>
       </c>
       <c r="L84" t="n">
-        <v>689.03</v>
+        <v>265.76</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:47:24</t>
+          <t>09:53:57</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.18</v>
+        <v>5.5</v>
       </c>
       <c r="F85" t="n">
-        <v>12</v>
+        <v>12.38</v>
       </c>
       <c r="G85" t="n">
-        <v>357.9</v>
+        <v>327.8</v>
       </c>
       <c r="H85" t="n">
-        <v>77.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>372.14</v>
+        <v>-4.57</v>
       </c>
       <c r="K85" t="n">
-        <v>-65.09999999999999</v>
+        <v>-160.9</v>
       </c>
       <c r="L85" t="n">
-        <v>377.79</v>
+        <v>160.97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:53:05</t>
+          <t>09:57:13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.17</v>
+        <v>6.15</v>
       </c>
       <c r="F86" t="n">
-        <v>11.48</v>
+        <v>12.09</v>
       </c>
       <c r="G86" t="n">
-        <v>340.9</v>
+        <v>358.7</v>
       </c>
       <c r="H86" t="n">
-        <v>73.3</v>
+        <v>71.7</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>534.41</v>
+        <v>-282.56</v>
       </c>
       <c r="K86" t="n">
-        <v>-517.47</v>
+        <v>-248.39</v>
       </c>
       <c r="L86" t="n">
-        <v>743.89</v>
+        <v>376.21</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:54:10</t>
+          <t>09:59:41</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.59</v>
+        <v>6.08</v>
       </c>
       <c r="F87" t="n">
-        <v>11.69</v>
+        <v>11.67</v>
       </c>
       <c r="G87" t="n">
-        <v>342.9</v>
+        <v>334.1</v>
       </c>
       <c r="H87" t="n">
-        <v>77.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>428.76</v>
+        <v>241.28</v>
       </c>
       <c r="K87" t="n">
-        <v>-211.04</v>
+        <v>-344.19</v>
       </c>
       <c r="L87" t="n">
-        <v>477.88</v>
+        <v>420.33</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:56:27</t>
+          <t>10:01:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.06</v>
+        <v>6</v>
       </c>
       <c r="F88" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="G88" t="n">
-        <v>348.2</v>
+        <v>349.8</v>
       </c>
       <c r="H88" t="n">
-        <v>75.8</v>
+        <v>67</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-346.63</v>
+        <v>-527.74</v>
       </c>
       <c r="K88" t="n">
-        <v>241.16</v>
+        <v>139.45</v>
       </c>
       <c r="L88" t="n">
-        <v>422.27</v>
+        <v>545.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>64.87</v>
+        <v>63.43</v>
       </c>
       <c r="K14" t="n">
-        <v>27.38</v>
+        <v>26.77</v>
       </c>
       <c r="L14" t="n">
-        <v>70.41</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-120.47</v>
+        <v>-110.52</v>
       </c>
       <c r="K15" t="n">
-        <v>-84.86</v>
+        <v>-77.86</v>
       </c>
       <c r="L15" t="n">
-        <v>147.36</v>
+        <v>135.19</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-25.44</v>
+        <v>-24.47</v>
       </c>
       <c r="K16" t="n">
-        <v>77.68000000000001</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>81.73999999999999</v>
+        <v>78.64</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>121.05</v>
+        <v>112.59</v>
       </c>
       <c r="K17" t="n">
-        <v>11.33</v>
+        <v>10.54</v>
       </c>
       <c r="L17" t="n">
-        <v>121.58</v>
+        <v>113.08</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>120.19</v>
+        <v>100.02</v>
       </c>
       <c r="K18" t="n">
-        <v>97.81999999999999</v>
+        <v>81.41</v>
       </c>
       <c r="L18" t="n">
-        <v>154.97</v>
+        <v>128.96</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.57</v>
+        <v>-7.69</v>
       </c>
       <c r="K19" t="n">
-        <v>103.79</v>
+        <v>93.08</v>
       </c>
       <c r="L19" t="n">
-        <v>104.14</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-141.01</v>
+        <v>-140.6</v>
       </c>
       <c r="K20" t="n">
-        <v>24.33</v>
+        <v>24.26</v>
       </c>
       <c r="L20" t="n">
-        <v>143.09</v>
+        <v>142.68</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.58</v>
+        <v>-10.37</v>
       </c>
       <c r="K21" t="n">
-        <v>147</v>
+        <v>144.05</v>
       </c>
       <c r="L21" t="n">
-        <v>147.38</v>
+        <v>144.42</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-65.69</v>
+        <v>-64.03</v>
       </c>
       <c r="K22" t="n">
-        <v>142.18</v>
+        <v>138.58</v>
       </c>
       <c r="L22" t="n">
-        <v>156.62</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>229.81</v>
+        <v>244.52</v>
       </c>
       <c r="K23" t="n">
-        <v>51.85</v>
+        <v>55.17</v>
       </c>
       <c r="L23" t="n">
-        <v>235.58</v>
+        <v>250.66</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>206.75</v>
+        <v>215.36</v>
       </c>
       <c r="K24" t="n">
-        <v>-60.31</v>
+        <v>-62.82</v>
       </c>
       <c r="L24" t="n">
-        <v>215.37</v>
+        <v>224.33</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.78</v>
+        <v>-11.4</v>
       </c>
       <c r="K25" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>10.82</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-296.31</v>
+        <v>-298.73</v>
       </c>
       <c r="K26" t="n">
-        <v>252.93</v>
+        <v>255</v>
       </c>
       <c r="L26" t="n">
-        <v>389.58</v>
+        <v>392.76</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>134.89</v>
+        <v>153.65</v>
       </c>
       <c r="K27" t="n">
-        <v>234.09</v>
+        <v>266.65</v>
       </c>
       <c r="L27" t="n">
-        <v>270.18</v>
+        <v>307.75</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-508.68</v>
+        <v>-555.76</v>
       </c>
       <c r="K28" t="n">
-        <v>-43.89</v>
+        <v>-47.95</v>
       </c>
       <c r="L28" t="n">
-        <v>510.57</v>
+        <v>557.8200000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-29.06</v>
+        <v>-26.98</v>
       </c>
       <c r="K29" t="n">
-        <v>-107.69</v>
+        <v>-99.98</v>
       </c>
       <c r="L29" t="n">
-        <v>111.54</v>
+        <v>103.56</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>101.12</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>10.68</v>
+        <v>9.67</v>
       </c>
       <c r="L30" t="n">
-        <v>101.69</v>
+        <v>92.08</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-87.56999999999999</v>
+        <v>-81.05</v>
       </c>
       <c r="K31" t="n">
-        <v>-60.32</v>
+        <v>-55.83</v>
       </c>
       <c r="L31" t="n">
-        <v>106.33</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>27.53</v>
+        <v>25.64</v>
       </c>
       <c r="K32" t="n">
-        <v>132.17</v>
+        <v>123.05</v>
       </c>
       <c r="L32" t="n">
-        <v>135.01</v>
+        <v>125.69</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>62.72</v>
+        <v>60.44</v>
       </c>
       <c r="K33" t="n">
-        <v>45.14</v>
+        <v>43.5</v>
       </c>
       <c r="L33" t="n">
-        <v>77.27</v>
+        <v>74.47</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>12.15</v>
+        <v>11.52</v>
       </c>
       <c r="K34" t="n">
-        <v>-107.68</v>
+        <v>-102.13</v>
       </c>
       <c r="L34" t="n">
-        <v>108.36</v>
+        <v>102.77</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-122.38</v>
+        <v>-120.26</v>
       </c>
       <c r="K35" t="n">
-        <v>79.7</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>146.04</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="K36" t="n">
-        <v>128.7</v>
+        <v>130.08</v>
       </c>
       <c r="L36" t="n">
-        <v>128.71</v>
+        <v>130.09</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-211.57</v>
+        <v>-201.72</v>
       </c>
       <c r="K37" t="n">
-        <v>34.02</v>
+        <v>32.43</v>
       </c>
       <c r="L37" t="n">
-        <v>214.28</v>
+        <v>204.31</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>219.77</v>
+        <v>230.49</v>
       </c>
       <c r="K38" t="n">
-        <v>225.14</v>
+        <v>236.12</v>
       </c>
       <c r="L38" t="n">
-        <v>314.62</v>
+        <v>329.97</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-172.95</v>
+        <v>-178.12</v>
       </c>
       <c r="K39" t="n">
-        <v>130.04</v>
+        <v>133.93</v>
       </c>
       <c r="L39" t="n">
-        <v>216.38</v>
+        <v>222.86</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>179.79</v>
+        <v>185.09</v>
       </c>
       <c r="K40" t="n">
-        <v>168.1</v>
+        <v>173.05</v>
       </c>
       <c r="L40" t="n">
-        <v>246.13</v>
+        <v>253.39</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-25.55</v>
+        <v>-30.85</v>
       </c>
       <c r="K41" t="n">
-        <v>-217.71</v>
+        <v>-262.86</v>
       </c>
       <c r="L41" t="n">
-        <v>219.21</v>
+        <v>264.67</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-83.22</v>
+        <v>-89.42</v>
       </c>
       <c r="K42" t="n">
-        <v>246.28</v>
+        <v>264.63</v>
       </c>
       <c r="L42" t="n">
-        <v>259.96</v>
+        <v>279.33</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-86.43000000000001</v>
+        <v>-104.12</v>
       </c>
       <c r="K43" t="n">
-        <v>182.76</v>
+        <v>220.16</v>
       </c>
       <c r="L43" t="n">
-        <v>202.16</v>
+        <v>243.54</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>70.5</v>
+        <v>60.42</v>
       </c>
       <c r="K44" t="n">
-        <v>-62.35</v>
+        <v>-53.44</v>
       </c>
       <c r="L44" t="n">
-        <v>94.12</v>
+        <v>80.67</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>83.95999999999999</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.18</v>
+        <v>-7.16</v>
       </c>
       <c r="L45" t="n">
-        <v>84.36</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>83.09</v>
+        <v>77.03</v>
       </c>
       <c r="K46" t="n">
-        <v>79.75</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>115.17</v>
+        <v>106.77</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-87.31999999999999</v>
+        <v>-76.89</v>
       </c>
       <c r="K47" t="n">
-        <v>27.41</v>
+        <v>24.14</v>
       </c>
       <c r="L47" t="n">
-        <v>91.52</v>
+        <v>80.59</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-69.01000000000001</v>
+        <v>-58.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-128.15</v>
+        <v>-108.88</v>
       </c>
       <c r="L48" t="n">
-        <v>145.55</v>
+        <v>123.66</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-23.21</v>
+        <v>-21.49</v>
       </c>
       <c r="K49" t="n">
-        <v>-83.83</v>
+        <v>-77.63</v>
       </c>
       <c r="L49" t="n">
-        <v>86.98999999999999</v>
+        <v>80.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>142.22</v>
+        <v>140.77</v>
       </c>
       <c r="K50" t="n">
-        <v>-13.68</v>
+        <v>-13.54</v>
       </c>
       <c r="L50" t="n">
-        <v>142.88</v>
+        <v>141.42</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-154.71</v>
+        <v>-152.58</v>
       </c>
       <c r="K51" t="n">
-        <v>-19.38</v>
+        <v>-19.11</v>
       </c>
       <c r="L51" t="n">
-        <v>155.92</v>
+        <v>153.77</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-38.61</v>
+        <v>-38.84</v>
       </c>
       <c r="K52" t="n">
-        <v>130.38</v>
+        <v>131.18</v>
       </c>
       <c r="L52" t="n">
-        <v>135.98</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>331.45</v>
+        <v>339.25</v>
       </c>
       <c r="K53" t="n">
-        <v>93.98999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="L53" t="n">
-        <v>344.52</v>
+        <v>352.62</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-259.09</v>
+        <v>-275.81</v>
       </c>
       <c r="K54" t="n">
-        <v>-96.95</v>
+        <v>-103.21</v>
       </c>
       <c r="L54" t="n">
-        <v>276.64</v>
+        <v>294.48</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-158.18</v>
+        <v>-169.38</v>
       </c>
       <c r="K55" t="n">
-        <v>-139.63</v>
+        <v>-149.51</v>
       </c>
       <c r="L55" t="n">
-        <v>210.99</v>
+        <v>225.93</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-258.3</v>
+        <v>-313.33</v>
       </c>
       <c r="K56" t="n">
-        <v>-172.47</v>
+        <v>-209.22</v>
       </c>
       <c r="L56" t="n">
-        <v>310.59</v>
+        <v>376.76</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-222.24</v>
+        <v>-248.27</v>
       </c>
       <c r="K57" t="n">
-        <v>-374.38</v>
+        <v>-418.22</v>
       </c>
       <c r="L57" t="n">
-        <v>435.38</v>
+        <v>486.36</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>236.1</v>
+        <v>286.87</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.32</v>
+        <v>-7.67</v>
       </c>
       <c r="L58" t="n">
-        <v>236.18</v>
+        <v>286.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-56.27</v>
+        <v>-55.66</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.2</v>
+        <v>-12.07</v>
       </c>
       <c r="L59" t="n">
-        <v>57.57</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-69.73999999999999</v>
+        <v>-57.49</v>
       </c>
       <c r="K60" t="n">
-        <v>-37.43</v>
+        <v>-30.86</v>
       </c>
       <c r="L60" t="n">
-        <v>79.15000000000001</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-87.02</v>
+        <v>-74.16</v>
       </c>
       <c r="K61" t="n">
-        <v>38.77</v>
+        <v>33.04</v>
       </c>
       <c r="L61" t="n">
-        <v>95.27</v>
+        <v>81.18000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-228.62</v>
+        <v>-182.74</v>
       </c>
       <c r="K62" t="n">
-        <v>-31.28</v>
+        <v>-25.01</v>
       </c>
       <c r="L62" t="n">
-        <v>230.76</v>
+        <v>184.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-80.97</v>
+        <v>-77.31</v>
       </c>
       <c r="K63" t="n">
-        <v>-60.4</v>
+        <v>-57.67</v>
       </c>
       <c r="L63" t="n">
-        <v>101.02</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>89.15000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>-59.59</v>
+        <v>-51.42</v>
       </c>
       <c r="L64" t="n">
-        <v>107.23</v>
+        <v>92.53</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>58.25</v>
+        <v>61</v>
       </c>
       <c r="K65" t="n">
-        <v>-74.09</v>
+        <v>-77.59</v>
       </c>
       <c r="L65" t="n">
-        <v>94.25</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>-156.92</v>
+        <v>-153.22</v>
       </c>
       <c r="K66" t="n">
-        <v>78.03</v>
+        <v>76.19</v>
       </c>
       <c r="L66" t="n">
-        <v>175.25</v>
+        <v>171.12</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-144.43</v>
+        <v>-143.47</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.92</v>
+        <v>-3.9</v>
       </c>
       <c r="L67" t="n">
-        <v>144.49</v>
+        <v>143.52</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>84.34999999999999</v>
+        <v>95.52</v>
       </c>
       <c r="K68" t="n">
-        <v>-143.54</v>
+        <v>-162.55</v>
       </c>
       <c r="L68" t="n">
-        <v>166.49</v>
+        <v>188.54</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>148.15</v>
+        <v>164.83</v>
       </c>
       <c r="K69" t="n">
-        <v>-75.31999999999999</v>
+        <v>-83.79000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>166.2</v>
+        <v>184.9</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-145.65</v>
+        <v>-160.66</v>
       </c>
       <c r="K70" t="n">
-        <v>-116.89</v>
+        <v>-128.93</v>
       </c>
       <c r="L70" t="n">
-        <v>186.75</v>
+        <v>205.99</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-231.39</v>
+        <v>-260.93</v>
       </c>
       <c r="K71" t="n">
-        <v>341.34</v>
+        <v>384.91</v>
       </c>
       <c r="L71" t="n">
-        <v>412.38</v>
+        <v>465.01</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-107.45</v>
+        <v>-121.77</v>
       </c>
       <c r="K72" t="n">
-        <v>381.49</v>
+        <v>432.3</v>
       </c>
       <c r="L72" t="n">
-        <v>396.33</v>
+        <v>449.12</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.17</v>
+        <v>-6.18</v>
       </c>
       <c r="K73" t="n">
-        <v>-230.2</v>
+        <v>-275.47</v>
       </c>
       <c r="L73" t="n">
-        <v>230.26</v>
+        <v>275.54</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-75.38</v>
+        <v>-61.06</v>
       </c>
       <c r="K74" t="n">
-        <v>53.57</v>
+        <v>43.39</v>
       </c>
       <c r="L74" t="n">
-        <v>92.48</v>
+        <v>74.91</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-110.35</v>
+        <v>-87.16</v>
       </c>
       <c r="K75" t="n">
-        <v>23.81</v>
+        <v>18.81</v>
       </c>
       <c r="L75" t="n">
-        <v>112.89</v>
+        <v>89.17</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>30.33</v>
+        <v>25.29</v>
       </c>
       <c r="K76" t="n">
-        <v>70.59</v>
+        <v>58.86</v>
       </c>
       <c r="L76" t="n">
-        <v>76.83</v>
+        <v>64.06</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="K77" t="n">
-        <v>32.16</v>
+        <v>27.73</v>
       </c>
       <c r="L77" t="n">
-        <v>32.19</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>119.17</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>40.73</v>
+        <v>34.04</v>
       </c>
       <c r="L78" t="n">
-        <v>125.94</v>
+        <v>105.26</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>22.84</v>
+        <v>19.74</v>
       </c>
       <c r="K79" t="n">
-        <v>-47.7</v>
+        <v>-41.22</v>
       </c>
       <c r="L79" t="n">
-        <v>52.88</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>136.8</v>
+        <v>137.68</v>
       </c>
       <c r="K80" t="n">
-        <v>54.59</v>
+        <v>54.94</v>
       </c>
       <c r="L80" t="n">
-        <v>147.29</v>
+        <v>148.24</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-70.93000000000001</v>
+        <v>-68.34</v>
       </c>
       <c r="K81" t="n">
-        <v>189.41</v>
+        <v>182.5</v>
       </c>
       <c r="L81" t="n">
-        <v>202.25</v>
+        <v>194.87</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-22.23</v>
+        <v>-22.9</v>
       </c>
       <c r="K82" t="n">
-        <v>104.38</v>
+        <v>107.51</v>
       </c>
       <c r="L82" t="n">
-        <v>106.73</v>
+        <v>109.92</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>129.97</v>
+        <v>143.88</v>
       </c>
       <c r="K83" t="n">
-        <v>-139.4</v>
+        <v>-154.33</v>
       </c>
       <c r="L83" t="n">
-        <v>190.59</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>155.3</v>
+        <v>164.82</v>
       </c>
       <c r="K84" t="n">
-        <v>215.67</v>
+        <v>228.89</v>
       </c>
       <c r="L84" t="n">
-        <v>265.76</v>
+        <v>282.06</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.57</v>
+        <v>-5.15</v>
       </c>
       <c r="K85" t="n">
-        <v>-160.9</v>
+        <v>-181.12</v>
       </c>
       <c r="L85" t="n">
-        <v>160.97</v>
+        <v>181.19</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-282.56</v>
+        <v>-335</v>
       </c>
       <c r="K86" t="n">
-        <v>-248.39</v>
+        <v>-294.49</v>
       </c>
       <c r="L86" t="n">
-        <v>376.21</v>
+        <v>446.03</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>241.28</v>
+        <v>282.82</v>
       </c>
       <c r="K87" t="n">
-        <v>-344.19</v>
+        <v>-403.45</v>
       </c>
       <c r="L87" t="n">
-        <v>420.33</v>
+        <v>492.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-527.74</v>
+        <v>-600.88</v>
       </c>
       <c r="K88" t="n">
-        <v>139.45</v>
+        <v>158.78</v>
       </c>
       <c r="L88" t="n">
-        <v>545.85</v>
+        <v>621.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>63.43</v>
+        <v>64.47</v>
       </c>
       <c r="K14" t="n">
-        <v>26.77</v>
+        <v>27.21</v>
       </c>
       <c r="L14" t="n">
-        <v>68.84999999999999</v>
+        <v>69.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-110.52</v>
+        <v>-102.74</v>
       </c>
       <c r="K15" t="n">
-        <v>-77.86</v>
+        <v>-72.37</v>
       </c>
       <c r="L15" t="n">
-        <v>135.19</v>
+        <v>125.67</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-24.47</v>
+        <v>-24.27</v>
       </c>
       <c r="K16" t="n">
-        <v>74.73999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="L16" t="n">
-        <v>78.64</v>
+        <v>78.01000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>112.59</v>
+        <v>109.7</v>
       </c>
       <c r="K17" t="n">
-        <v>10.54</v>
+        <v>10.26</v>
       </c>
       <c r="L17" t="n">
-        <v>113.08</v>
+        <v>110.17</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>100.02</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>81.41</v>
+        <v>78.42</v>
       </c>
       <c r="L18" t="n">
-        <v>128.96</v>
+        <v>124.23</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.69</v>
+        <v>-7.68</v>
       </c>
       <c r="K19" t="n">
-        <v>93.08</v>
+        <v>93.02</v>
       </c>
       <c r="L19" t="n">
-        <v>93.40000000000001</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-140.6</v>
+        <v>-142.28</v>
       </c>
       <c r="K20" t="n">
-        <v>24.26</v>
+        <v>24.55</v>
       </c>
       <c r="L20" t="n">
-        <v>142.68</v>
+        <v>144.38</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.37</v>
+        <v>-10.27</v>
       </c>
       <c r="K21" t="n">
-        <v>144.05</v>
+        <v>142.68</v>
       </c>
       <c r="L21" t="n">
-        <v>144.42</v>
+        <v>143.05</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-64.03</v>
+        <v>-62.96</v>
       </c>
       <c r="K22" t="n">
-        <v>138.58</v>
+        <v>136.28</v>
       </c>
       <c r="L22" t="n">
-        <v>152.66</v>
+        <v>150.12</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>244.52</v>
+        <v>244.27</v>
       </c>
       <c r="K23" t="n">
-        <v>55.17</v>
+        <v>55.11</v>
       </c>
       <c r="L23" t="n">
-        <v>250.66</v>
+        <v>250.41</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>215.36</v>
+        <v>213.55</v>
       </c>
       <c r="K24" t="n">
-        <v>-62.82</v>
+        <v>-62.29</v>
       </c>
       <c r="L24" t="n">
-        <v>224.33</v>
+        <v>222.45</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.4</v>
+        <v>-11.97</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="L25" t="n">
-        <v>11.43</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-298.73</v>
+        <v>-284.77</v>
       </c>
       <c r="K26" t="n">
-        <v>255</v>
+        <v>243.08</v>
       </c>
       <c r="L26" t="n">
-        <v>392.76</v>
+        <v>374.41</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>153.65</v>
+        <v>156.82</v>
       </c>
       <c r="K27" t="n">
-        <v>266.65</v>
+        <v>272.14</v>
       </c>
       <c r="L27" t="n">
-        <v>307.75</v>
+        <v>314.09</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-555.76</v>
+        <v>-531.54</v>
       </c>
       <c r="K28" t="n">
-        <v>-47.95</v>
+        <v>-45.86</v>
       </c>
       <c r="L28" t="n">
-        <v>557.8200000000001</v>
+        <v>533.52</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.98</v>
+        <v>-25.85</v>
       </c>
       <c r="K29" t="n">
-        <v>-99.98</v>
+        <v>-95.81</v>
       </c>
       <c r="L29" t="n">
-        <v>103.56</v>
+        <v>99.23999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>91.56999999999999</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>9.67</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>92.08</v>
+        <v>90.18000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-81.05</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-55.83</v>
+        <v>-53.51</v>
       </c>
       <c r="L31" t="n">
-        <v>98.42</v>
+        <v>94.33</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>25.64</v>
+        <v>24.7</v>
       </c>
       <c r="K32" t="n">
-        <v>123.05</v>
+        <v>118.58</v>
       </c>
       <c r="L32" t="n">
-        <v>125.69</v>
+        <v>121.13</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>60.44</v>
+        <v>62.91</v>
       </c>
       <c r="K33" t="n">
-        <v>43.5</v>
+        <v>45.28</v>
       </c>
       <c r="L33" t="n">
-        <v>74.47</v>
+        <v>77.51000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>11.52</v>
+        <v>11.27</v>
       </c>
       <c r="K34" t="n">
-        <v>-102.13</v>
+        <v>-99.89</v>
       </c>
       <c r="L34" t="n">
-        <v>102.77</v>
+        <v>100.53</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-120.26</v>
+        <v>-119.4</v>
       </c>
       <c r="K35" t="n">
-        <v>78.31999999999999</v>
+        <v>77.77</v>
       </c>
       <c r="L35" t="n">
-        <v>143.51</v>
+        <v>142.49</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.06</v>
+        <v>-1.11</v>
       </c>
       <c r="K36" t="n">
-        <v>130.08</v>
+        <v>135.31</v>
       </c>
       <c r="L36" t="n">
-        <v>130.09</v>
+        <v>135.32</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-201.72</v>
+        <v>-196.39</v>
       </c>
       <c r="K37" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="L37" t="n">
-        <v>204.31</v>
+        <v>198.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>230.49</v>
+        <v>224.37</v>
       </c>
       <c r="K38" t="n">
-        <v>236.12</v>
+        <v>229.86</v>
       </c>
       <c r="L38" t="n">
-        <v>329.97</v>
+        <v>321.21</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-178.12</v>
+        <v>-175.18</v>
       </c>
       <c r="K39" t="n">
-        <v>133.93</v>
+        <v>131.71</v>
       </c>
       <c r="L39" t="n">
-        <v>222.86</v>
+        <v>219.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>185.09</v>
+        <v>179.72</v>
       </c>
       <c r="K40" t="n">
-        <v>173.05</v>
+        <v>168.03</v>
       </c>
       <c r="L40" t="n">
-        <v>253.39</v>
+        <v>246.04</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-30.85</v>
+        <v>-32.93</v>
       </c>
       <c r="K41" t="n">
-        <v>-262.86</v>
+        <v>-280.6</v>
       </c>
       <c r="L41" t="n">
-        <v>264.67</v>
+        <v>282.53</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-89.42</v>
+        <v>-90.12</v>
       </c>
       <c r="K42" t="n">
-        <v>264.63</v>
+        <v>266.71</v>
       </c>
       <c r="L42" t="n">
-        <v>279.33</v>
+        <v>281.52</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-104.12</v>
+        <v>-112.16</v>
       </c>
       <c r="K43" t="n">
-        <v>220.16</v>
+        <v>237.15</v>
       </c>
       <c r="L43" t="n">
-        <v>243.54</v>
+        <v>262.33</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>60.42</v>
+        <v>61.04</v>
       </c>
       <c r="K44" t="n">
-        <v>-53.44</v>
+        <v>-53.98</v>
       </c>
       <c r="L44" t="n">
-        <v>80.67</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>73.51000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.16</v>
+        <v>-7.34</v>
       </c>
       <c r="L45" t="n">
-        <v>73.86</v>
+        <v>75.76000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>77.03</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>73.93000000000001</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>106.77</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-76.89</v>
+        <v>-78.88</v>
       </c>
       <c r="K47" t="n">
-        <v>24.14</v>
+        <v>24.76</v>
       </c>
       <c r="L47" t="n">
-        <v>80.59</v>
+        <v>82.68000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.63</v>
+        <v>-57.15</v>
       </c>
       <c r="K48" t="n">
-        <v>-108.88</v>
+        <v>-106.13</v>
       </c>
       <c r="L48" t="n">
-        <v>123.66</v>
+        <v>120.54</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-21.49</v>
+        <v>-22.13</v>
       </c>
       <c r="K49" t="n">
-        <v>-77.63</v>
+        <v>-79.92</v>
       </c>
       <c r="L49" t="n">
-        <v>80.55</v>
+        <v>82.92</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>140.77</v>
+        <v>141.85</v>
       </c>
       <c r="K50" t="n">
-        <v>-13.54</v>
+        <v>-13.64</v>
       </c>
       <c r="L50" t="n">
-        <v>141.42</v>
+        <v>142.51</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-152.58</v>
+        <v>-154.08</v>
       </c>
       <c r="K51" t="n">
-        <v>-19.11</v>
+        <v>-19.3</v>
       </c>
       <c r="L51" t="n">
-        <v>153.77</v>
+        <v>155.28</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-38.84</v>
+        <v>-40.04</v>
       </c>
       <c r="K52" t="n">
-        <v>131.18</v>
+        <v>135.22</v>
       </c>
       <c r="L52" t="n">
-        <v>136.81</v>
+        <v>141.02</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>339.25</v>
+        <v>324.29</v>
       </c>
       <c r="K53" t="n">
-        <v>96.2</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>352.62</v>
+        <v>337.08</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-275.81</v>
+        <v>-273.77</v>
       </c>
       <c r="K54" t="n">
-        <v>-103.21</v>
+        <v>-102.45</v>
       </c>
       <c r="L54" t="n">
-        <v>294.48</v>
+        <v>292.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-169.38</v>
+        <v>-171.25</v>
       </c>
       <c r="K55" t="n">
-        <v>-149.51</v>
+        <v>-151.16</v>
       </c>
       <c r="L55" t="n">
-        <v>225.93</v>
+        <v>228.42</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-313.33</v>
+        <v>-328.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-209.22</v>
+        <v>-219.05</v>
       </c>
       <c r="L56" t="n">
-        <v>376.76</v>
+        <v>394.46</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-248.27</v>
+        <v>-243.11</v>
       </c>
       <c r="K57" t="n">
-        <v>-418.22</v>
+        <v>-409.54</v>
       </c>
       <c r="L57" t="n">
-        <v>486.36</v>
+        <v>476.26</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>286.87</v>
+        <v>307.03</v>
       </c>
       <c r="K58" t="n">
-        <v>-7.67</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>286.97</v>
+        <v>307.14</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-55.66</v>
+        <v>-58.96</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.07</v>
+        <v>-12.78</v>
       </c>
       <c r="L59" t="n">
-        <v>56.95</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-57.49</v>
+        <v>-58.68</v>
       </c>
       <c r="K60" t="n">
-        <v>-30.86</v>
+        <v>-31.5</v>
       </c>
       <c r="L60" t="n">
-        <v>65.25</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-74.16</v>
+        <v>-73.05</v>
       </c>
       <c r="K61" t="n">
-        <v>33.04</v>
+        <v>32.54</v>
       </c>
       <c r="L61" t="n">
-        <v>81.18000000000001</v>
+        <v>79.97</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-182.74</v>
+        <v>-167.14</v>
       </c>
       <c r="K62" t="n">
-        <v>-25.01</v>
+        <v>-22.87</v>
       </c>
       <c r="L62" t="n">
-        <v>184.44</v>
+        <v>168.7</v>
       </c>
     </row>
     <row r="63">
@@ -2698,7 +2698,7 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-77.31</v>
+        <v>-77.31999999999999</v>
       </c>
       <c r="K63" t="n">
         <v>-57.67</v>
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>76.93000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>-51.42</v>
+        <v>-51.74</v>
       </c>
       <c r="L64" t="n">
-        <v>92.53</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>61</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-77.59</v>
+        <v>-83.26000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>98.7</v>
+        <v>105.91</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>-153.22</v>
+        <v>-153.53</v>
       </c>
       <c r="K66" t="n">
-        <v>76.19</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>171.12</v>
+        <v>171.47</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-143.47</v>
+        <v>-145.65</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.9</v>
+        <v>-3.96</v>
       </c>
       <c r="L67" t="n">
-        <v>143.52</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>95.52</v>
+        <v>101.27</v>
       </c>
       <c r="K68" t="n">
-        <v>-162.55</v>
+        <v>-172.33</v>
       </c>
       <c r="L68" t="n">
-        <v>188.54</v>
+        <v>199.89</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>164.83</v>
+        <v>172.87</v>
       </c>
       <c r="K69" t="n">
-        <v>-83.79000000000001</v>
+        <v>-87.88</v>
       </c>
       <c r="L69" t="n">
-        <v>184.9</v>
+        <v>193.93</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-160.66</v>
+        <v>-165.88</v>
       </c>
       <c r="K70" t="n">
-        <v>-128.93</v>
+        <v>-133.13</v>
       </c>
       <c r="L70" t="n">
-        <v>205.99</v>
+        <v>212.7</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-260.93</v>
+        <v>-256.41</v>
       </c>
       <c r="K71" t="n">
-        <v>384.91</v>
+        <v>378.24</v>
       </c>
       <c r="L71" t="n">
-        <v>465.01</v>
+        <v>456.95</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-121.77</v>
+        <v>-120.37</v>
       </c>
       <c r="K72" t="n">
-        <v>432.3</v>
+        <v>427.33</v>
       </c>
       <c r="L72" t="n">
-        <v>449.12</v>
+        <v>443.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.18</v>
+        <v>-6.53</v>
       </c>
       <c r="K73" t="n">
-        <v>-275.47</v>
+        <v>-291.09</v>
       </c>
       <c r="L73" t="n">
-        <v>275.54</v>
+        <v>291.16</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-61.06</v>
+        <v>-61.87</v>
       </c>
       <c r="K74" t="n">
-        <v>43.39</v>
+        <v>43.97</v>
       </c>
       <c r="L74" t="n">
-        <v>74.91</v>
+        <v>75.91</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-87.16</v>
+        <v>-85.75</v>
       </c>
       <c r="K75" t="n">
-        <v>18.81</v>
+        <v>18.5</v>
       </c>
       <c r="L75" t="n">
-        <v>89.17</v>
+        <v>87.72</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>25.29</v>
+        <v>26.49</v>
       </c>
       <c r="K76" t="n">
-        <v>58.86</v>
+        <v>61.66</v>
       </c>
       <c r="L76" t="n">
-        <v>64.06</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="K77" t="n">
-        <v>27.73</v>
+        <v>29.92</v>
       </c>
       <c r="L77" t="n">
-        <v>27.77</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>99.59999999999999</v>
+        <v>98.27</v>
       </c>
       <c r="K78" t="n">
-        <v>34.04</v>
+        <v>33.59</v>
       </c>
       <c r="L78" t="n">
-        <v>105.26</v>
+        <v>103.85</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>19.74</v>
+        <v>21.53</v>
       </c>
       <c r="K79" t="n">
-        <v>-41.22</v>
+        <v>-44.96</v>
       </c>
       <c r="L79" t="n">
-        <v>45.7</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>137.68</v>
+        <v>142.5</v>
       </c>
       <c r="K80" t="n">
-        <v>54.94</v>
+        <v>56.86</v>
       </c>
       <c r="L80" t="n">
-        <v>148.24</v>
+        <v>153.43</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-68.34</v>
+        <v>-67.55</v>
       </c>
       <c r="K81" t="n">
-        <v>182.5</v>
+        <v>180.39</v>
       </c>
       <c r="L81" t="n">
-        <v>194.87</v>
+        <v>192.62</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-22.9</v>
+        <v>-24.13</v>
       </c>
       <c r="K82" t="n">
-        <v>107.51</v>
+        <v>113.3</v>
       </c>
       <c r="L82" t="n">
-        <v>109.92</v>
+        <v>115.84</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>143.88</v>
+        <v>149.09</v>
       </c>
       <c r="K83" t="n">
-        <v>-154.33</v>
+        <v>-159.92</v>
       </c>
       <c r="L83" t="n">
-        <v>211</v>
+        <v>218.64</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>164.82</v>
+        <v>162.81</v>
       </c>
       <c r="K84" t="n">
-        <v>228.89</v>
+        <v>226.09</v>
       </c>
       <c r="L84" t="n">
-        <v>282.06</v>
+        <v>278.61</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.15</v>
+        <v>-5.45</v>
       </c>
       <c r="K85" t="n">
-        <v>-181.12</v>
+        <v>-191.78</v>
       </c>
       <c r="L85" t="n">
-        <v>181.19</v>
+        <v>191.86</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-335</v>
+        <v>-338.79</v>
       </c>
       <c r="K86" t="n">
-        <v>-294.49</v>
+        <v>-297.82</v>
       </c>
       <c r="L86" t="n">
-        <v>446.03</v>
+        <v>451.09</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>282.82</v>
+        <v>282.88</v>
       </c>
       <c r="K87" t="n">
-        <v>-403.45</v>
+        <v>-403.53</v>
       </c>
       <c r="L87" t="n">
-        <v>492.7</v>
+        <v>492.81</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-600.88</v>
+        <v>-581.8</v>
       </c>
       <c r="K88" t="n">
-        <v>158.78</v>
+        <v>153.74</v>
       </c>
       <c r="L88" t="n">
-        <v>621.5</v>
+        <v>601.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -628,25 +628,25 @@
         <v>4.58</v>
       </c>
       <c r="F14" t="n">
-        <v>11.99</v>
+        <v>8.98</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>353.4</v>
       </c>
       <c r="H14" t="n">
-        <v>71.3</v>
+        <v>79.3</v>
       </c>
       <c r="I14" t="n">
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>64.47</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>27.21</v>
+        <v>30.98</v>
       </c>
       <c r="L14" t="n">
-        <v>69.98</v>
+        <v>75.02</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>4.16</v>
       </c>
       <c r="F15" t="n">
-        <v>12.52</v>
+        <v>11.12</v>
       </c>
       <c r="G15" t="n">
-        <v>350.3</v>
+        <v>4.1</v>
       </c>
       <c r="H15" t="n">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-102.74</v>
+        <v>-105.51</v>
       </c>
       <c r="K15" t="n">
-        <v>-72.37</v>
+        <v>-73.62</v>
       </c>
       <c r="L15" t="n">
-        <v>125.67</v>
+        <v>128.65</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>4.37</v>
       </c>
       <c r="F16" t="n">
-        <v>10.78</v>
+        <v>11.38</v>
       </c>
       <c r="G16" t="n">
-        <v>356.4</v>
+        <v>329.2</v>
       </c>
       <c r="H16" t="n">
-        <v>79.5</v>
+        <v>77.3</v>
       </c>
       <c r="I16" t="n">
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-24.27</v>
+        <v>-28.23</v>
       </c>
       <c r="K16" t="n">
-        <v>74.14</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>78.01000000000001</v>
+        <v>86.72</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>4.8</v>
       </c>
       <c r="F17" t="n">
-        <v>11.73</v>
+        <v>10.08</v>
       </c>
       <c r="G17" t="n">
-        <v>339.4</v>
+        <v>348.4</v>
       </c>
       <c r="H17" t="n">
-        <v>69.5</v>
+        <v>68.7</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>109.7</v>
+        <v>112.2</v>
       </c>
       <c r="K17" t="n">
-        <v>10.26</v>
+        <v>14.82</v>
       </c>
       <c r="L17" t="n">
-        <v>110.17</v>
+        <v>113.18</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>5.4</v>
       </c>
       <c r="F18" t="n">
-        <v>11.7</v>
+        <v>10.9</v>
       </c>
       <c r="G18" t="n">
-        <v>354.4</v>
+        <v>347.6</v>
       </c>
       <c r="H18" t="n">
-        <v>71.5</v>
+        <v>76.3</v>
       </c>
       <c r="I18" t="n">
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>96.34999999999999</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>78.42</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>124.23</v>
+        <v>129.74</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>5.13</v>
       </c>
       <c r="F19" t="n">
-        <v>11.55</v>
+        <v>10.38</v>
       </c>
       <c r="G19" t="n">
-        <v>355.3</v>
+        <v>344.8</v>
       </c>
       <c r="H19" t="n">
-        <v>78.5</v>
+        <v>76.7</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.68</v>
+        <v>-10.49</v>
       </c>
       <c r="K19" t="n">
-        <v>93.02</v>
+        <v>103.33</v>
       </c>
       <c r="L19" t="n">
-        <v>93.33</v>
+        <v>103.87</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>4.69</v>
       </c>
       <c r="F20" t="n">
-        <v>11.33</v>
+        <v>10.02</v>
       </c>
       <c r="G20" t="n">
-        <v>346.9</v>
+        <v>340.4</v>
       </c>
       <c r="H20" t="n">
-        <v>73.3</v>
+        <v>72.5</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-142.28</v>
+        <v>-144.96</v>
       </c>
       <c r="K20" t="n">
-        <v>24.55</v>
+        <v>44.17</v>
       </c>
       <c r="L20" t="n">
-        <v>144.38</v>
+        <v>151.54</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>4.5</v>
       </c>
       <c r="F21" t="n">
-        <v>11.47</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>357.6</v>
+        <v>343.1</v>
       </c>
       <c r="H21" t="n">
-        <v>69.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.27</v>
+        <v>-19.74</v>
       </c>
       <c r="K21" t="n">
-        <v>142.68</v>
+        <v>173.04</v>
       </c>
       <c r="L21" t="n">
-        <v>143.05</v>
+        <v>174.16</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>4.39</v>
       </c>
       <c r="F22" t="n">
-        <v>11.77</v>
+        <v>9.01</v>
       </c>
       <c r="G22" t="n">
-        <v>350.8</v>
+        <v>349.2</v>
       </c>
       <c r="H22" t="n">
-        <v>72.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-62.96</v>
+        <v>-70.47</v>
       </c>
       <c r="K22" t="n">
-        <v>136.28</v>
+        <v>161.61</v>
       </c>
       <c r="L22" t="n">
-        <v>150.12</v>
+        <v>176.3</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>5.3</v>
       </c>
       <c r="F23" t="n">
-        <v>12.51</v>
+        <v>10.55</v>
       </c>
       <c r="G23" t="n">
-        <v>348.7</v>
+        <v>3.9</v>
       </c>
       <c r="H23" t="n">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>244.27</v>
+        <v>245.44</v>
       </c>
       <c r="K23" t="n">
-        <v>55.11</v>
+        <v>88.87</v>
       </c>
       <c r="L23" t="n">
-        <v>250.41</v>
+        <v>261.04</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>4.73</v>
       </c>
       <c r="F24" t="n">
-        <v>11.51</v>
+        <v>10.05</v>
       </c>
       <c r="G24" t="n">
-        <v>356.8</v>
+        <v>343.9</v>
       </c>
       <c r="H24" t="n">
-        <v>72.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="I24" t="n">
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>213.55</v>
+        <v>223.61</v>
       </c>
       <c r="K24" t="n">
-        <v>-62.29</v>
+        <v>-34.89</v>
       </c>
       <c r="L24" t="n">
-        <v>222.45</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>5.17</v>
       </c>
       <c r="F25" t="n">
-        <v>11.75</v>
+        <v>12.6</v>
       </c>
       <c r="G25" t="n">
         <v>348.7</v>
       </c>
       <c r="H25" t="n">
-        <v>71.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.97</v>
+        <v>-49.84</v>
       </c>
       <c r="K25" t="n">
-        <v>0.98</v>
+        <v>117.75</v>
       </c>
       <c r="L25" t="n">
-        <v>12.01</v>
+        <v>127.86</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>4.3</v>
       </c>
       <c r="F26" t="n">
-        <v>11.23</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>352.6</v>
+        <v>338.3</v>
       </c>
       <c r="H26" t="n">
-        <v>71.2</v>
+        <v>75.3</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-284.77</v>
+        <v>-309.18</v>
       </c>
       <c r="K26" t="n">
-        <v>243.08</v>
+        <v>272.96</v>
       </c>
       <c r="L26" t="n">
-        <v>374.41</v>
+        <v>412.44</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>4.79</v>
       </c>
       <c r="F27" t="n">
-        <v>11.83</v>
+        <v>9.09</v>
       </c>
       <c r="G27" t="n">
-        <v>1.7</v>
+        <v>350.2</v>
       </c>
       <c r="H27" t="n">
-        <v>78.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>156.82</v>
+        <v>138.78</v>
       </c>
       <c r="K27" t="n">
-        <v>272.14</v>
+        <v>323.6</v>
       </c>
       <c r="L27" t="n">
-        <v>314.09</v>
+        <v>352.11</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>5.08</v>
       </c>
       <c r="F28" t="n">
-        <v>12.16</v>
+        <v>12.6</v>
       </c>
       <c r="G28" t="n">
-        <v>344.2</v>
+        <v>357</v>
       </c>
       <c r="H28" t="n">
-        <v>77.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-531.54</v>
+        <v>-523.83</v>
       </c>
       <c r="K28" t="n">
-        <v>-45.86</v>
+        <v>-13.15</v>
       </c>
       <c r="L28" t="n">
-        <v>533.52</v>
+        <v>523.99</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>4.62</v>
       </c>
       <c r="F29" t="n">
-        <v>11.88</v>
+        <v>11.51</v>
       </c>
       <c r="G29" t="n">
-        <v>356.4</v>
+        <v>345.5</v>
       </c>
       <c r="H29" t="n">
-        <v>84.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.85</v>
+        <v>33.18</v>
       </c>
       <c r="K29" t="n">
-        <v>-95.81</v>
+        <v>-61.45</v>
       </c>
       <c r="L29" t="n">
-        <v>99.23999999999999</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="30">
@@ -1297,28 +1297,28 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.94</v>
+        <v>4.43</v>
       </c>
       <c r="F30" t="n">
-        <v>11.49</v>
+        <v>8.84</v>
       </c>
       <c r="G30" t="n">
-        <v>347.3</v>
+        <v>1.9</v>
       </c>
       <c r="H30" t="n">
-        <v>69.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="I30" t="n">
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>89.68000000000001</v>
+        <v>-15.05</v>
       </c>
       <c r="K30" t="n">
-        <v>9.470000000000001</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>90.18000000000001</v>
+        <v>95.68000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1339,28 +1339,28 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="F31" t="n">
-        <v>11.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>339.9</v>
+        <v>340.3</v>
       </c>
       <c r="H31" t="n">
-        <v>72.7</v>
+        <v>67.3</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-77.68000000000001</v>
+        <v>57.43</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.51</v>
+        <v>69.72</v>
       </c>
       <c r="L31" t="n">
-        <v>94.33</v>
+        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1381,28 +1381,28 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.72</v>
+        <v>6.01</v>
       </c>
       <c r="F32" t="n">
-        <v>11.8</v>
+        <v>13.57</v>
       </c>
       <c r="G32" t="n">
-        <v>355</v>
+        <v>350.8</v>
       </c>
       <c r="H32" t="n">
-        <v>79.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>24.7</v>
+        <v>-50.36</v>
       </c>
       <c r="K32" t="n">
-        <v>118.58</v>
+        <v>-32.82</v>
       </c>
       <c r="L32" t="n">
-        <v>121.13</v>
+        <v>60.11</v>
       </c>
     </row>
     <row r="33">
@@ -1423,28 +1423,28 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.93</v>
+        <v>5.08</v>
       </c>
       <c r="F33" t="n">
-        <v>11.49</v>
+        <v>12.01</v>
       </c>
       <c r="G33" t="n">
-        <v>354.1</v>
+        <v>341</v>
       </c>
       <c r="H33" t="n">
-        <v>72.8</v>
+        <v>75.3</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>62.91</v>
+        <v>-86.65000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>45.28</v>
+        <v>7.04</v>
       </c>
       <c r="L33" t="n">
-        <v>77.51000000000001</v>
+        <v>86.93000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1465,28 +1465,28 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.47</v>
+        <v>4.63</v>
       </c>
       <c r="F34" t="n">
-        <v>11.53</v>
+        <v>10.7</v>
       </c>
       <c r="G34" t="n">
-        <v>349.1</v>
+        <v>339.1</v>
       </c>
       <c r="H34" t="n">
-        <v>71.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>11.27</v>
+        <v>-48.14</v>
       </c>
       <c r="K34" t="n">
-        <v>-99.89</v>
+        <v>-61.27</v>
       </c>
       <c r="L34" t="n">
-        <v>100.53</v>
+        <v>77.92</v>
       </c>
     </row>
     <row r="35">
@@ -1507,28 +1507,28 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.41</v>
+        <v>5.33</v>
       </c>
       <c r="F35" t="n">
-        <v>11.74</v>
+        <v>10.4</v>
       </c>
       <c r="G35" t="n">
-        <v>358.7</v>
+        <v>5.9</v>
       </c>
       <c r="H35" t="n">
-        <v>72.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I35" t="n">
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-119.4</v>
+        <v>-118.12</v>
       </c>
       <c r="K35" t="n">
-        <v>77.77</v>
+        <v>33.77</v>
       </c>
       <c r="L35" t="n">
-        <v>142.49</v>
+        <v>122.85</v>
       </c>
     </row>
     <row r="36">
@@ -1549,28 +1549,28 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.69</v>
+        <v>4.94</v>
       </c>
       <c r="F36" t="n">
-        <v>11.82</v>
+        <v>11.23</v>
       </c>
       <c r="G36" t="n">
-        <v>347.9</v>
+        <v>3.9</v>
       </c>
       <c r="H36" t="n">
-        <v>72.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.11</v>
+        <v>176.05</v>
       </c>
       <c r="K36" t="n">
-        <v>135.31</v>
+        <v>179.06</v>
       </c>
       <c r="L36" t="n">
-        <v>135.32</v>
+        <v>251.11</v>
       </c>
     </row>
     <row r="37">
@@ -1591,28 +1591,28 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.6</v>
+        <v>5.46</v>
       </c>
       <c r="F37" t="n">
-        <v>11.81</v>
+        <v>12.87</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9</v>
+        <v>354.2</v>
       </c>
       <c r="H37" t="n">
-        <v>80.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-196.39</v>
+        <v>-161.02</v>
       </c>
       <c r="K37" t="n">
-        <v>31.58</v>
+        <v>195.92</v>
       </c>
       <c r="L37" t="n">
-        <v>198.91</v>
+        <v>253.59</v>
       </c>
     </row>
     <row r="38">
@@ -1633,28 +1633,28 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.78</v>
+        <v>5.11</v>
       </c>
       <c r="F38" t="n">
-        <v>12.49</v>
+        <v>12.67</v>
       </c>
       <c r="G38" t="n">
-        <v>352.9</v>
+        <v>359</v>
       </c>
       <c r="H38" t="n">
-        <v>80.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>224.37</v>
+        <v>-197.78</v>
       </c>
       <c r="K38" t="n">
-        <v>229.86</v>
+        <v>-10.9</v>
       </c>
       <c r="L38" t="n">
-        <v>321.21</v>
+        <v>198.08</v>
       </c>
     </row>
     <row r="39">
@@ -1675,28 +1675,28 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="F39" t="n">
-        <v>11.82</v>
+        <v>10.55</v>
       </c>
       <c r="G39" t="n">
-        <v>3.8</v>
+        <v>356.2</v>
       </c>
       <c r="H39" t="n">
-        <v>70</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-175.18</v>
+        <v>193.77</v>
       </c>
       <c r="K39" t="n">
-        <v>131.71</v>
+        <v>-44.94</v>
       </c>
       <c r="L39" t="n">
-        <v>219.17</v>
+        <v>198.91</v>
       </c>
     </row>
     <row r="40">
@@ -1717,28 +1717,28 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.82</v>
+        <v>5.48</v>
       </c>
       <c r="F40" t="n">
-        <v>12.18</v>
+        <v>11.86</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4</v>
+        <v>358.9</v>
       </c>
       <c r="H40" t="n">
-        <v>71.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>179.72</v>
+        <v>-188.74</v>
       </c>
       <c r="K40" t="n">
-        <v>168.03</v>
+        <v>226.2</v>
       </c>
       <c r="L40" t="n">
-        <v>246.04</v>
+        <v>294.6</v>
       </c>
     </row>
     <row r="41">
@@ -1759,28 +1759,28 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
       <c r="F41" t="n">
-        <v>11.82</v>
+        <v>11.6</v>
       </c>
       <c r="G41" t="n">
-        <v>350.2</v>
+        <v>337.6</v>
       </c>
       <c r="H41" t="n">
-        <v>76.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-32.93</v>
+        <v>34.27</v>
       </c>
       <c r="K41" t="n">
-        <v>-280.6</v>
+        <v>-479.14</v>
       </c>
       <c r="L41" t="n">
-        <v>282.53</v>
+        <v>480.37</v>
       </c>
     </row>
     <row r="42">
@@ -1801,28 +1801,28 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.44</v>
+        <v>5.28</v>
       </c>
       <c r="F42" t="n">
-        <v>12.09</v>
+        <v>11.69</v>
       </c>
       <c r="G42" t="n">
-        <v>330.3</v>
+        <v>347.6</v>
       </c>
       <c r="H42" t="n">
-        <v>75.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-90.12</v>
+        <v>-445.42</v>
       </c>
       <c r="K42" t="n">
-        <v>266.71</v>
+        <v>-403.38</v>
       </c>
       <c r="L42" t="n">
-        <v>281.52</v>
+        <v>600.9299999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1843,28 +1843,28 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="F43" t="n">
-        <v>11.97</v>
+        <v>12.61</v>
       </c>
       <c r="G43" t="n">
-        <v>347.8</v>
+        <v>356</v>
       </c>
       <c r="H43" t="n">
-        <v>64.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-112.16</v>
+        <v>194.77</v>
       </c>
       <c r="K43" t="n">
-        <v>237.15</v>
+        <v>-254.12</v>
       </c>
       <c r="L43" t="n">
-        <v>262.33</v>
+        <v>320.18</v>
       </c>
     </row>
     <row r="44">
@@ -1885,28 +1885,28 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.37</v>
+        <v>4.44</v>
       </c>
       <c r="F44" t="n">
-        <v>11.14</v>
+        <v>11.34</v>
       </c>
       <c r="G44" t="n">
-        <v>340.7</v>
+        <v>354.9</v>
       </c>
       <c r="H44" t="n">
-        <v>76.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>61.04</v>
+        <v>-67.41</v>
       </c>
       <c r="K44" t="n">
-        <v>-53.98</v>
+        <v>34.29</v>
       </c>
       <c r="L44" t="n">
-        <v>81.48999999999999</v>
+        <v>75.63</v>
       </c>
     </row>
     <row r="45">
@@ -1927,28 +1927,28 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.33</v>
+        <v>4.83</v>
       </c>
       <c r="F45" t="n">
-        <v>11.6</v>
+        <v>7.56</v>
       </c>
       <c r="G45" t="n">
-        <v>344.4</v>
+        <v>342.1</v>
       </c>
       <c r="H45" t="n">
-        <v>74.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I45" t="n">
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>75.40000000000001</v>
+        <v>-68.25</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.34</v>
+        <v>-38.54</v>
       </c>
       <c r="L45" t="n">
-        <v>75.76000000000001</v>
+        <v>78.39</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>4.73</v>
       </c>
       <c r="F46" t="n">
-        <v>11.42</v>
+        <v>12.96</v>
       </c>
       <c r="G46" t="n">
-        <v>345.6</v>
+        <v>0.3</v>
       </c>
       <c r="H46" t="n">
-        <v>70.7</v>
+        <v>79.2</v>
       </c>
       <c r="I46" t="n">
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>73.93000000000001</v>
+        <v>105.24</v>
       </c>
       <c r="K46" t="n">
-        <v>70.95999999999999</v>
+        <v>-8.48</v>
       </c>
       <c r="L46" t="n">
-        <v>102.47</v>
+        <v>105.58</v>
       </c>
     </row>
     <row r="47">
@@ -2011,28 +2011,28 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.62</v>
+        <v>4.53</v>
       </c>
       <c r="F47" t="n">
-        <v>11.63</v>
+        <v>10.99</v>
       </c>
       <c r="G47" t="n">
-        <v>337.4</v>
+        <v>354</v>
       </c>
       <c r="H47" t="n">
-        <v>73.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="I47" t="n">
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-78.88</v>
+        <v>83.39</v>
       </c>
       <c r="K47" t="n">
-        <v>24.76</v>
+        <v>-8.74</v>
       </c>
       <c r="L47" t="n">
-        <v>82.68000000000001</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="48">
@@ -2053,28 +2053,28 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.33</v>
+        <v>4.85</v>
       </c>
       <c r="F48" t="n">
-        <v>11.51</v>
+        <v>10.26</v>
       </c>
       <c r="G48" t="n">
-        <v>348.3</v>
+        <v>349</v>
       </c>
       <c r="H48" t="n">
-        <v>76.5</v>
+        <v>68</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-57.15</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-106.13</v>
+        <v>-125.59</v>
       </c>
       <c r="L48" t="n">
-        <v>120.54</v>
+        <v>125.92</v>
       </c>
     </row>
     <row r="49">
@@ -2095,28 +2095,28 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.1</v>
+        <v>4.56</v>
       </c>
       <c r="F49" t="n">
-        <v>12</v>
+        <v>11.41</v>
       </c>
       <c r="G49" t="n">
-        <v>337.6</v>
+        <v>348.2</v>
       </c>
       <c r="H49" t="n">
-        <v>65.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-22.13</v>
+        <v>-99.06</v>
       </c>
       <c r="K49" t="n">
-        <v>-79.92</v>
+        <v>21.25</v>
       </c>
       <c r="L49" t="n">
-        <v>82.92</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="50">
@@ -2137,28 +2137,28 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.81</v>
+        <v>5.16</v>
       </c>
       <c r="F50" t="n">
-        <v>11.36</v>
+        <v>10.52</v>
       </c>
       <c r="G50" t="n">
-        <v>354.1</v>
+        <v>358.7</v>
       </c>
       <c r="H50" t="n">
-        <v>74</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>141.85</v>
+        <v>119.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-13.64</v>
+        <v>-59.76</v>
       </c>
       <c r="L50" t="n">
-        <v>142.51</v>
+        <v>133.43</v>
       </c>
     </row>
     <row r="51">
@@ -2179,28 +2179,28 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.29</v>
+        <v>5.33</v>
       </c>
       <c r="F51" t="n">
-        <v>11.62</v>
+        <v>13.57</v>
       </c>
       <c r="G51" t="n">
-        <v>358.9</v>
+        <v>341.2</v>
       </c>
       <c r="H51" t="n">
-        <v>63.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-154.08</v>
+        <v>-65.48</v>
       </c>
       <c r="K51" t="n">
-        <v>-19.3</v>
+        <v>136.86</v>
       </c>
       <c r="L51" t="n">
-        <v>155.28</v>
+        <v>151.72</v>
       </c>
     </row>
     <row r="52">
@@ -2221,28 +2221,28 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.12</v>
+        <v>4.71</v>
       </c>
       <c r="F52" t="n">
-        <v>11.59</v>
+        <v>10.29</v>
       </c>
       <c r="G52" t="n">
-        <v>356.7</v>
+        <v>347.9</v>
       </c>
       <c r="H52" t="n">
-        <v>69.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I52" t="n">
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-40.04</v>
+        <v>-40.5</v>
       </c>
       <c r="K52" t="n">
-        <v>135.22</v>
+        <v>-110.8</v>
       </c>
       <c r="L52" t="n">
-        <v>141.02</v>
+        <v>117.97</v>
       </c>
     </row>
     <row r="53">
@@ -2263,28 +2263,28 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.17</v>
+        <v>5.06</v>
       </c>
       <c r="F53" t="n">
-        <v>11.95</v>
+        <v>13.35</v>
       </c>
       <c r="G53" t="n">
-        <v>358.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>78.8</v>
+        <v>74.5</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>324.29</v>
+        <v>138.79</v>
       </c>
       <c r="K53" t="n">
-        <v>91.95999999999999</v>
+        <v>113.19</v>
       </c>
       <c r="L53" t="n">
-        <v>337.08</v>
+        <v>179.1</v>
       </c>
     </row>
     <row r="54">
@@ -2305,28 +2305,28 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.68</v>
+        <v>5.33</v>
       </c>
       <c r="F54" t="n">
-        <v>11.29</v>
+        <v>13.57</v>
       </c>
       <c r="G54" t="n">
-        <v>357.9</v>
+        <v>344</v>
       </c>
       <c r="H54" t="n">
-        <v>61.7</v>
+        <v>68.8</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-273.77</v>
+        <v>-243.07</v>
       </c>
       <c r="K54" t="n">
-        <v>-102.45</v>
+        <v>12.68</v>
       </c>
       <c r="L54" t="n">
-        <v>292.31</v>
+        <v>243.4</v>
       </c>
     </row>
     <row r="55">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.07</v>
+        <v>5.54</v>
       </c>
       <c r="F55" t="n">
-        <v>11.71</v>
+        <v>13.57</v>
       </c>
       <c r="G55" t="n">
-        <v>350.5</v>
+        <v>355.9</v>
       </c>
       <c r="H55" t="n">
-        <v>81.7</v>
+        <v>73</v>
       </c>
       <c r="I55" t="n">
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-171.25</v>
+        <v>-263.28</v>
       </c>
       <c r="K55" t="n">
-        <v>-151.16</v>
+        <v>8.41</v>
       </c>
       <c r="L55" t="n">
-        <v>228.42</v>
+        <v>263.42</v>
       </c>
     </row>
     <row r="56">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.86</v>
+        <v>5.21</v>
       </c>
       <c r="F56" t="n">
-        <v>12.12</v>
+        <v>13.57</v>
       </c>
       <c r="G56" t="n">
-        <v>351.6</v>
+        <v>356.1</v>
       </c>
       <c r="H56" t="n">
-        <v>78.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-328.06</v>
+        <v>-341.35</v>
       </c>
       <c r="K56" t="n">
-        <v>-219.05</v>
+        <v>-156.16</v>
       </c>
       <c r="L56" t="n">
-        <v>394.46</v>
+        <v>375.37</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>5.16</v>
       </c>
       <c r="F57" t="n">
-        <v>12.68</v>
+        <v>13.4</v>
       </c>
       <c r="G57" t="n">
-        <v>343.8</v>
+        <v>7.2</v>
       </c>
       <c r="H57" t="n">
-        <v>74.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-243.11</v>
+        <v>-231.72</v>
       </c>
       <c r="K57" t="n">
-        <v>-409.54</v>
+        <v>-402.57</v>
       </c>
       <c r="L57" t="n">
-        <v>476.26</v>
+        <v>464.49</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>5.28</v>
       </c>
       <c r="F58" t="n">
-        <v>11.83</v>
+        <v>10.9</v>
       </c>
       <c r="G58" t="n">
-        <v>354.7</v>
+        <v>350.4</v>
       </c>
       <c r="H58" t="n">
-        <v>69.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>307.03</v>
+        <v>303.37</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.210000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="L58" t="n">
-        <v>307.14</v>
+        <v>311.39</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>4.86</v>
       </c>
       <c r="F59" t="n">
-        <v>11.88</v>
+        <v>12.86</v>
       </c>
       <c r="G59" t="n">
-        <v>352</v>
+        <v>351.3</v>
       </c>
       <c r="H59" t="n">
-        <v>69.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I59" t="n">
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-58.96</v>
+        <v>-69.38</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.78</v>
+        <v>-11.45</v>
       </c>
       <c r="L59" t="n">
-        <v>60.32</v>
+        <v>70.31999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>5.65</v>
       </c>
       <c r="F60" t="n">
-        <v>11.06</v>
+        <v>10.77</v>
       </c>
       <c r="G60" t="n">
-        <v>332.6</v>
+        <v>334.8</v>
       </c>
       <c r="H60" t="n">
-        <v>66.2</v>
+        <v>65.3</v>
       </c>
       <c r="I60" t="n">
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-58.68</v>
+        <v>-63.11</v>
       </c>
       <c r="K60" t="n">
-        <v>-31.5</v>
+        <v>-31.06</v>
       </c>
       <c r="L60" t="n">
-        <v>66.59999999999999</v>
+        <v>70.34</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>5.28</v>
       </c>
       <c r="F61" t="n">
-        <v>11.93</v>
+        <v>12.51</v>
       </c>
       <c r="G61" t="n">
-        <v>336.3</v>
+        <v>352.4</v>
       </c>
       <c r="H61" t="n">
-        <v>78.5</v>
+        <v>67.2</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-73.05</v>
+        <v>-78.56999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>32.54</v>
+        <v>37.14</v>
       </c>
       <c r="L61" t="n">
-        <v>79.97</v>
+        <v>86.91</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>5.46</v>
       </c>
       <c r="F62" t="n">
-        <v>11.89</v>
+        <v>9.67</v>
       </c>
       <c r="G62" t="n">
-        <v>357.4</v>
+        <v>351.5</v>
       </c>
       <c r="H62" t="n">
-        <v>64.2</v>
+        <v>77.8</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-167.14</v>
+        <v>-157.84</v>
       </c>
       <c r="K62" t="n">
-        <v>-22.87</v>
+        <v>-18.35</v>
       </c>
       <c r="L62" t="n">
-        <v>168.7</v>
+        <v>158.91</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>4.78</v>
       </c>
       <c r="F63" t="n">
-        <v>11.89</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>357.3</v>
+        <v>351.5</v>
       </c>
       <c r="H63" t="n">
-        <v>79.8</v>
+        <v>77.7</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-77.31999999999999</v>
+        <v>-76.79000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-57.67</v>
+        <v>-51.65</v>
       </c>
       <c r="L63" t="n">
-        <v>96.45</v>
+        <v>92.54000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>5.68</v>
       </c>
       <c r="F64" t="n">
-        <v>11.45</v>
+        <v>11.74</v>
       </c>
       <c r="G64" t="n">
-        <v>347.1</v>
+        <v>342.6</v>
       </c>
       <c r="H64" t="n">
-        <v>68.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>77.40000000000001</v>
+        <v>84.41</v>
       </c>
       <c r="K64" t="n">
-        <v>-51.74</v>
+        <v>-50.74</v>
       </c>
       <c r="L64" t="n">
-        <v>93.09999999999999</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>4.98</v>
       </c>
       <c r="F65" t="n">
-        <v>11.23</v>
+        <v>13.57</v>
       </c>
       <c r="G65" t="n">
-        <v>342.1</v>
+        <v>338.2</v>
       </c>
       <c r="H65" t="n">
-        <v>75.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I65" t="n">
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>65.45999999999999</v>
+        <v>84.05</v>
       </c>
       <c r="K65" t="n">
-        <v>-83.26000000000001</v>
+        <v>-77.34999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>105.91</v>
+        <v>114.23</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>5.74</v>
       </c>
       <c r="F66" t="n">
-        <v>11.24</v>
+        <v>13.57</v>
       </c>
       <c r="G66" t="n">
-        <v>353.8</v>
+        <v>338.6</v>
       </c>
       <c r="H66" t="n">
-        <v>74.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-153.53</v>
+        <v>-160.05</v>
       </c>
       <c r="K66" t="n">
-        <v>76.34999999999999</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>171.47</v>
+        <v>187.49</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>4.98</v>
       </c>
       <c r="F67" t="n">
-        <v>11.98</v>
+        <v>11.73</v>
       </c>
       <c r="G67" t="n">
-        <v>340.1</v>
+        <v>353.3</v>
       </c>
       <c r="H67" t="n">
-        <v>76.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-145.65</v>
+        <v>-153.91</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.96</v>
+        <v>24.9</v>
       </c>
       <c r="L67" t="n">
-        <v>145.7</v>
+        <v>155.91</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>5.84</v>
       </c>
       <c r="F68" t="n">
-        <v>11.65</v>
+        <v>11.6</v>
       </c>
       <c r="G68" t="n">
-        <v>342.1</v>
+        <v>346.6</v>
       </c>
       <c r="H68" t="n">
-        <v>66.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I68" t="n">
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>101.27</v>
+        <v>128.6</v>
       </c>
       <c r="K68" t="n">
-        <v>-172.33</v>
+        <v>-158.4</v>
       </c>
       <c r="L68" t="n">
-        <v>199.89</v>
+        <v>204.03</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>5.34</v>
       </c>
       <c r="F69" t="n">
-        <v>11.71</v>
+        <v>12.54</v>
       </c>
       <c r="G69" t="n">
-        <v>347.8</v>
+        <v>355.3</v>
       </c>
       <c r="H69" t="n">
-        <v>75.5</v>
+        <v>72.3</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>172.87</v>
+        <v>139.93</v>
       </c>
       <c r="K69" t="n">
-        <v>-87.88</v>
+        <v>243.59</v>
       </c>
       <c r="L69" t="n">
-        <v>193.93</v>
+        <v>280.92</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.73</v>
+        <v>5.63</v>
       </c>
       <c r="F70" t="n">
-        <v>11.24</v>
+        <v>11.63</v>
       </c>
       <c r="G70" t="n">
-        <v>347.9</v>
+        <v>344.4</v>
       </c>
       <c r="H70" t="n">
-        <v>76.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-165.88</v>
+        <v>-228.16</v>
       </c>
       <c r="K70" t="n">
-        <v>-133.13</v>
+        <v>43.37</v>
       </c>
       <c r="L70" t="n">
-        <v>212.7</v>
+        <v>232.25</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.33</v>
+        <v>5.6</v>
       </c>
       <c r="F71" t="n">
-        <v>12.48</v>
+        <v>11.63</v>
       </c>
       <c r="G71" t="n">
-        <v>342</v>
+        <v>354.1</v>
       </c>
       <c r="H71" t="n">
-        <v>68.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-256.41</v>
+        <v>427.96</v>
       </c>
       <c r="K71" t="n">
-        <v>378.24</v>
+        <v>54.16</v>
       </c>
       <c r="L71" t="n">
-        <v>456.95</v>
+        <v>431.37</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.33</v>
+        <v>6.28</v>
       </c>
       <c r="F72" t="n">
-        <v>12.13</v>
+        <v>13.57</v>
       </c>
       <c r="G72" t="n">
-        <v>354.2</v>
+        <v>1.6</v>
       </c>
       <c r="H72" t="n">
-        <v>74.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-120.37</v>
+        <v>504.63</v>
       </c>
       <c r="K72" t="n">
-        <v>427.33</v>
+        <v>-80.11</v>
       </c>
       <c r="L72" t="n">
-        <v>443.96</v>
+        <v>510.95</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.2</v>
+        <v>5.91</v>
       </c>
       <c r="F73" t="n">
-        <v>12.46</v>
+        <v>13.28</v>
       </c>
       <c r="G73" t="n">
-        <v>347.1</v>
+        <v>2.9</v>
       </c>
       <c r="H73" t="n">
-        <v>77.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.53</v>
+        <v>39.01</v>
       </c>
       <c r="K73" t="n">
-        <v>-291.09</v>
+        <v>-369.37</v>
       </c>
       <c r="L73" t="n">
-        <v>291.16</v>
+        <v>371.43</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>5.85</v>
       </c>
       <c r="F74" t="n">
-        <v>12.3</v>
+        <v>13.57</v>
       </c>
       <c r="G74" t="n">
-        <v>343.1</v>
+        <v>359.8</v>
       </c>
       <c r="H74" t="n">
-        <v>76.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I74" t="n">
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-61.87</v>
+        <v>-65.87</v>
       </c>
       <c r="K74" t="n">
-        <v>43.97</v>
+        <v>51.05</v>
       </c>
       <c r="L74" t="n">
-        <v>75.91</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>5.71</v>
       </c>
       <c r="F75" t="n">
-        <v>11.66</v>
+        <v>13.46</v>
       </c>
       <c r="G75" t="n">
-        <v>357.8</v>
+        <v>346.9</v>
       </c>
       <c r="H75" t="n">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-85.75</v>
+        <v>-97.83</v>
       </c>
       <c r="K75" t="n">
-        <v>18.5</v>
+        <v>22.96</v>
       </c>
       <c r="L75" t="n">
-        <v>87.72</v>
+        <v>100.49</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>5.8</v>
       </c>
       <c r="F76" t="n">
-        <v>10.96</v>
+        <v>12.86</v>
       </c>
       <c r="G76" t="n">
-        <v>4</v>
+        <v>332.9</v>
       </c>
       <c r="H76" t="n">
-        <v>70.2</v>
+        <v>81</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>26.49</v>
+        <v>23.25</v>
       </c>
       <c r="K76" t="n">
-        <v>61.66</v>
+        <v>68.09</v>
       </c>
       <c r="L76" t="n">
-        <v>67.11</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>5.21</v>
       </c>
       <c r="F77" t="n">
-        <v>12.49</v>
+        <v>13.14</v>
       </c>
       <c r="G77" t="n">
-        <v>335.3</v>
+        <v>3.4</v>
       </c>
       <c r="H77" t="n">
-        <v>73.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>1.48</v>
+        <v>11.46</v>
       </c>
       <c r="K77" t="n">
-        <v>29.92</v>
+        <v>62.02</v>
       </c>
       <c r="L77" t="n">
-        <v>29.95</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>6.15</v>
       </c>
       <c r="F78" t="n">
-        <v>11.99</v>
+        <v>13.57</v>
       </c>
       <c r="G78" t="n">
-        <v>356.5</v>
+        <v>353.4</v>
       </c>
       <c r="H78" t="n">
-        <v>70</v>
+        <v>77.3</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>98.27</v>
+        <v>106.52</v>
       </c>
       <c r="K78" t="n">
-        <v>33.59</v>
+        <v>44.52</v>
       </c>
       <c r="L78" t="n">
-        <v>103.85</v>
+        <v>115.45</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>5.18</v>
       </c>
       <c r="F79" t="n">
-        <v>12.05</v>
+        <v>13.15</v>
       </c>
       <c r="G79" t="n">
-        <v>352.8</v>
+        <v>354.7</v>
       </c>
       <c r="H79" t="n">
-        <v>73.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>21.53</v>
+        <v>21.49</v>
       </c>
       <c r="K79" t="n">
-        <v>-44.96</v>
+        <v>-31.95</v>
       </c>
       <c r="L79" t="n">
-        <v>49.85</v>
+        <v>38.51</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>5.62</v>
       </c>
       <c r="F80" t="n">
-        <v>11.82</v>
+        <v>13.57</v>
       </c>
       <c r="G80" t="n">
-        <v>347.1</v>
+        <v>350.1</v>
       </c>
       <c r="H80" t="n">
-        <v>76.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>142.5</v>
+        <v>139.77</v>
       </c>
       <c r="K80" t="n">
-        <v>56.86</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>153.43</v>
+        <v>171.74</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>5.97</v>
       </c>
       <c r="F81" t="n">
-        <v>12.45</v>
+        <v>13.57</v>
       </c>
       <c r="G81" t="n">
-        <v>354.9</v>
+        <v>2.7</v>
       </c>
       <c r="H81" t="n">
-        <v>81.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="I81" t="n">
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-67.55</v>
+        <v>-62.34</v>
       </c>
       <c r="K81" t="n">
-        <v>180.39</v>
+        <v>207.46</v>
       </c>
       <c r="L81" t="n">
-        <v>192.62</v>
+        <v>216.63</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>4.85</v>
       </c>
       <c r="F82" t="n">
-        <v>10.96</v>
+        <v>13.35</v>
       </c>
       <c r="G82" t="n">
-        <v>354.2</v>
+        <v>332.9</v>
       </c>
       <c r="H82" t="n">
-        <v>78</v>
+        <v>76.2</v>
       </c>
       <c r="I82" t="n">
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-24.13</v>
+        <v>-45.76</v>
       </c>
       <c r="K82" t="n">
-        <v>113.3</v>
+        <v>135.36</v>
       </c>
       <c r="L82" t="n">
-        <v>115.84</v>
+        <v>142.88</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>5.76</v>
       </c>
       <c r="F83" t="n">
-        <v>12.02</v>
+        <v>13.57</v>
       </c>
       <c r="G83" t="n">
-        <v>348.7</v>
+        <v>354</v>
       </c>
       <c r="H83" t="n">
-        <v>75.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>149.09</v>
+        <v>190.98</v>
       </c>
       <c r="K83" t="n">
-        <v>-159.92</v>
+        <v>-144.15</v>
       </c>
       <c r="L83" t="n">
-        <v>218.64</v>
+        <v>239.27</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>5.76</v>
       </c>
       <c r="F84" t="n">
-        <v>12.42</v>
+        <v>13.57</v>
       </c>
       <c r="G84" t="n">
-        <v>354.8</v>
+        <v>2</v>
       </c>
       <c r="H84" t="n">
-        <v>72.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I84" t="n">
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>162.81</v>
+        <v>171.49</v>
       </c>
       <c r="K84" t="n">
-        <v>226.09</v>
+        <v>263.25</v>
       </c>
       <c r="L84" t="n">
-        <v>278.61</v>
+        <v>314.18</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>5.5</v>
       </c>
       <c r="F85" t="n">
-        <v>12.38</v>
+        <v>13.21</v>
       </c>
       <c r="G85" t="n">
-        <v>327.8</v>
+        <v>1.3</v>
       </c>
       <c r="H85" t="n">
-        <v>78.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.45</v>
+        <v>48.6</v>
       </c>
       <c r="K85" t="n">
-        <v>-191.78</v>
+        <v>-203.16</v>
       </c>
       <c r="L85" t="n">
-        <v>191.86</v>
+        <v>208.9</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>6.15</v>
       </c>
       <c r="F86" t="n">
-        <v>12.09</v>
+        <v>13.57</v>
       </c>
       <c r="G86" t="n">
-        <v>358.7</v>
+        <v>355.6</v>
       </c>
       <c r="H86" t="n">
-        <v>71.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-338.79</v>
+        <v>-424.1</v>
       </c>
       <c r="K86" t="n">
-        <v>-297.82</v>
+        <v>-301.89</v>
       </c>
       <c r="L86" t="n">
-        <v>451.09</v>
+        <v>520.5700000000001</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>6.08</v>
       </c>
       <c r="F87" t="n">
-        <v>11.67</v>
+        <v>13.57</v>
       </c>
       <c r="G87" t="n">
-        <v>334.1</v>
+        <v>347.1</v>
       </c>
       <c r="H87" t="n">
-        <v>75.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>282.88</v>
+        <v>330.11</v>
       </c>
       <c r="K87" t="n">
-        <v>-403.53</v>
+        <v>-399.34</v>
       </c>
       <c r="L87" t="n">
-        <v>492.81</v>
+        <v>518.11</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>6</v>
       </c>
       <c r="F88" t="n">
-        <v>12</v>
+        <v>12.45</v>
       </c>
       <c r="G88" t="n">
-        <v>349.8</v>
+        <v>353.7</v>
       </c>
       <c r="H88" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-581.8</v>
+        <v>-617.97</v>
       </c>
       <c r="K88" t="n">
-        <v>153.74</v>
+        <v>205.73</v>
       </c>
       <c r="L88" t="n">
-        <v>601.77</v>
+        <v>651.3200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>68.31999999999999</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>30.98</v>
+        <v>33.59</v>
       </c>
       <c r="L14" t="n">
-        <v>75.02</v>
+        <v>81.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-105.51</v>
+        <v>-112.83</v>
       </c>
       <c r="K15" t="n">
-        <v>-73.62</v>
+        <v>-78.73</v>
       </c>
       <c r="L15" t="n">
-        <v>128.65</v>
+        <v>137.58</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-28.23</v>
+        <v>-30.16</v>
       </c>
       <c r="K16" t="n">
-        <v>81.98999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>86.72</v>
+        <v>92.64</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>112.2</v>
+        <v>123.34</v>
       </c>
       <c r="K17" t="n">
-        <v>14.82</v>
+        <v>16.29</v>
       </c>
       <c r="L17" t="n">
-        <v>113.18</v>
+        <v>124.41</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>97.70999999999999</v>
+        <v>110.14</v>
       </c>
       <c r="K18" t="n">
-        <v>85.34999999999999</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>129.74</v>
+        <v>146.24</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.49</v>
+        <v>-11.52</v>
       </c>
       <c r="K19" t="n">
-        <v>103.33</v>
+        <v>113.44</v>
       </c>
       <c r="L19" t="n">
-        <v>103.87</v>
+        <v>114.03</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-144.96</v>
+        <v>-157.78</v>
       </c>
       <c r="K20" t="n">
-        <v>44.17</v>
+        <v>48.08</v>
       </c>
       <c r="L20" t="n">
-        <v>151.54</v>
+        <v>164.94</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.74</v>
+        <v>-22.42</v>
       </c>
       <c r="K21" t="n">
-        <v>173.04</v>
+        <v>196.52</v>
       </c>
       <c r="L21" t="n">
-        <v>174.16</v>
+        <v>197.79</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-70.47</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>161.61</v>
+        <v>183.56</v>
       </c>
       <c r="L22" t="n">
-        <v>176.3</v>
+        <v>200.25</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>245.44</v>
+        <v>274.43</v>
       </c>
       <c r="K23" t="n">
-        <v>88.87</v>
+        <v>99.36</v>
       </c>
       <c r="L23" t="n">
-        <v>261.04</v>
+        <v>291.86</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>223.61</v>
+        <v>256.55</v>
       </c>
       <c r="K24" t="n">
-        <v>-34.89</v>
+        <v>-40.03</v>
       </c>
       <c r="L24" t="n">
-        <v>226.32</v>
+        <v>259.65</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-49.84</v>
+        <v>-54.89</v>
       </c>
       <c r="K25" t="n">
-        <v>117.75</v>
+        <v>129.68</v>
       </c>
       <c r="L25" t="n">
-        <v>127.86</v>
+        <v>140.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-309.18</v>
+        <v>-341.81</v>
       </c>
       <c r="K26" t="n">
-        <v>272.96</v>
+        <v>301.77</v>
       </c>
       <c r="L26" t="n">
-        <v>412.44</v>
+        <v>455.95</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>138.78</v>
+        <v>160.62</v>
       </c>
       <c r="K27" t="n">
-        <v>323.6</v>
+        <v>374.53</v>
       </c>
       <c r="L27" t="n">
-        <v>352.11</v>
+        <v>407.51</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-523.83</v>
+        <v>-582.21</v>
       </c>
       <c r="K28" t="n">
-        <v>-13.15</v>
+        <v>-14.62</v>
       </c>
       <c r="L28" t="n">
-        <v>523.99</v>
+        <v>582.39</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>33.18</v>
+        <v>36.49</v>
       </c>
       <c r="K29" t="n">
-        <v>-61.45</v>
+        <v>-67.59</v>
       </c>
       <c r="L29" t="n">
-        <v>69.83</v>
+        <v>76.81</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.05</v>
+        <v>-17.03</v>
       </c>
       <c r="K30" t="n">
-        <v>94.48999999999999</v>
+        <v>106.92</v>
       </c>
       <c r="L30" t="n">
-        <v>95.68000000000001</v>
+        <v>108.27</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>57.43</v>
+        <v>61.25</v>
       </c>
       <c r="K31" t="n">
-        <v>69.72</v>
+        <v>74.36</v>
       </c>
       <c r="L31" t="n">
-        <v>90.31999999999999</v>
+        <v>96.34</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-50.36</v>
+        <v>-54.82</v>
       </c>
       <c r="K32" t="n">
-        <v>-32.82</v>
+        <v>-35.73</v>
       </c>
       <c r="L32" t="n">
-        <v>60.11</v>
+        <v>65.44</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-86.65000000000001</v>
+        <v>-96.48999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>7.04</v>
+        <v>7.84</v>
       </c>
       <c r="L33" t="n">
-        <v>86.93000000000001</v>
+        <v>96.81</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-48.14</v>
+        <v>-54.43</v>
       </c>
       <c r="K34" t="n">
-        <v>-61.27</v>
+        <v>-69.28</v>
       </c>
       <c r="L34" t="n">
-        <v>77.92</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-118.12</v>
+        <v>-126.39</v>
       </c>
       <c r="K35" t="n">
-        <v>33.77</v>
+        <v>36.13</v>
       </c>
       <c r="L35" t="n">
-        <v>122.85</v>
+        <v>131.45</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>176.05</v>
+        <v>199.67</v>
       </c>
       <c r="K36" t="n">
-        <v>179.06</v>
+        <v>203.08</v>
       </c>
       <c r="L36" t="n">
-        <v>251.11</v>
+        <v>284.8</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-161.02</v>
+        <v>-180.07</v>
       </c>
       <c r="K37" t="n">
-        <v>195.92</v>
+        <v>219.1</v>
       </c>
       <c r="L37" t="n">
-        <v>253.59</v>
+        <v>283.6</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-197.78</v>
+        <v>-227.17</v>
       </c>
       <c r="K38" t="n">
-        <v>-10.9</v>
+        <v>-12.52</v>
       </c>
       <c r="L38" t="n">
-        <v>198.08</v>
+        <v>227.51</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>193.77</v>
+        <v>209.73</v>
       </c>
       <c r="K39" t="n">
-        <v>-44.94</v>
+        <v>-48.64</v>
       </c>
       <c r="L39" t="n">
-        <v>198.91</v>
+        <v>215.3</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-188.74</v>
+        <v>-216.99</v>
       </c>
       <c r="K40" t="n">
-        <v>226.2</v>
+        <v>260.06</v>
       </c>
       <c r="L40" t="n">
-        <v>294.6</v>
+        <v>338.7</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>34.27</v>
+        <v>39.72</v>
       </c>
       <c r="K41" t="n">
-        <v>-479.14</v>
+        <v>-555.3099999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>480.37</v>
+        <v>556.73</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-445.42</v>
+        <v>-516.95</v>
       </c>
       <c r="K42" t="n">
-        <v>-403.38</v>
+        <v>-468.16</v>
       </c>
       <c r="L42" t="n">
-        <v>600.9299999999999</v>
+        <v>697.4299999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>194.77</v>
+        <v>209.48</v>
       </c>
       <c r="K43" t="n">
-        <v>-254.12</v>
+        <v>-273.31</v>
       </c>
       <c r="L43" t="n">
-        <v>320.18</v>
+        <v>344.36</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-67.41</v>
+        <v>-75.26000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>34.29</v>
+        <v>38.29</v>
       </c>
       <c r="L44" t="n">
-        <v>75.63</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-68.25</v>
+        <v>-77.09999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-38.54</v>
+        <v>-43.54</v>
       </c>
       <c r="L45" t="n">
-        <v>78.39</v>
+        <v>88.54000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>105.24</v>
+        <v>115.71</v>
       </c>
       <c r="K46" t="n">
-        <v>-8.48</v>
+        <v>-9.32</v>
       </c>
       <c r="L46" t="n">
-        <v>105.58</v>
+        <v>116.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>83.39</v>
+        <v>87.58</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.74</v>
+        <v>-9.18</v>
       </c>
       <c r="L47" t="n">
-        <v>83.84</v>
+        <v>88.06</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-9.109999999999999</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-125.59</v>
+        <v>-136.01</v>
       </c>
       <c r="L48" t="n">
-        <v>125.92</v>
+        <v>136.37</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>-99.06</v>
+        <v>-112.03</v>
       </c>
       <c r="K49" t="n">
-        <v>21.25</v>
+        <v>24.04</v>
       </c>
       <c r="L49" t="n">
-        <v>101.31</v>
+        <v>114.58</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>119.3</v>
+        <v>133.47</v>
       </c>
       <c r="K50" t="n">
-        <v>-59.76</v>
+        <v>-66.84999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>133.43</v>
+        <v>149.28</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-65.48</v>
+        <v>-74.23</v>
       </c>
       <c r="K51" t="n">
-        <v>136.86</v>
+        <v>155.15</v>
       </c>
       <c r="L51" t="n">
-        <v>151.72</v>
+        <v>171.99</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-40.5</v>
+        <v>-44.74</v>
       </c>
       <c r="K52" t="n">
-        <v>-110.8</v>
+        <v>-122.39</v>
       </c>
       <c r="L52" t="n">
-        <v>117.97</v>
+        <v>130.31</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>138.79</v>
+        <v>152.81</v>
       </c>
       <c r="K53" t="n">
-        <v>113.19</v>
+        <v>124.62</v>
       </c>
       <c r="L53" t="n">
-        <v>179.1</v>
+        <v>197.18</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-243.07</v>
+        <v>-279.35</v>
       </c>
       <c r="K54" t="n">
-        <v>12.68</v>
+        <v>14.58</v>
       </c>
       <c r="L54" t="n">
-        <v>243.4</v>
+        <v>279.73</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-263.28</v>
+        <v>-298.71</v>
       </c>
       <c r="K55" t="n">
-        <v>8.41</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>263.42</v>
+        <v>298.86</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>-341.35</v>
+        <v>-396.02</v>
       </c>
       <c r="K56" t="n">
-        <v>-156.16</v>
+        <v>-181.17</v>
       </c>
       <c r="L56" t="n">
-        <v>375.37</v>
+        <v>435.5</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-231.72</v>
+        <v>-257.66</v>
       </c>
       <c r="K57" t="n">
-        <v>-402.57</v>
+        <v>-447.63</v>
       </c>
       <c r="L57" t="n">
-        <v>464.49</v>
+        <v>516.49</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>303.37</v>
+        <v>326.92</v>
       </c>
       <c r="K58" t="n">
-        <v>70.2</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>311.39</v>
+        <v>335.56</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-69.38</v>
+        <v>-77.31999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-11.45</v>
+        <v>-12.75</v>
       </c>
       <c r="L59" t="n">
-        <v>70.31999999999999</v>
+        <v>78.37</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-63.11</v>
+        <v>-65.97</v>
       </c>
       <c r="K60" t="n">
-        <v>-31.06</v>
+        <v>-32.47</v>
       </c>
       <c r="L60" t="n">
-        <v>70.34</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-78.56999999999999</v>
+        <v>-83.61</v>
       </c>
       <c r="K61" t="n">
-        <v>37.14</v>
+        <v>39.52</v>
       </c>
       <c r="L61" t="n">
-        <v>86.91</v>
+        <v>92.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-157.84</v>
+        <v>-165.16</v>
       </c>
       <c r="K62" t="n">
-        <v>-18.35</v>
+        <v>-19.2</v>
       </c>
       <c r="L62" t="n">
-        <v>158.91</v>
+        <v>166.28</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-76.79000000000001</v>
+        <v>-80.56</v>
       </c>
       <c r="K63" t="n">
-        <v>-51.65</v>
+        <v>-54.19</v>
       </c>
       <c r="L63" t="n">
-        <v>92.54000000000001</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>84.41</v>
+        <v>93.34</v>
       </c>
       <c r="K64" t="n">
-        <v>-50.74</v>
+        <v>-56.1</v>
       </c>
       <c r="L64" t="n">
-        <v>98.48999999999999</v>
+        <v>108.91</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>84.05</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-77.34999999999999</v>
+        <v>-81.45</v>
       </c>
       <c r="L65" t="n">
-        <v>114.23</v>
+        <v>120.29</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-160.05</v>
+        <v>-171.17</v>
       </c>
       <c r="K66" t="n">
-        <v>97.65000000000001</v>
+        <v>104.43</v>
       </c>
       <c r="L66" t="n">
-        <v>187.49</v>
+        <v>200.51</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-153.91</v>
+        <v>-172.23</v>
       </c>
       <c r="K67" t="n">
-        <v>24.9</v>
+        <v>27.86</v>
       </c>
       <c r="L67" t="n">
-        <v>155.91</v>
+        <v>174.47</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>128.6</v>
+        <v>141.85</v>
       </c>
       <c r="K68" t="n">
-        <v>-158.4</v>
+        <v>-174.72</v>
       </c>
       <c r="L68" t="n">
-        <v>204.03</v>
+        <v>225.05</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>139.93</v>
+        <v>156.47</v>
       </c>
       <c r="K69" t="n">
-        <v>243.59</v>
+        <v>272.39</v>
       </c>
       <c r="L69" t="n">
-        <v>280.92</v>
+        <v>314.13</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-228.16</v>
+        <v>-262.4</v>
       </c>
       <c r="K70" t="n">
-        <v>43.37</v>
+        <v>49.88</v>
       </c>
       <c r="L70" t="n">
-        <v>232.25</v>
+        <v>267.1</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>427.96</v>
+        <v>490.81</v>
       </c>
       <c r="K71" t="n">
-        <v>54.16</v>
+        <v>62.11</v>
       </c>
       <c r="L71" t="n">
-        <v>431.37</v>
+        <v>494.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>504.63</v>
+        <v>563.75</v>
       </c>
       <c r="K72" t="n">
-        <v>-80.11</v>
+        <v>-89.48999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>510.95</v>
+        <v>570.8099999999999</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>39.01</v>
+        <v>44.79</v>
       </c>
       <c r="K73" t="n">
-        <v>-369.37</v>
+        <v>-424.16</v>
       </c>
       <c r="L73" t="n">
-        <v>371.43</v>
+        <v>426.51</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-65.87</v>
+        <v>-74.09</v>
       </c>
       <c r="K74" t="n">
-        <v>51.05</v>
+        <v>57.42</v>
       </c>
       <c r="L74" t="n">
-        <v>83.33</v>
+        <v>93.73</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-97.83</v>
+        <v>-110.1</v>
       </c>
       <c r="K75" t="n">
-        <v>22.96</v>
+        <v>25.84</v>
       </c>
       <c r="L75" t="n">
-        <v>100.49</v>
+        <v>113.09</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>23.25</v>
+        <v>25.07</v>
       </c>
       <c r="K76" t="n">
-        <v>68.09</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>71.95</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>11.46</v>
+        <v>12.92</v>
       </c>
       <c r="K77" t="n">
-        <v>62.02</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>63.07</v>
+        <v>71.15000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>106.52</v>
+        <v>110.84</v>
       </c>
       <c r="K78" t="n">
-        <v>44.52</v>
+        <v>46.32</v>
       </c>
       <c r="L78" t="n">
-        <v>115.45</v>
+        <v>120.13</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>21.49</v>
+        <v>23.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-31.95</v>
+        <v>-35.07</v>
       </c>
       <c r="L79" t="n">
-        <v>38.51</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>17</v>
       </c>
       <c r="J80" t="n">
-        <v>139.77</v>
+        <v>156.28</v>
       </c>
       <c r="K80" t="n">
-        <v>99.79000000000001</v>
+        <v>111.58</v>
       </c>
       <c r="L80" t="n">
-        <v>171.74</v>
+        <v>192.03</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-62.34</v>
+        <v>-67.7</v>
       </c>
       <c r="K81" t="n">
-        <v>207.46</v>
+        <v>225.3</v>
       </c>
       <c r="L81" t="n">
-        <v>216.63</v>
+        <v>235.25</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-45.76</v>
+        <v>-48.23</v>
       </c>
       <c r="K82" t="n">
-        <v>135.36</v>
+        <v>142.67</v>
       </c>
       <c r="L82" t="n">
-        <v>142.88</v>
+        <v>150.6</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>190.98</v>
+        <v>210.62</v>
       </c>
       <c r="K83" t="n">
-        <v>-144.15</v>
+        <v>-158.97</v>
       </c>
       <c r="L83" t="n">
-        <v>239.27</v>
+        <v>263.88</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>171.49</v>
+        <v>183.18</v>
       </c>
       <c r="K84" t="n">
-        <v>263.25</v>
+        <v>281.2</v>
       </c>
       <c r="L84" t="n">
-        <v>314.18</v>
+        <v>335.6</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>48.6</v>
+        <v>55.88</v>
       </c>
       <c r="K85" t="n">
-        <v>-203.16</v>
+        <v>-233.59</v>
       </c>
       <c r="L85" t="n">
-        <v>208.9</v>
+        <v>240.18</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-424.1</v>
+        <v>-493.99</v>
       </c>
       <c r="K86" t="n">
-        <v>-301.89</v>
+        <v>-351.64</v>
       </c>
       <c r="L86" t="n">
-        <v>520.5700000000001</v>
+        <v>606.36</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>330.11</v>
+        <v>379.3</v>
       </c>
       <c r="K87" t="n">
-        <v>-399.34</v>
+        <v>-458.85</v>
       </c>
       <c r="L87" t="n">
-        <v>518.11</v>
+        <v>595.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-617.97</v>
+        <v>-719.4299999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>205.73</v>
+        <v>239.5</v>
       </c>
       <c r="L88" t="n">
-        <v>651.3200000000001</v>
+        <v>758.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.58</v>
+        <v>4.22</v>
       </c>
       <c r="F14" t="n">
-        <v>8.98</v>
+        <v>6.53</v>
       </c>
       <c r="G14" t="n">
-        <v>353.4</v>
+        <v>338.4</v>
       </c>
       <c r="H14" t="n">
-        <v>79.3</v>
+        <v>61.9</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>74.06999999999999</v>
+        <v>-84.26000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>33.59</v>
+        <v>-39.88</v>
       </c>
       <c r="L14" t="n">
-        <v>81.33</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:23:07</t>
+          <t>06:23:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.16</v>
+        <v>5.13</v>
       </c>
       <c r="F15" t="n">
-        <v>11.12</v>
+        <v>10.34</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1</v>
+        <v>347.8</v>
       </c>
       <c r="H15" t="n">
-        <v>74.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-112.83</v>
+        <v>33.04</v>
       </c>
       <c r="K15" t="n">
-        <v>-78.73</v>
+        <v>97.19</v>
       </c>
       <c r="L15" t="n">
-        <v>137.58</v>
+        <v>102.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:24:42</t>
+          <t>06:25:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.37</v>
+        <v>4.21</v>
       </c>
       <c r="F16" t="n">
-        <v>11.38</v>
+        <v>9.56</v>
       </c>
       <c r="G16" t="n">
-        <v>329.2</v>
+        <v>352.8</v>
       </c>
       <c r="H16" t="n">
-        <v>77.3</v>
+        <v>51</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>-30.16</v>
+        <v>29.47</v>
       </c>
       <c r="K16" t="n">
-        <v>87.59999999999999</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>92.64</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:28:38</t>
+          <t>06:28:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.8</v>
+        <v>4.35</v>
       </c>
       <c r="F17" t="n">
-        <v>10.08</v>
+        <v>9.73</v>
       </c>
       <c r="G17" t="n">
-        <v>348.4</v>
+        <v>349.6</v>
       </c>
       <c r="H17" t="n">
-        <v>68.7</v>
+        <v>14.5</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>123.34</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>16.29</v>
+        <v>115.34</v>
       </c>
       <c r="L17" t="n">
-        <v>124.41</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:30:25</t>
+          <t>06:30:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="F18" t="n">
-        <v>10.9</v>
+        <v>11.91</v>
       </c>
       <c r="G18" t="n">
-        <v>347.6</v>
+        <v>359.2</v>
       </c>
       <c r="H18" t="n">
-        <v>76.3</v>
+        <v>49</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>110.14</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>96.20999999999999</v>
+        <v>137.32</v>
       </c>
       <c r="L18" t="n">
-        <v>146.24</v>
+        <v>155.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:31:17</t>
+          <t>06:31:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.13</v>
+        <v>4.98</v>
       </c>
       <c r="F19" t="n">
-        <v>10.38</v>
+        <v>10.99</v>
       </c>
       <c r="G19" t="n">
-        <v>344.8</v>
+        <v>351.5</v>
       </c>
       <c r="H19" t="n">
-        <v>76.7</v>
+        <v>29.2</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>-11.52</v>
+        <v>-140.58</v>
       </c>
       <c r="K19" t="n">
-        <v>113.44</v>
+        <v>106.99</v>
       </c>
       <c r="L19" t="n">
-        <v>114.03</v>
+        <v>176.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:36:53</t>
+          <t>06:36:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.69</v>
+        <v>5.04</v>
       </c>
       <c r="F20" t="n">
-        <v>10.02</v>
+        <v>11.98</v>
       </c>
       <c r="G20" t="n">
-        <v>340.4</v>
+        <v>337.5</v>
       </c>
       <c r="H20" t="n">
-        <v>72.5</v>
+        <v>82</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-157.78</v>
+        <v>15.86</v>
       </c>
       <c r="K20" t="n">
-        <v>48.08</v>
+        <v>-225.2</v>
       </c>
       <c r="L20" t="n">
-        <v>164.94</v>
+        <v>225.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:39:15</t>
+          <t>06:38:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="F21" t="n">
-        <v>9.359999999999999</v>
+        <v>10.94</v>
       </c>
       <c r="G21" t="n">
-        <v>343.1</v>
+        <v>345</v>
       </c>
       <c r="H21" t="n">
-        <v>77.90000000000001</v>
+        <v>53.7</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.42</v>
+        <v>206.88</v>
       </c>
       <c r="K21" t="n">
-        <v>196.52</v>
+        <v>-33</v>
       </c>
       <c r="L21" t="n">
-        <v>197.79</v>
+        <v>209.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:41:12</t>
+          <t>06:39:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.39</v>
+        <v>5.13</v>
       </c>
       <c r="F22" t="n">
-        <v>9.01</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>349.2</v>
+        <v>336.6</v>
       </c>
       <c r="H22" t="n">
-        <v>74.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>-80.04000000000001</v>
+        <v>-215.94</v>
       </c>
       <c r="K22" t="n">
-        <v>183.56</v>
+        <v>-121.02</v>
       </c>
       <c r="L22" t="n">
-        <v>200.25</v>
+        <v>247.54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:46:00</t>
+          <t>06:44:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.3</v>
+        <v>4.31</v>
       </c>
       <c r="F23" t="n">
-        <v>10.55</v>
+        <v>8.9</v>
       </c>
       <c r="G23" t="n">
-        <v>3.9</v>
+        <v>355.2</v>
       </c>
       <c r="H23" t="n">
-        <v>73.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>274.43</v>
+        <v>-4.12</v>
       </c>
       <c r="K23" t="n">
-        <v>99.36</v>
+        <v>204.6</v>
       </c>
       <c r="L23" t="n">
-        <v>291.86</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:48:17</t>
+          <t>06:45:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.73</v>
+        <v>4.57</v>
       </c>
       <c r="F24" t="n">
-        <v>10.05</v>
+        <v>10.37</v>
       </c>
       <c r="G24" t="n">
-        <v>343.9</v>
+        <v>333</v>
       </c>
       <c r="H24" t="n">
-        <v>77.5</v>
+        <v>79.8</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>256.55</v>
+        <v>-198.64</v>
       </c>
       <c r="K24" t="n">
-        <v>-40.03</v>
+        <v>277.04</v>
       </c>
       <c r="L24" t="n">
-        <v>259.65</v>
+        <v>340.89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:49:13</t>
+          <t>06:47:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.17</v>
+        <v>4.24</v>
       </c>
       <c r="F25" t="n">
-        <v>12.6</v>
+        <v>5.62</v>
       </c>
       <c r="G25" t="n">
-        <v>348.7</v>
+        <v>346.4</v>
       </c>
       <c r="H25" t="n">
-        <v>73.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="I25" t="n">
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-54.89</v>
+        <v>333.97</v>
       </c>
       <c r="K25" t="n">
-        <v>129.68</v>
+        <v>-32.58</v>
       </c>
       <c r="L25" t="n">
-        <v>140.82</v>
+        <v>335.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:53:08</t>
+          <t>06:51:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.3</v>
+        <v>4.72</v>
       </c>
       <c r="F26" t="n">
-        <v>8.550000000000001</v>
+        <v>10.54</v>
       </c>
       <c r="G26" t="n">
-        <v>338.3</v>
+        <v>354.2</v>
       </c>
       <c r="H26" t="n">
-        <v>75.3</v>
+        <v>26.9</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>-341.81</v>
+        <v>-67.87</v>
       </c>
       <c r="K26" t="n">
-        <v>301.77</v>
+        <v>-373.52</v>
       </c>
       <c r="L26" t="n">
-        <v>455.95</v>
+        <v>379.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:55:10</t>
+          <t>06:53:37</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.79</v>
+        <v>4.56</v>
       </c>
       <c r="F27" t="n">
-        <v>9.09</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>350.2</v>
+        <v>353.6</v>
       </c>
       <c r="H27" t="n">
-        <v>79.90000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>160.62</v>
+        <v>257.87</v>
       </c>
       <c r="K27" t="n">
-        <v>374.53</v>
+        <v>173.78</v>
       </c>
       <c r="L27" t="n">
-        <v>407.51</v>
+        <v>310.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:56:24</t>
+          <t>06:56:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.08</v>
+        <v>4.82</v>
       </c>
       <c r="F28" t="n">
-        <v>12.6</v>
+        <v>10.32</v>
       </c>
       <c r="G28" t="n">
-        <v>357</v>
+        <v>341.8</v>
       </c>
       <c r="H28" t="n">
-        <v>71.09999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-582.21</v>
+        <v>240.04</v>
       </c>
       <c r="K28" t="n">
-        <v>-14.62</v>
+        <v>344.06</v>
       </c>
       <c r="L28" t="n">
-        <v>582.39</v>
+        <v>419.52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:09:31</t>
+          <t>07:03:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.62</v>
+        <v>5.03</v>
       </c>
       <c r="F29" t="n">
-        <v>11.51</v>
+        <v>11.21</v>
       </c>
       <c r="G29" t="n">
-        <v>345.5</v>
+        <v>354.3</v>
       </c>
       <c r="H29" t="n">
-        <v>81.90000000000001</v>
+        <v>50.5</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>36.49</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-67.59</v>
+        <v>51.77</v>
       </c>
       <c r="L29" t="n">
-        <v>76.81</v>
+        <v>103.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:11:13</t>
+          <t>07:04:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.43</v>
+        <v>5.37</v>
       </c>
       <c r="F30" t="n">
-        <v>8.84</v>
+        <v>11.86</v>
       </c>
       <c r="G30" t="n">
-        <v>1.9</v>
+        <v>352.1</v>
       </c>
       <c r="H30" t="n">
-        <v>71.2</v>
+        <v>56.2</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.03</v>
+        <v>-107.46</v>
       </c>
       <c r="K30" t="n">
-        <v>106.92</v>
+        <v>41.79</v>
       </c>
       <c r="L30" t="n">
-        <v>108.27</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:13:36</t>
+          <t>07:07:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.74</v>
+        <v>4.99</v>
       </c>
       <c r="F31" t="n">
-        <v>8.800000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="G31" t="n">
-        <v>340.3</v>
+        <v>346.1</v>
       </c>
       <c r="H31" t="n">
-        <v>67.3</v>
+        <v>36.4</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>61.25</v>
+        <v>100.26</v>
       </c>
       <c r="K31" t="n">
-        <v>74.36</v>
+        <v>30.68</v>
       </c>
       <c r="L31" t="n">
-        <v>96.34</v>
+        <v>104.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:17:14</t>
+          <t>07:13:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.01</v>
+        <v>4.86</v>
       </c>
       <c r="F32" t="n">
-        <v>13.57</v>
+        <v>10.07</v>
       </c>
       <c r="G32" t="n">
-        <v>350.8</v>
+        <v>329</v>
       </c>
       <c r="H32" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-54.82</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-35.73</v>
+        <v>121.5</v>
       </c>
       <c r="L32" t="n">
-        <v>65.44</v>
+        <v>150.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:18:10</t>
+          <t>07:14:24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.08</v>
+        <v>5.04</v>
       </c>
       <c r="F33" t="n">
-        <v>12.01</v>
+        <v>9.56</v>
       </c>
       <c r="G33" t="n">
-        <v>341</v>
+        <v>340.9</v>
       </c>
       <c r="H33" t="n">
-        <v>75.3</v>
+        <v>86.2</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J33" t="n">
-        <v>-96.48999999999999</v>
+        <v>-74.05</v>
       </c>
       <c r="K33" t="n">
-        <v>7.84</v>
+        <v>133.95</v>
       </c>
       <c r="L33" t="n">
-        <v>96.81</v>
+        <v>153.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:19:55</t>
+          <t>07:15:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.63</v>
+        <v>4.87</v>
       </c>
       <c r="F34" t="n">
-        <v>10.7</v>
+        <v>12.65</v>
       </c>
       <c r="G34" t="n">
-        <v>339.1</v>
+        <v>338.2</v>
       </c>
       <c r="H34" t="n">
-        <v>67.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-54.43</v>
+        <v>37</v>
       </c>
       <c r="K34" t="n">
-        <v>-69.28</v>
+        <v>89.8</v>
       </c>
       <c r="L34" t="n">
-        <v>88.09999999999999</v>
+        <v>97.12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:24:33</t>
+          <t>07:19:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.33</v>
+        <v>5.26</v>
       </c>
       <c r="F35" t="n">
-        <v>10.4</v>
+        <v>9.77</v>
       </c>
       <c r="G35" t="n">
-        <v>5.9</v>
+        <v>359.4</v>
       </c>
       <c r="H35" t="n">
-        <v>76.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-126.39</v>
+        <v>-132.39</v>
       </c>
       <c r="K35" t="n">
-        <v>36.13</v>
+        <v>157.98</v>
       </c>
       <c r="L35" t="n">
-        <v>131.45</v>
+        <v>206.12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:26:40</t>
+          <t>07:21:11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="F36" t="n">
-        <v>11.23</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>3.9</v>
+        <v>335.8</v>
       </c>
       <c r="H36" t="n">
-        <v>76.2</v>
+        <v>24.7</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>199.67</v>
+        <v>-187.93</v>
       </c>
       <c r="K36" t="n">
-        <v>203.08</v>
+        <v>-116.48</v>
       </c>
       <c r="L36" t="n">
-        <v>284.8</v>
+        <v>221.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:28:58</t>
+          <t>07:22:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.46</v>
+        <v>4.62</v>
       </c>
       <c r="F37" t="n">
-        <v>12.87</v>
+        <v>11.5</v>
       </c>
       <c r="G37" t="n">
-        <v>354.2</v>
+        <v>337.2</v>
       </c>
       <c r="H37" t="n">
-        <v>74.40000000000001</v>
+        <v>57.3</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-180.07</v>
+        <v>-166.38</v>
       </c>
       <c r="K37" t="n">
-        <v>219.1</v>
+        <v>-91.55</v>
       </c>
       <c r="L37" t="n">
-        <v>283.6</v>
+        <v>189.91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:33:36</t>
+          <t>07:26:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.11</v>
+        <v>5.34</v>
       </c>
       <c r="F38" t="n">
-        <v>12.67</v>
+        <v>11.08</v>
       </c>
       <c r="G38" t="n">
-        <v>359</v>
+        <v>332.9</v>
       </c>
       <c r="H38" t="n">
-        <v>79.40000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-227.17</v>
+        <v>190.64</v>
       </c>
       <c r="K38" t="n">
-        <v>-12.52</v>
+        <v>196.87</v>
       </c>
       <c r="L38" t="n">
-        <v>227.51</v>
+        <v>274.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:35:36</t>
+          <t>07:28:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.6</v>
+        <v>5.07</v>
       </c>
       <c r="F39" t="n">
-        <v>10.55</v>
+        <v>13.23</v>
       </c>
       <c r="G39" t="n">
-        <v>356.2</v>
+        <v>350</v>
       </c>
       <c r="H39" t="n">
-        <v>68.59999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>209.73</v>
+        <v>-127.45</v>
       </c>
       <c r="K39" t="n">
-        <v>-48.64</v>
+        <v>-221.1</v>
       </c>
       <c r="L39" t="n">
-        <v>215.3</v>
+        <v>255.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:36:51</t>
+          <t>07:30:02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.48</v>
+        <v>4.7</v>
       </c>
       <c r="F40" t="n">
-        <v>11.86</v>
+        <v>10.82</v>
       </c>
       <c r="G40" t="n">
-        <v>358.9</v>
+        <v>345.9</v>
       </c>
       <c r="H40" t="n">
-        <v>79.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-216.99</v>
+        <v>-162.77</v>
       </c>
       <c r="K40" t="n">
-        <v>260.06</v>
+        <v>288.84</v>
       </c>
       <c r="L40" t="n">
-        <v>338.7</v>
+        <v>331.55</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:41:39</t>
+          <t>07:34:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.02</v>
+        <v>5.28</v>
       </c>
       <c r="F41" t="n">
-        <v>11.6</v>
+        <v>12.98</v>
       </c>
       <c r="G41" t="n">
-        <v>337.6</v>
+        <v>355.8</v>
       </c>
       <c r="H41" t="n">
-        <v>70.40000000000001</v>
+        <v>53.1</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J41" t="n">
-        <v>39.72</v>
+        <v>-399.13</v>
       </c>
       <c r="K41" t="n">
-        <v>-555.3099999999999</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>556.73</v>
+        <v>399.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:43:30</t>
+          <t>07:36:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.28</v>
+        <v>4.82</v>
       </c>
       <c r="F42" t="n">
-        <v>11.69</v>
+        <v>12.6</v>
       </c>
       <c r="G42" t="n">
-        <v>347.6</v>
+        <v>348.5</v>
       </c>
       <c r="H42" t="n">
-        <v>78</v>
+        <v>70.8</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-516.95</v>
+        <v>-275.4</v>
       </c>
       <c r="K42" t="n">
-        <v>-468.16</v>
+        <v>248.58</v>
       </c>
       <c r="L42" t="n">
-        <v>697.4299999999999</v>
+        <v>370.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:44:25</t>
+          <t>07:37:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.92</v>
+        <v>5.03</v>
       </c>
       <c r="F43" t="n">
-        <v>12.61</v>
+        <v>13.57</v>
       </c>
       <c r="G43" t="n">
-        <v>356</v>
+        <v>356.5</v>
       </c>
       <c r="H43" t="n">
-        <v>74.90000000000001</v>
+        <v>44</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>209.48</v>
+        <v>-130.24</v>
       </c>
       <c r="K43" t="n">
-        <v>-273.31</v>
+        <v>300.94</v>
       </c>
       <c r="L43" t="n">
-        <v>344.36</v>
+        <v>327.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:55:31</t>
+          <t>07:47:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.44</v>
+        <v>5.05</v>
       </c>
       <c r="F44" t="n">
-        <v>11.34</v>
+        <v>12.19</v>
       </c>
       <c r="G44" t="n">
-        <v>354.9</v>
+        <v>336.2</v>
       </c>
       <c r="H44" t="n">
-        <v>71.09999999999999</v>
+        <v>42.3</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-75.26000000000001</v>
+        <v>-105.02</v>
       </c>
       <c r="K44" t="n">
-        <v>38.29</v>
+        <v>-65.39</v>
       </c>
       <c r="L44" t="n">
-        <v>84.44</v>
+        <v>123.71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:57:47</t>
+          <t>07:48:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.83</v>
+        <v>4.34</v>
       </c>
       <c r="F45" t="n">
-        <v>7.56</v>
+        <v>7.03</v>
       </c>
       <c r="G45" t="n">
         <v>342.1</v>
       </c>
       <c r="H45" t="n">
-        <v>73.40000000000001</v>
+        <v>46.2</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-77.09999999999999</v>
+        <v>31.33</v>
       </c>
       <c r="K45" t="n">
-        <v>-43.54</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>88.54000000000001</v>
+        <v>86.19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:59:18</t>
+          <t>07:50:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.73</v>
+        <v>5.37</v>
       </c>
       <c r="F46" t="n">
-        <v>12.96</v>
+        <v>13.33</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3</v>
+        <v>354.4</v>
       </c>
       <c r="H46" t="n">
-        <v>79.2</v>
+        <v>61.8</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J46" t="n">
-        <v>115.71</v>
+        <v>-56.23</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.32</v>
+        <v>123.88</v>
       </c>
       <c r="L46" t="n">
-        <v>116.08</v>
+        <v>136.04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:04:55</t>
+          <t>07:55:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.53</v>
+        <v>5.02</v>
       </c>
       <c r="F47" t="n">
-        <v>10.99</v>
+        <v>12.29</v>
       </c>
       <c r="G47" t="n">
-        <v>354</v>
+        <v>341.4</v>
       </c>
       <c r="H47" t="n">
-        <v>74.5</v>
+        <v>60.2</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>87.58</v>
+        <v>-169.87</v>
       </c>
       <c r="K47" t="n">
-        <v>-9.18</v>
+        <v>16.19</v>
       </c>
       <c r="L47" t="n">
-        <v>88.06</v>
+        <v>170.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:06:55</t>
+          <t>07:56:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.85</v>
+        <v>4.68</v>
       </c>
       <c r="F48" t="n">
-        <v>10.26</v>
+        <v>9.92</v>
       </c>
       <c r="G48" t="n">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="H48" t="n">
-        <v>68</v>
+        <v>63.5</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-9.859999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-136.01</v>
+        <v>-122.61</v>
       </c>
       <c r="L48" t="n">
-        <v>136.37</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:07:56</t>
+          <t>07:57:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.56</v>
+        <v>5.4</v>
       </c>
       <c r="F49" t="n">
-        <v>11.41</v>
+        <v>13.23</v>
       </c>
       <c r="G49" t="n">
-        <v>348.2</v>
+        <v>351.9</v>
       </c>
       <c r="H49" t="n">
-        <v>67.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-112.03</v>
+        <v>-149.65</v>
       </c>
       <c r="K49" t="n">
-        <v>24.04</v>
+        <v>-38.69</v>
       </c>
       <c r="L49" t="n">
-        <v>114.58</v>
+        <v>154.57</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:11:19</t>
+          <t>08:02:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.16</v>
+        <v>4.71</v>
       </c>
       <c r="F50" t="n">
-        <v>10.52</v>
+        <v>9.68</v>
       </c>
       <c r="G50" t="n">
-        <v>358.7</v>
+        <v>345.7</v>
       </c>
       <c r="H50" t="n">
-        <v>70.40000000000001</v>
+        <v>39.2</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>133.47</v>
+        <v>33.92</v>
       </c>
       <c r="K50" t="n">
-        <v>-66.84999999999999</v>
+        <v>168.32</v>
       </c>
       <c r="L50" t="n">
-        <v>149.28</v>
+        <v>171.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:12:46</t>
+          <t>08:03:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.33</v>
+        <v>5.13</v>
       </c>
       <c r="F51" t="n">
-        <v>13.57</v>
+        <v>11.39</v>
       </c>
       <c r="G51" t="n">
-        <v>341.2</v>
+        <v>345.9</v>
       </c>
       <c r="H51" t="n">
-        <v>68.90000000000001</v>
+        <v>44.6</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-74.23</v>
+        <v>244.29</v>
       </c>
       <c r="K51" t="n">
-        <v>155.15</v>
+        <v>118.6</v>
       </c>
       <c r="L51" t="n">
-        <v>171.99</v>
+        <v>271.56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:13:39</t>
+          <t>08:04:54</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.71</v>
+        <v>5.36</v>
       </c>
       <c r="F52" t="n">
-        <v>10.29</v>
+        <v>11.35</v>
       </c>
       <c r="G52" t="n">
-        <v>347.9</v>
+        <v>340.6</v>
       </c>
       <c r="H52" t="n">
-        <v>71.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-44.74</v>
+        <v>198.46</v>
       </c>
       <c r="K52" t="n">
-        <v>-122.39</v>
+        <v>-45.6</v>
       </c>
       <c r="L52" t="n">
-        <v>130.31</v>
+        <v>203.63</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:19:10</t>
+          <t>08:09:58</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.06</v>
+        <v>4.78</v>
       </c>
       <c r="F53" t="n">
-        <v>13.35</v>
+        <v>10.91</v>
       </c>
       <c r="G53" t="n">
-        <v>8.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="H53" t="n">
-        <v>74.5</v>
+        <v>37.6</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>152.81</v>
+        <v>28.11</v>
       </c>
       <c r="K53" t="n">
-        <v>124.62</v>
+        <v>324.18</v>
       </c>
       <c r="L53" t="n">
-        <v>197.18</v>
+        <v>325.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:20:22</t>
+          <t>08:11:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.33</v>
+        <v>4.61</v>
       </c>
       <c r="F54" t="n">
-        <v>13.57</v>
+        <v>11.61</v>
       </c>
       <c r="G54" t="n">
         <v>344</v>
       </c>
       <c r="H54" t="n">
-        <v>68.8</v>
+        <v>52</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>-279.35</v>
+        <v>106.91</v>
       </c>
       <c r="K54" t="n">
-        <v>14.58</v>
+        <v>358.19</v>
       </c>
       <c r="L54" t="n">
-        <v>279.73</v>
+        <v>373.81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:22:01</t>
+          <t>08:12:02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.54</v>
+        <v>4.84</v>
       </c>
       <c r="F55" t="n">
-        <v>13.57</v>
+        <v>12.14</v>
       </c>
       <c r="G55" t="n">
-        <v>355.9</v>
+        <v>347.3</v>
       </c>
       <c r="H55" t="n">
-        <v>73</v>
+        <v>44.8</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-298.71</v>
+        <v>4.28</v>
       </c>
       <c r="K55" t="n">
-        <v>9.539999999999999</v>
+        <v>265.33</v>
       </c>
       <c r="L55" t="n">
-        <v>298.86</v>
+        <v>265.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:27:10</t>
+          <t>08:16:52</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.21</v>
+        <v>5.14</v>
       </c>
       <c r="F56" t="n">
-        <v>13.57</v>
+        <v>11.55</v>
       </c>
       <c r="G56" t="n">
-        <v>356.1</v>
+        <v>357.2</v>
       </c>
       <c r="H56" t="n">
-        <v>74.90000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-396.02</v>
+        <v>-408.8</v>
       </c>
       <c r="K56" t="n">
-        <v>-181.17</v>
+        <v>-255.79</v>
       </c>
       <c r="L56" t="n">
-        <v>435.5</v>
+        <v>482.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:28:51</t>
+          <t>08:19:03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.16</v>
+        <v>5.17</v>
       </c>
       <c r="F57" t="n">
-        <v>13.4</v>
+        <v>12.36</v>
       </c>
       <c r="G57" t="n">
-        <v>7.2</v>
+        <v>350.3</v>
       </c>
       <c r="H57" t="n">
-        <v>70.90000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-257.66</v>
+        <v>416.05</v>
       </c>
       <c r="K57" t="n">
-        <v>-447.63</v>
+        <v>75.13</v>
       </c>
       <c r="L57" t="n">
-        <v>516.49</v>
+        <v>422.78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:30:56</t>
+          <t>08:20:04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.28</v>
+        <v>4.9</v>
       </c>
       <c r="F58" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
       <c r="G58" t="n">
-        <v>350.4</v>
+        <v>351.8</v>
       </c>
       <c r="H58" t="n">
-        <v>76.40000000000001</v>
+        <v>44.5</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>326.92</v>
+        <v>219.77</v>
       </c>
       <c r="K58" t="n">
-        <v>75.65000000000001</v>
+        <v>-295.25</v>
       </c>
       <c r="L58" t="n">
-        <v>335.56</v>
+        <v>368.06</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:39:59</t>
+          <t>08:27:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.86</v>
+        <v>5.03</v>
       </c>
       <c r="F59" t="n">
-        <v>12.86</v>
+        <v>12.91</v>
       </c>
       <c r="G59" t="n">
-        <v>351.3</v>
+        <v>349.3</v>
       </c>
       <c r="H59" t="n">
-        <v>75.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-77.31999999999999</v>
+        <v>-42.61</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.75</v>
+        <v>85.3</v>
       </c>
       <c r="L59" t="n">
-        <v>78.37</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:42:26</t>
+          <t>08:29:04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.65</v>
+        <v>5.25</v>
       </c>
       <c r="F60" t="n">
-        <v>10.77</v>
+        <v>12.09</v>
       </c>
       <c r="G60" t="n">
-        <v>334.8</v>
+        <v>354.1</v>
       </c>
       <c r="H60" t="n">
-        <v>65.3</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-65.97</v>
+        <v>-86.33</v>
       </c>
       <c r="K60" t="n">
-        <v>-32.47</v>
+        <v>-45.03</v>
       </c>
       <c r="L60" t="n">
-        <v>73.52</v>
+        <v>97.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:44:06</t>
+          <t>08:30:34</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="F61" t="n">
-        <v>12.51</v>
+        <v>12.85</v>
       </c>
       <c r="G61" t="n">
-        <v>352.4</v>
+        <v>358.5</v>
       </c>
       <c r="H61" t="n">
-        <v>67.2</v>
+        <v>51.9</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J61" t="n">
-        <v>-83.61</v>
+        <v>11.61</v>
       </c>
       <c r="K61" t="n">
-        <v>39.52</v>
+        <v>144.57</v>
       </c>
       <c r="L61" t="n">
-        <v>92.48</v>
+        <v>145.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:47:04</t>
+          <t>08:36:29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.46</v>
+        <v>5.41</v>
       </c>
       <c r="F62" t="n">
-        <v>9.67</v>
+        <v>13.57</v>
       </c>
       <c r="G62" t="n">
-        <v>351.5</v>
+        <v>341.7</v>
       </c>
       <c r="H62" t="n">
-        <v>77.8</v>
+        <v>46.6</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>-165.16</v>
+        <v>-125.25</v>
       </c>
       <c r="K62" t="n">
-        <v>-19.2</v>
+        <v>11.08</v>
       </c>
       <c r="L62" t="n">
-        <v>166.28</v>
+        <v>125.74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:49:22</t>
+          <t>08:37:06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.78</v>
+        <v>4.83</v>
       </c>
       <c r="F63" t="n">
-        <v>9.890000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="G63" t="n">
-        <v>351.5</v>
+        <v>10.3</v>
       </c>
       <c r="H63" t="n">
-        <v>77.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-80.56</v>
+        <v>48.66</v>
       </c>
       <c r="K63" t="n">
-        <v>-54.19</v>
+        <v>119.56</v>
       </c>
       <c r="L63" t="n">
-        <v>97.09</v>
+        <v>129.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:50:30</t>
+          <t>08:38:40</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.68</v>
+        <v>4.83</v>
       </c>
       <c r="F64" t="n">
-        <v>11.74</v>
+        <v>9.98</v>
       </c>
       <c r="G64" t="n">
-        <v>342.6</v>
+        <v>356.5</v>
       </c>
       <c r="H64" t="n">
-        <v>72.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>93.34</v>
+        <v>-134.64</v>
       </c>
       <c r="K64" t="n">
-        <v>-56.1</v>
+        <v>74.98</v>
       </c>
       <c r="L64" t="n">
-        <v>108.91</v>
+        <v>154.11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:55:50</t>
+          <t>08:42:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.98</v>
+        <v>5.9</v>
       </c>
       <c r="F65" t="n">
         <v>13.57</v>
       </c>
       <c r="G65" t="n">
-        <v>338.2</v>
+        <v>344.2</v>
       </c>
       <c r="H65" t="n">
-        <v>70.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J65" t="n">
-        <v>88.51000000000001</v>
+        <v>4.68</v>
       </c>
       <c r="K65" t="n">
-        <v>-81.45</v>
+        <v>284.3</v>
       </c>
       <c r="L65" t="n">
-        <v>120.29</v>
+        <v>284.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:58:06</t>
+          <t>08:44:16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.74</v>
+        <v>4.54</v>
       </c>
       <c r="F66" t="n">
-        <v>13.57</v>
+        <v>11.48</v>
       </c>
       <c r="G66" t="n">
-        <v>338.6</v>
+        <v>355</v>
       </c>
       <c r="H66" t="n">
-        <v>75.90000000000001</v>
+        <v>45.9</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-171.17</v>
+        <v>-148.43</v>
       </c>
       <c r="K66" t="n">
-        <v>104.43</v>
+        <v>-41.05</v>
       </c>
       <c r="L66" t="n">
-        <v>200.51</v>
+        <v>154.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:58:49</t>
+          <t>08:45:23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.98</v>
+        <v>5.88</v>
       </c>
       <c r="F67" t="n">
-        <v>11.73</v>
+        <v>13.57</v>
       </c>
       <c r="G67" t="n">
-        <v>353.3</v>
+        <v>337.1</v>
       </c>
       <c r="H67" t="n">
-        <v>69.09999999999999</v>
+        <v>43.7</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-172.23</v>
+        <v>-158.54</v>
       </c>
       <c r="K67" t="n">
-        <v>27.86</v>
+        <v>154.54</v>
       </c>
       <c r="L67" t="n">
-        <v>174.47</v>
+        <v>221.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:04:00</t>
+          <t>08:51:13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.84</v>
+        <v>5.33</v>
       </c>
       <c r="F68" t="n">
-        <v>11.6</v>
+        <v>11.95</v>
       </c>
       <c r="G68" t="n">
-        <v>346.6</v>
+        <v>356.2</v>
       </c>
       <c r="H68" t="n">
-        <v>70.09999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>141.85</v>
+        <v>-130.59</v>
       </c>
       <c r="K68" t="n">
-        <v>-174.72</v>
+        <v>277.23</v>
       </c>
       <c r="L68" t="n">
-        <v>225.05</v>
+        <v>306.45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:04:54</t>
+          <t>08:52:35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.34</v>
+        <v>5.01</v>
       </c>
       <c r="F69" t="n">
-        <v>12.54</v>
+        <v>12.58</v>
       </c>
       <c r="G69" t="n">
-        <v>355.3</v>
+        <v>347.3</v>
       </c>
       <c r="H69" t="n">
-        <v>72.3</v>
+        <v>66.2</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>156.47</v>
+        <v>38.19</v>
       </c>
       <c r="K69" t="n">
-        <v>272.39</v>
+        <v>289.6</v>
       </c>
       <c r="L69" t="n">
-        <v>314.13</v>
+        <v>292.11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:06:01</t>
+          <t>08:53:54</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.63</v>
+        <v>5.43</v>
       </c>
       <c r="F70" t="n">
-        <v>11.63</v>
+        <v>13.57</v>
       </c>
       <c r="G70" t="n">
-        <v>344.4</v>
+        <v>337.7</v>
       </c>
       <c r="H70" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-262.4</v>
+        <v>176.61</v>
       </c>
       <c r="K70" t="n">
-        <v>49.88</v>
+        <v>174.41</v>
       </c>
       <c r="L70" t="n">
-        <v>267.1</v>
+        <v>248.21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:11:24</t>
+          <t>08:58:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="F71" t="n">
-        <v>11.63</v>
+        <v>12.7</v>
       </c>
       <c r="G71" t="n">
-        <v>354.1</v>
+        <v>342.1</v>
       </c>
       <c r="H71" t="n">
-        <v>80.7</v>
+        <v>35.6</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>490.81</v>
+        <v>125.69</v>
       </c>
       <c r="K71" t="n">
-        <v>62.11</v>
+        <v>312.69</v>
       </c>
       <c r="L71" t="n">
-        <v>494.73</v>
+        <v>337.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:12:23</t>
+          <t>08:59:36</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.28</v>
+        <v>5.51</v>
       </c>
       <c r="F72" t="n">
-        <v>13.57</v>
+        <v>11.82</v>
       </c>
       <c r="G72" t="n">
-        <v>1.6</v>
+        <v>351.6</v>
       </c>
       <c r="H72" t="n">
-        <v>77.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>563.75</v>
+        <v>-125.86</v>
       </c>
       <c r="K72" t="n">
-        <v>-89.48999999999999</v>
+        <v>-417.66</v>
       </c>
       <c r="L72" t="n">
-        <v>570.8099999999999</v>
+        <v>436.21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:14:39</t>
+          <t>09:00:14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.91</v>
+        <v>4.95</v>
       </c>
       <c r="F73" t="n">
-        <v>13.28</v>
+        <v>11.81</v>
       </c>
       <c r="G73" t="n">
-        <v>2.9</v>
+        <v>352</v>
       </c>
       <c r="H73" t="n">
-        <v>72.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>44.79</v>
+        <v>-135.56</v>
       </c>
       <c r="K73" t="n">
-        <v>-424.16</v>
+        <v>343.01</v>
       </c>
       <c r="L73" t="n">
-        <v>426.51</v>
+        <v>368.83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:25:44</t>
+          <t>09:13:03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.85</v>
+        <v>5.06</v>
       </c>
       <c r="F74" t="n">
-        <v>13.57</v>
+        <v>13.45</v>
       </c>
       <c r="G74" t="n">
-        <v>359.8</v>
+        <v>341.9</v>
       </c>
       <c r="H74" t="n">
-        <v>70.59999999999999</v>
+        <v>27</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-74.09</v>
+        <v>26.41</v>
       </c>
       <c r="K74" t="n">
-        <v>57.42</v>
+        <v>102.59</v>
       </c>
       <c r="L74" t="n">
-        <v>93.73</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:28:04</t>
+          <t>09:14:20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.71</v>
+        <v>5.53</v>
       </c>
       <c r="F75" t="n">
-        <v>13.46</v>
+        <v>13.57</v>
       </c>
       <c r="G75" t="n">
-        <v>346.9</v>
+        <v>351</v>
       </c>
       <c r="H75" t="n">
-        <v>77.90000000000001</v>
+        <v>48.5</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-110.1</v>
+        <v>159.16</v>
       </c>
       <c r="K75" t="n">
-        <v>25.84</v>
+        <v>25.52</v>
       </c>
       <c r="L75" t="n">
-        <v>113.09</v>
+        <v>161.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:29:38</t>
+          <t>09:15:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.8</v>
+        <v>5.61</v>
       </c>
       <c r="F76" t="n">
-        <v>12.86</v>
+        <v>11.66</v>
       </c>
       <c r="G76" t="n">
-        <v>332.9</v>
+        <v>2.2</v>
       </c>
       <c r="H76" t="n">
-        <v>81</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J76" t="n">
-        <v>25.07</v>
+        <v>101.59</v>
       </c>
       <c r="K76" t="n">
-        <v>73.43000000000001</v>
+        <v>-19.69</v>
       </c>
       <c r="L76" t="n">
-        <v>77.59</v>
+        <v>103.48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:32:51</t>
+          <t>09:19:11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.21</v>
+        <v>5.53</v>
       </c>
       <c r="F77" t="n">
-        <v>13.14</v>
+        <v>12.96</v>
       </c>
       <c r="G77" t="n">
-        <v>3.4</v>
+        <v>342.4</v>
       </c>
       <c r="H77" t="n">
-        <v>66.7</v>
+        <v>53.7</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J77" t="n">
-        <v>12.92</v>
+        <v>-87.05</v>
       </c>
       <c r="K77" t="n">
-        <v>69.95999999999999</v>
+        <v>167.06</v>
       </c>
       <c r="L77" t="n">
-        <v>71.15000000000001</v>
+        <v>188.38</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:34:54</t>
+          <t>09:20:39</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.15</v>
+        <v>5.36</v>
       </c>
       <c r="F78" t="n">
         <v>13.57</v>
       </c>
       <c r="G78" t="n">
-        <v>353.4</v>
+        <v>357.3</v>
       </c>
       <c r="H78" t="n">
-        <v>77.3</v>
+        <v>39.1</v>
       </c>
       <c r="I78" t="n">
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>110.84</v>
+        <v>-158</v>
       </c>
       <c r="K78" t="n">
-        <v>46.32</v>
+        <v>-22.73</v>
       </c>
       <c r="L78" t="n">
-        <v>120.13</v>
+        <v>159.63</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:36:28</t>
+          <t>09:21:56</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.18</v>
+        <v>5.58</v>
       </c>
       <c r="F79" t="n">
-        <v>13.15</v>
+        <v>13.05</v>
       </c>
       <c r="G79" t="n">
-        <v>354.7</v>
+        <v>349.9</v>
       </c>
       <c r="H79" t="n">
-        <v>75.40000000000001</v>
+        <v>30.3</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>23.59</v>
+        <v>-21.46</v>
       </c>
       <c r="K79" t="n">
-        <v>-35.07</v>
+        <v>-152.81</v>
       </c>
       <c r="L79" t="n">
-        <v>42.26</v>
+        <v>154.31</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:41:16</t>
+          <t>09:27:25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.62</v>
+        <v>5.39</v>
       </c>
       <c r="F80" t="n">
         <v>13.57</v>
       </c>
       <c r="G80" t="n">
-        <v>350.1</v>
+        <v>339.3</v>
       </c>
       <c r="H80" t="n">
-        <v>72.59999999999999</v>
+        <v>34.5</v>
       </c>
       <c r="I80" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>156.28</v>
+        <v>-108.89</v>
       </c>
       <c r="K80" t="n">
-        <v>111.58</v>
+        <v>177.04</v>
       </c>
       <c r="L80" t="n">
-        <v>192.03</v>
+        <v>207.84</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:42:35</t>
+          <t>09:29:44</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.97</v>
+        <v>5.13</v>
       </c>
       <c r="F81" t="n">
-        <v>13.57</v>
+        <v>10.32</v>
       </c>
       <c r="G81" t="n">
-        <v>2.7</v>
+        <v>346.3</v>
       </c>
       <c r="H81" t="n">
-        <v>76.5</v>
+        <v>90.8</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J81" t="n">
-        <v>-67.7</v>
+        <v>-56.16</v>
       </c>
       <c r="K81" t="n">
-        <v>225.3</v>
+        <v>175.93</v>
       </c>
       <c r="L81" t="n">
-        <v>235.25</v>
+        <v>184.68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:44:38</t>
+          <t>09:31:57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.85</v>
+        <v>5.64</v>
       </c>
       <c r="F82" t="n">
-        <v>13.35</v>
+        <v>13.57</v>
       </c>
       <c r="G82" t="n">
-        <v>332.9</v>
+        <v>4.7</v>
       </c>
       <c r="H82" t="n">
-        <v>76.2</v>
+        <v>35.5</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-48.23</v>
+        <v>203.57</v>
       </c>
       <c r="K82" t="n">
-        <v>142.67</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>150.6</v>
+        <v>221.22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:49:49</t>
+          <t>09:36:39</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.76</v>
+        <v>5.15</v>
       </c>
       <c r="F83" t="n">
-        <v>13.57</v>
+        <v>12.03</v>
       </c>
       <c r="G83" t="n">
-        <v>354</v>
+        <v>324.4</v>
       </c>
       <c r="H83" t="n">
-        <v>73.40000000000001</v>
+        <v>20</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J83" t="n">
-        <v>210.62</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-158.97</v>
+        <v>161.16</v>
       </c>
       <c r="L83" t="n">
-        <v>263.88</v>
+        <v>177.38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:52:27</t>
+          <t>09:38:48</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.76</v>
+        <v>5.86</v>
       </c>
       <c r="F84" t="n">
         <v>13.57</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>357.7</v>
       </c>
       <c r="H84" t="n">
-        <v>76.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>183.18</v>
+        <v>-4.98</v>
       </c>
       <c r="K84" t="n">
-        <v>281.2</v>
+        <v>340.26</v>
       </c>
       <c r="L84" t="n">
-        <v>335.6</v>
+        <v>340.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:53:57</t>
+          <t>09:41:05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.5</v>
+        <v>6.92</v>
       </c>
       <c r="F85" t="n">
-        <v>13.21</v>
+        <v>13.57</v>
       </c>
       <c r="G85" t="n">
-        <v>1.3</v>
+        <v>342.8</v>
       </c>
       <c r="H85" t="n">
-        <v>62.9</v>
+        <v>60.2</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>55.88</v>
+        <v>343.33</v>
       </c>
       <c r="K85" t="n">
-        <v>-233.59</v>
+        <v>-99.56999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>240.18</v>
+        <v>357.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:57:13</t>
+          <t>09:46:17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.15</v>
+        <v>4.93</v>
       </c>
       <c r="F86" t="n">
-        <v>13.57</v>
+        <v>11.15</v>
       </c>
       <c r="G86" t="n">
-        <v>355.6</v>
+        <v>357.7</v>
       </c>
       <c r="H86" t="n">
-        <v>78.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-493.99</v>
+        <v>-149.1</v>
       </c>
       <c r="K86" t="n">
-        <v>-351.64</v>
+        <v>285.6</v>
       </c>
       <c r="L86" t="n">
-        <v>606.36</v>
+        <v>322.18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:59:41</t>
+          <t>09:47:49</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.08</v>
+        <v>5.62</v>
       </c>
       <c r="F87" t="n">
         <v>13.57</v>
       </c>
       <c r="G87" t="n">
-        <v>347.1</v>
+        <v>354.1</v>
       </c>
       <c r="H87" t="n">
-        <v>66.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>379.3</v>
+        <v>-295.71</v>
       </c>
       <c r="K87" t="n">
-        <v>-458.85</v>
+        <v>-276.33</v>
       </c>
       <c r="L87" t="n">
-        <v>595.33</v>
+        <v>404.72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:01:01</t>
+          <t>09:49:18</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>5.58</v>
       </c>
       <c r="F88" t="n">
-        <v>12.45</v>
+        <v>12.07</v>
       </c>
       <c r="G88" t="n">
-        <v>353.7</v>
+        <v>353.3</v>
       </c>
       <c r="H88" t="n">
-        <v>74</v>
+        <v>50.5</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>-719.4299999999999</v>
+        <v>127.64</v>
       </c>
       <c r="K88" t="n">
-        <v>239.5</v>
+        <v>303.05</v>
       </c>
       <c r="L88" t="n">
-        <v>758.25</v>
+        <v>328.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.22</v>
+        <v>3.64</v>
       </c>
       <c r="F14" t="n">
-        <v>6.53</v>
+        <v>5.91</v>
       </c>
       <c r="G14" t="n">
-        <v>338.4</v>
+        <v>337.4</v>
       </c>
       <c r="H14" t="n">
-        <v>61.9</v>
+        <v>50.3</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-84.26000000000001</v>
+        <v>-25.84</v>
       </c>
       <c r="K14" t="n">
-        <v>-39.88</v>
+        <v>46.16</v>
       </c>
       <c r="L14" t="n">
-        <v>93.22</v>
+        <v>52.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:23:53</t>
+          <t>06:23:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="F15" t="n">
-        <v>10.34</v>
+        <v>11.72</v>
       </c>
       <c r="G15" t="n">
-        <v>347.8</v>
+        <v>350.4</v>
       </c>
       <c r="H15" t="n">
-        <v>64.40000000000001</v>
+        <v>24.2</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>33.04</v>
+        <v>-109.4</v>
       </c>
       <c r="K15" t="n">
-        <v>97.19</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>102.66</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:25:13</t>
+          <t>06:25:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.21</v>
+        <v>4.86</v>
       </c>
       <c r="F16" t="n">
-        <v>9.56</v>
+        <v>8.99</v>
       </c>
       <c r="G16" t="n">
-        <v>352.8</v>
+        <v>353.9</v>
       </c>
       <c r="H16" t="n">
-        <v>51</v>
+        <v>36.9</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>29.47</v>
+        <v>98.08</v>
       </c>
       <c r="K16" t="n">
-        <v>-84.51000000000001</v>
+        <v>136.79</v>
       </c>
       <c r="L16" t="n">
-        <v>89.5</v>
+        <v>168.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:28:37</t>
+          <t>06:31:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.35</v>
+        <v>5.17</v>
       </c>
       <c r="F17" t="n">
-        <v>9.73</v>
+        <v>11.21</v>
       </c>
       <c r="G17" t="n">
-        <v>349.6</v>
+        <v>348.8</v>
       </c>
       <c r="H17" t="n">
-        <v>14.5</v>
+        <v>49.5</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>68.20999999999999</v>
+        <v>-38.43</v>
       </c>
       <c r="K17" t="n">
-        <v>115.34</v>
+        <v>112.03</v>
       </c>
       <c r="L17" t="n">
-        <v>134</v>
+        <v>118.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:30:21</t>
+          <t>06:32:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="F18" t="n">
-        <v>11.91</v>
+        <v>10.2</v>
       </c>
       <c r="G18" t="n">
-        <v>359.2</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
-        <v>49</v>
+        <v>83.2</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>73.34999999999999</v>
+        <v>114.8</v>
       </c>
       <c r="K18" t="n">
-        <v>137.32</v>
+        <v>-50.42</v>
       </c>
       <c r="L18" t="n">
-        <v>155.68</v>
+        <v>125.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:31:57</t>
+          <t>06:34:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="F19" t="n">
-        <v>10.99</v>
+        <v>12.86</v>
       </c>
       <c r="G19" t="n">
-        <v>351.5</v>
+        <v>355.4</v>
       </c>
       <c r="H19" t="n">
-        <v>29.2</v>
+        <v>74.7</v>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>-140.58</v>
+        <v>103.7</v>
       </c>
       <c r="K19" t="n">
-        <v>106.99</v>
+        <v>-34.53</v>
       </c>
       <c r="L19" t="n">
-        <v>176.66</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:36:12</t>
+          <t>06:40:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="F20" t="n">
-        <v>11.98</v>
+        <v>11.52</v>
       </c>
       <c r="G20" t="n">
-        <v>337.5</v>
+        <v>352.1</v>
       </c>
       <c r="H20" t="n">
-        <v>82</v>
+        <v>18.5</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>15.86</v>
+        <v>36.52</v>
       </c>
       <c r="K20" t="n">
-        <v>-225.2</v>
+        <v>207.45</v>
       </c>
       <c r="L20" t="n">
-        <v>225.76</v>
+        <v>210.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:38:26</t>
+          <t>06:41:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.44</v>
+        <v>4.71</v>
       </c>
       <c r="F21" t="n">
-        <v>10.94</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>345</v>
+        <v>341.6</v>
       </c>
       <c r="H21" t="n">
-        <v>53.7</v>
+        <v>36</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>206.88</v>
+        <v>187.15</v>
       </c>
       <c r="K21" t="n">
-        <v>-33</v>
+        <v>28.41</v>
       </c>
       <c r="L21" t="n">
-        <v>209.5</v>
+        <v>189.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:39:52</t>
+          <t>06:43:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.13</v>
+        <v>4.87</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>10.89</v>
       </c>
       <c r="G22" t="n">
-        <v>336.6</v>
+        <v>345.6</v>
       </c>
       <c r="H22" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-215.94</v>
+        <v>32.89</v>
       </c>
       <c r="K22" t="n">
-        <v>-121.02</v>
+        <v>-225</v>
       </c>
       <c r="L22" t="n">
-        <v>247.54</v>
+        <v>227.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:44:19</t>
+          <t>06:47:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="F23" t="n">
-        <v>8.9</v>
+        <v>9.01</v>
       </c>
       <c r="G23" t="n">
-        <v>355.2</v>
+        <v>347</v>
       </c>
       <c r="H23" t="n">
-        <v>65.3</v>
+        <v>66</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.12</v>
+        <v>-49.31</v>
       </c>
       <c r="K23" t="n">
-        <v>204.6</v>
+        <v>255.28</v>
       </c>
       <c r="L23" t="n">
-        <v>204.65</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:45:24</t>
+          <t>06:48:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.57</v>
+        <v>3.85</v>
       </c>
       <c r="F24" t="n">
-        <v>10.37</v>
+        <v>6.15</v>
       </c>
       <c r="G24" t="n">
-        <v>333</v>
+        <v>350.9</v>
       </c>
       <c r="H24" t="n">
-        <v>79.8</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-198.64</v>
+        <v>200.74</v>
       </c>
       <c r="K24" t="n">
-        <v>277.04</v>
+        <v>30.04</v>
       </c>
       <c r="L24" t="n">
-        <v>340.89</v>
+        <v>202.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:47:15</t>
+          <t>06:50:37</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.24</v>
+        <v>4.41</v>
       </c>
       <c r="F25" t="n">
-        <v>5.62</v>
+        <v>10.44</v>
       </c>
       <c r="G25" t="n">
-        <v>346.4</v>
+        <v>339.1</v>
       </c>
       <c r="H25" t="n">
-        <v>71.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>333.97</v>
+        <v>-139.86</v>
       </c>
       <c r="K25" t="n">
-        <v>-32.58</v>
+        <v>-125.59</v>
       </c>
       <c r="L25" t="n">
-        <v>335.55</v>
+        <v>187.97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:51:18</t>
+          <t>06:54:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.72</v>
+        <v>4.83</v>
       </c>
       <c r="F26" t="n">
-        <v>10.54</v>
+        <v>9.59</v>
       </c>
       <c r="G26" t="n">
-        <v>354.2</v>
+        <v>359.9</v>
       </c>
       <c r="H26" t="n">
-        <v>26.9</v>
+        <v>40.7</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-67.87</v>
+        <v>303.11</v>
       </c>
       <c r="K26" t="n">
-        <v>-373.52</v>
+        <v>-137.82</v>
       </c>
       <c r="L26" t="n">
-        <v>379.63</v>
+        <v>332.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:53:37</t>
+          <t>06:56:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="F27" t="n">
-        <v>8.859999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="G27" t="n">
-        <v>353.6</v>
+        <v>347.6</v>
       </c>
       <c r="H27" t="n">
-        <v>47.4</v>
+        <v>71.7</v>
       </c>
       <c r="I27" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>257.87</v>
+        <v>292.43</v>
       </c>
       <c r="K27" t="n">
-        <v>173.78</v>
+        <v>174</v>
       </c>
       <c r="L27" t="n">
-        <v>310.96</v>
+        <v>340.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:56:03</t>
+          <t>06:58:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.82</v>
+        <v>4.44</v>
       </c>
       <c r="F28" t="n">
-        <v>10.32</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>341.8</v>
+        <v>341.2</v>
       </c>
       <c r="H28" t="n">
-        <v>46.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>240.04</v>
+        <v>-126.54</v>
       </c>
       <c r="K28" t="n">
-        <v>344.06</v>
+        <v>316.31</v>
       </c>
       <c r="L28" t="n">
-        <v>419.52</v>
+        <v>340.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:03:01</t>
+          <t>07:08:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.03</v>
+        <v>4.79</v>
       </c>
       <c r="F29" t="n">
-        <v>11.21</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>354.3</v>
+        <v>346.5</v>
       </c>
       <c r="H29" t="n">
-        <v>50.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>89.20999999999999</v>
+        <v>-94.34999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>51.77</v>
+        <v>-12.4</v>
       </c>
       <c r="L29" t="n">
-        <v>103.14</v>
+        <v>95.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:04:59</t>
+          <t>07:10:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.37</v>
+        <v>4.85</v>
       </c>
       <c r="F30" t="n">
-        <v>11.86</v>
+        <v>12.08</v>
       </c>
       <c r="G30" t="n">
-        <v>352.1</v>
+        <v>346.5</v>
       </c>
       <c r="H30" t="n">
-        <v>56.2</v>
+        <v>41.8</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-107.46</v>
+        <v>-107.48</v>
       </c>
       <c r="K30" t="n">
-        <v>41.79</v>
+        <v>-49.96</v>
       </c>
       <c r="L30" t="n">
-        <v>115.3</v>
+        <v>118.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:07:40</t>
+          <t>07:11:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.99</v>
+        <v>4.91</v>
       </c>
       <c r="F31" t="n">
-        <v>9.08</v>
+        <v>9.25</v>
       </c>
       <c r="G31" t="n">
-        <v>346.1</v>
+        <v>341.6</v>
       </c>
       <c r="H31" t="n">
-        <v>36.4</v>
+        <v>14.2</v>
       </c>
       <c r="I31" t="n">
         <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>100.26</v>
+        <v>-84.5</v>
       </c>
       <c r="K31" t="n">
-        <v>30.68</v>
+        <v>9.94</v>
       </c>
       <c r="L31" t="n">
-        <v>104.85</v>
+        <v>85.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:13:00</t>
+          <t>07:15:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.86</v>
+        <v>4.58</v>
       </c>
       <c r="F32" t="n">
-        <v>10.07</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>329</v>
+        <v>357.2</v>
       </c>
       <c r="H32" t="n">
-        <v>55</v>
+        <v>35.8</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>88.01000000000001</v>
+        <v>-62.46</v>
       </c>
       <c r="K32" t="n">
-        <v>121.5</v>
+        <v>-104.07</v>
       </c>
       <c r="L32" t="n">
-        <v>150.03</v>
+        <v>121.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:14:24</t>
+          <t>07:16:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.04</v>
+        <v>4.9</v>
       </c>
       <c r="F33" t="n">
-        <v>9.56</v>
+        <v>11.04</v>
       </c>
       <c r="G33" t="n">
-        <v>340.9</v>
+        <v>336.9</v>
       </c>
       <c r="H33" t="n">
-        <v>86.2</v>
+        <v>36.3</v>
       </c>
       <c r="I33" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-74.05</v>
+        <v>11.06</v>
       </c>
       <c r="K33" t="n">
-        <v>133.95</v>
+        <v>135.38</v>
       </c>
       <c r="L33" t="n">
-        <v>153.06</v>
+        <v>135.83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:15:17</t>
+          <t>07:18:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="F34" t="n">
-        <v>12.65</v>
+        <v>10.39</v>
       </c>
       <c r="G34" t="n">
-        <v>338.2</v>
+        <v>347.4</v>
       </c>
       <c r="H34" t="n">
-        <v>54</v>
+        <v>48.7</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>37</v>
+        <v>-0.54</v>
       </c>
       <c r="K34" t="n">
-        <v>89.8</v>
+        <v>-137.09</v>
       </c>
       <c r="L34" t="n">
-        <v>97.12</v>
+        <v>137.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:19:08</t>
+          <t>07:22:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.26</v>
+        <v>4.45</v>
       </c>
       <c r="F35" t="n">
-        <v>9.77</v>
+        <v>8.99</v>
       </c>
       <c r="G35" t="n">
-        <v>359.4</v>
+        <v>343.9</v>
       </c>
       <c r="H35" t="n">
-        <v>55.6</v>
+        <v>37.1</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J35" t="n">
-        <v>-132.39</v>
+        <v>61.31</v>
       </c>
       <c r="K35" t="n">
-        <v>157.98</v>
+        <v>24.6</v>
       </c>
       <c r="L35" t="n">
-        <v>206.12</v>
+        <v>66.06999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:21:11</t>
+          <t>07:23:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.79</v>
+        <v>5.05</v>
       </c>
       <c r="F36" t="n">
-        <v>9.869999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="G36" t="n">
-        <v>335.8</v>
+        <v>343.6</v>
       </c>
       <c r="H36" t="n">
-        <v>24.7</v>
+        <v>92</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-187.93</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-116.48</v>
+        <v>-0.55</v>
       </c>
       <c r="L36" t="n">
-        <v>221.1</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:22:17</t>
+          <t>07:25:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.62</v>
+        <v>6.14</v>
       </c>
       <c r="F37" t="n">
-        <v>11.5</v>
+        <v>13.08</v>
       </c>
       <c r="G37" t="n">
-        <v>337.2</v>
+        <v>359.4</v>
       </c>
       <c r="H37" t="n">
-        <v>57.3</v>
+        <v>57.6</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>-166.38</v>
+        <v>212.93</v>
       </c>
       <c r="K37" t="n">
-        <v>-91.55</v>
+        <v>32.42</v>
       </c>
       <c r="L37" t="n">
-        <v>189.91</v>
+        <v>215.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:26:53</t>
+          <t>07:28:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>5.34</v>
+        <v>5.01</v>
       </c>
       <c r="F38" t="n">
-        <v>11.08</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>332.9</v>
+        <v>347.7</v>
       </c>
       <c r="H38" t="n">
-        <v>52.8</v>
+        <v>30.9</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>190.64</v>
+        <v>-34.94</v>
       </c>
       <c r="K38" t="n">
-        <v>196.87</v>
+        <v>203.42</v>
       </c>
       <c r="L38" t="n">
-        <v>274.05</v>
+        <v>206.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:28:40</t>
+          <t>07:31:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.07</v>
+        <v>4.81</v>
       </c>
       <c r="F39" t="n">
-        <v>13.23</v>
+        <v>11.15</v>
       </c>
       <c r="G39" t="n">
-        <v>350</v>
+        <v>354.9</v>
       </c>
       <c r="H39" t="n">
-        <v>61.5</v>
+        <v>90</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-127.45</v>
+        <v>9.27</v>
       </c>
       <c r="K39" t="n">
-        <v>-221.1</v>
+        <v>100.11</v>
       </c>
       <c r="L39" t="n">
-        <v>255.2</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:30:02</t>
+          <t>07:33:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="F40" t="n">
-        <v>10.82</v>
+        <v>9.74</v>
       </c>
       <c r="G40" t="n">
-        <v>345.9</v>
+        <v>332.1</v>
       </c>
       <c r="H40" t="n">
-        <v>78</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-162.77</v>
+        <v>65.13</v>
       </c>
       <c r="K40" t="n">
-        <v>288.84</v>
+        <v>-74.94</v>
       </c>
       <c r="L40" t="n">
-        <v>331.55</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:34:20</t>
+          <t>07:39:13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.28</v>
+        <v>5.51</v>
       </c>
       <c r="F41" t="n">
-        <v>12.98</v>
+        <v>11.17</v>
       </c>
       <c r="G41" t="n">
-        <v>355.8</v>
+        <v>355.5</v>
       </c>
       <c r="H41" t="n">
-        <v>53.1</v>
+        <v>46.5</v>
       </c>
       <c r="I41" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J41" t="n">
-        <v>-399.13</v>
+        <v>-1.42</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.949999999999999</v>
+        <v>-314.53</v>
       </c>
       <c r="L41" t="n">
-        <v>399.23</v>
+        <v>314.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:36:10</t>
+          <t>07:40:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="F42" t="n">
-        <v>12.6</v>
+        <v>12.62</v>
       </c>
       <c r="G42" t="n">
-        <v>348.5</v>
+        <v>339.5</v>
       </c>
       <c r="H42" t="n">
-        <v>70.8</v>
+        <v>44.2</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J42" t="n">
-        <v>-275.4</v>
+        <v>128.87</v>
       </c>
       <c r="K42" t="n">
-        <v>248.58</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>370.99</v>
+        <v>161.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:37:23</t>
+          <t>07:42:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.03</v>
+        <v>5.36</v>
       </c>
       <c r="F43" t="n">
-        <v>13.57</v>
+        <v>11.82</v>
       </c>
       <c r="G43" t="n">
-        <v>356.5</v>
+        <v>348.9</v>
       </c>
       <c r="H43" t="n">
-        <v>44</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I43" t="n">
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-130.24</v>
+        <v>118.39</v>
       </c>
       <c r="K43" t="n">
-        <v>300.94</v>
+        <v>322.74</v>
       </c>
       <c r="L43" t="n">
-        <v>327.91</v>
+        <v>343.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:47:52</t>
+          <t>07:50:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.05</v>
+        <v>5.22</v>
       </c>
       <c r="F44" t="n">
-        <v>12.19</v>
+        <v>12.51</v>
       </c>
       <c r="G44" t="n">
-        <v>336.2</v>
+        <v>333</v>
       </c>
       <c r="H44" t="n">
-        <v>42.3</v>
+        <v>58.4</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>-105.02</v>
+        <v>-79.25</v>
       </c>
       <c r="K44" t="n">
-        <v>-65.39</v>
+        <v>-12.8</v>
       </c>
       <c r="L44" t="n">
-        <v>123.71</v>
+        <v>80.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:48:28</t>
+          <t>07:52:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.34</v>
+        <v>5.49</v>
       </c>
       <c r="F45" t="n">
-        <v>7.03</v>
+        <v>13.57</v>
       </c>
       <c r="G45" t="n">
-        <v>342.1</v>
+        <v>334.8</v>
       </c>
       <c r="H45" t="n">
-        <v>46.2</v>
+        <v>51.3</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>31.33</v>
+        <v>53.83</v>
       </c>
       <c r="K45" t="n">
-        <v>80.29000000000001</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>86.19</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:50:47</t>
+          <t>07:53:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37</v>
+        <v>4.4</v>
       </c>
       <c r="F46" t="n">
-        <v>13.33</v>
+        <v>10.14</v>
       </c>
       <c r="G46" t="n">
-        <v>354.4</v>
+        <v>349.1</v>
       </c>
       <c r="H46" t="n">
-        <v>61.8</v>
+        <v>88.8</v>
       </c>
       <c r="I46" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>-56.23</v>
+        <v>-73.04000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>123.88</v>
+        <v>-64.08</v>
       </c>
       <c r="L46" t="n">
-        <v>136.04</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:55:01</t>
+          <t>07:59:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="F47" t="n">
-        <v>12.29</v>
+        <v>10.54</v>
       </c>
       <c r="G47" t="n">
-        <v>341.4</v>
+        <v>352.1</v>
       </c>
       <c r="H47" t="n">
-        <v>60.2</v>
+        <v>19</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>-169.87</v>
+        <v>-56.89</v>
       </c>
       <c r="K47" t="n">
-        <v>16.19</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>170.64</v>
+        <v>112.94</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:56:28</t>
+          <t>08:01:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.68</v>
+        <v>5.07</v>
       </c>
       <c r="F48" t="n">
-        <v>9.92</v>
+        <v>10.68</v>
       </c>
       <c r="G48" t="n">
-        <v>338</v>
+        <v>354.8</v>
       </c>
       <c r="H48" t="n">
-        <v>63.5</v>
+        <v>45.3</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>83.59999999999999</v>
+        <v>50.16</v>
       </c>
       <c r="K48" t="n">
-        <v>-122.61</v>
+        <v>104.71</v>
       </c>
       <c r="L48" t="n">
-        <v>148.4</v>
+        <v>116.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:57:45</t>
+          <t>08:03:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.4</v>
+        <v>4.66</v>
       </c>
       <c r="F49" t="n">
-        <v>13.23</v>
+        <v>11.3</v>
       </c>
       <c r="G49" t="n">
-        <v>351.9</v>
+        <v>3.2</v>
       </c>
       <c r="H49" t="n">
-        <v>93</v>
+        <v>36.5</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>-149.65</v>
+        <v>109.34</v>
       </c>
       <c r="K49" t="n">
-        <v>-38.69</v>
+        <v>-69.02</v>
       </c>
       <c r="L49" t="n">
-        <v>154.57</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:02:22</t>
+          <t>08:07:17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.71</v>
+        <v>4.65</v>
       </c>
       <c r="F50" t="n">
-        <v>9.68</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>345.7</v>
+        <v>350</v>
       </c>
       <c r="H50" t="n">
-        <v>39.2</v>
+        <v>43.1</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J50" t="n">
-        <v>33.92</v>
+        <v>79.64</v>
       </c>
       <c r="K50" t="n">
-        <v>168.32</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>171.7</v>
+        <v>114.62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:03:35</t>
+          <t>08:08:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.13</v>
+        <v>5.31</v>
       </c>
       <c r="F51" t="n">
-        <v>11.39</v>
+        <v>13.46</v>
       </c>
       <c r="G51" t="n">
-        <v>345.9</v>
+        <v>351.6</v>
       </c>
       <c r="H51" t="n">
-        <v>44.6</v>
+        <v>50.5</v>
       </c>
       <c r="I51" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>244.29</v>
+        <v>182.51</v>
       </c>
       <c r="K51" t="n">
-        <v>118.6</v>
+        <v>125.41</v>
       </c>
       <c r="L51" t="n">
-        <v>271.56</v>
+        <v>221.44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:04:54</t>
+          <t>08:10:34</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.36</v>
+        <v>5.76</v>
       </c>
       <c r="F52" t="n">
-        <v>11.35</v>
+        <v>13.57</v>
       </c>
       <c r="G52" t="n">
-        <v>340.6</v>
+        <v>347.2</v>
       </c>
       <c r="H52" t="n">
-        <v>66.5</v>
+        <v>58.5</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J52" t="n">
-        <v>198.46</v>
+        <v>-94.87</v>
       </c>
       <c r="K52" t="n">
-        <v>-45.6</v>
+        <v>236.74</v>
       </c>
       <c r="L52" t="n">
-        <v>203.63</v>
+        <v>255.04</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:09:58</t>
+          <t>08:16:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="F53" t="n">
-        <v>10.91</v>
+        <v>8.83</v>
       </c>
       <c r="G53" t="n">
-        <v>2.9</v>
+        <v>351.1</v>
       </c>
       <c r="H53" t="n">
-        <v>37.6</v>
+        <v>69.3</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J53" t="n">
-        <v>28.11</v>
+        <v>-278.31</v>
       </c>
       <c r="K53" t="n">
-        <v>324.18</v>
+        <v>-126</v>
       </c>
       <c r="L53" t="n">
-        <v>325.4</v>
+        <v>305.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:11:08</t>
+          <t>08:17:28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="F54" t="n">
-        <v>11.61</v>
+        <v>10.09</v>
       </c>
       <c r="G54" t="n">
-        <v>344</v>
+        <v>342.2</v>
       </c>
       <c r="H54" t="n">
-        <v>52</v>
+        <v>61.4</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J54" t="n">
-        <v>106.91</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>358.19</v>
+        <v>223.82</v>
       </c>
       <c r="L54" t="n">
-        <v>373.81</v>
+        <v>238.25</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:12:02</t>
+          <t>08:19:19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.84</v>
+        <v>5.14</v>
       </c>
       <c r="F55" t="n">
-        <v>12.14</v>
+        <v>12.1</v>
       </c>
       <c r="G55" t="n">
-        <v>347.3</v>
+        <v>352.8</v>
       </c>
       <c r="H55" t="n">
-        <v>44.8</v>
+        <v>32.4</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>4.28</v>
+        <v>-10.45</v>
       </c>
       <c r="K55" t="n">
-        <v>265.33</v>
+        <v>254.65</v>
       </c>
       <c r="L55" t="n">
-        <v>265.37</v>
+        <v>254.86</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:16:52</t>
+          <t>08:22:49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.14</v>
+        <v>5.7</v>
       </c>
       <c r="F56" t="n">
-        <v>11.55</v>
+        <v>13.57</v>
       </c>
       <c r="G56" t="n">
-        <v>357.2</v>
+        <v>355.8</v>
       </c>
       <c r="H56" t="n">
-        <v>51.6</v>
+        <v>69.2</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-408.8</v>
+        <v>362.27</v>
       </c>
       <c r="K56" t="n">
-        <v>-255.79</v>
+        <v>-205.93</v>
       </c>
       <c r="L56" t="n">
-        <v>482.23</v>
+        <v>416.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:19:03</t>
+          <t>08:24:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.17</v>
+        <v>4.97</v>
       </c>
       <c r="F57" t="n">
-        <v>12.36</v>
+        <v>13.57</v>
       </c>
       <c r="G57" t="n">
-        <v>350.3</v>
+        <v>348.3</v>
       </c>
       <c r="H57" t="n">
-        <v>63.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>416.05</v>
+        <v>-137.61</v>
       </c>
       <c r="K57" t="n">
-        <v>75.13</v>
+        <v>23.99</v>
       </c>
       <c r="L57" t="n">
-        <v>422.78</v>
+        <v>139.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:20:04</t>
+          <t>08:25:24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.9</v>
+        <v>5.04</v>
       </c>
       <c r="F58" t="n">
-        <v>10.89</v>
+        <v>12.64</v>
       </c>
       <c r="G58" t="n">
-        <v>351.8</v>
+        <v>359.2</v>
       </c>
       <c r="H58" t="n">
-        <v>44.5</v>
+        <v>60.7</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>219.77</v>
+        <v>181.37</v>
       </c>
       <c r="K58" t="n">
-        <v>-295.25</v>
+        <v>-262.87</v>
       </c>
       <c r="L58" t="n">
-        <v>368.06</v>
+        <v>319.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:27:31</t>
+          <t>08:34:14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.03</v>
+        <v>4.85</v>
       </c>
       <c r="F59" t="n">
-        <v>12.91</v>
+        <v>12.3</v>
       </c>
       <c r="G59" t="n">
-        <v>349.3</v>
+        <v>355.8</v>
       </c>
       <c r="H59" t="n">
-        <v>76.90000000000001</v>
+        <v>31.7</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-42.61</v>
+        <v>-55.7</v>
       </c>
       <c r="K59" t="n">
-        <v>85.3</v>
+        <v>-95.31999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>95.34999999999999</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:29:04</t>
+          <t>08:35:20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.25</v>
+        <v>5.84</v>
       </c>
       <c r="F60" t="n">
-        <v>12.09</v>
+        <v>13.13</v>
       </c>
       <c r="G60" t="n">
-        <v>354.1</v>
+        <v>338.1</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>57.7</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>-86.33</v>
+        <v>100.11</v>
       </c>
       <c r="K60" t="n">
-        <v>-45.03</v>
+        <v>74.02</v>
       </c>
       <c r="L60" t="n">
-        <v>97.36</v>
+        <v>124.51</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:30:34</t>
+          <t>08:37:31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="F61" t="n">
-        <v>12.85</v>
+        <v>11.82</v>
       </c>
       <c r="G61" t="n">
-        <v>358.5</v>
+        <v>331.6</v>
       </c>
       <c r="H61" t="n">
-        <v>51.9</v>
+        <v>38.4</v>
       </c>
       <c r="I61" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>11.61</v>
+        <v>65.69</v>
       </c>
       <c r="K61" t="n">
-        <v>144.57</v>
+        <v>-83.77</v>
       </c>
       <c r="L61" t="n">
-        <v>145.04</v>
+        <v>106.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:36:29</t>
+          <t>08:42:52</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.41</v>
+        <v>5.64</v>
       </c>
       <c r="F62" t="n">
         <v>13.57</v>
       </c>
       <c r="G62" t="n">
-        <v>341.7</v>
+        <v>347.7</v>
       </c>
       <c r="H62" t="n">
-        <v>46.6</v>
+        <v>98.3</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>-125.25</v>
+        <v>-148.96</v>
       </c>
       <c r="K62" t="n">
-        <v>11.08</v>
+        <v>18.59</v>
       </c>
       <c r="L62" t="n">
-        <v>125.74</v>
+        <v>150.12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:37:06</t>
+          <t>08:45:03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.83</v>
+        <v>5.44</v>
       </c>
       <c r="F63" t="n">
-        <v>10.15</v>
+        <v>13.57</v>
       </c>
       <c r="G63" t="n">
-        <v>10.3</v>
+        <v>359.4</v>
       </c>
       <c r="H63" t="n">
-        <v>70.40000000000001</v>
+        <v>56</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>48.66</v>
+        <v>-126.82</v>
       </c>
       <c r="K63" t="n">
-        <v>119.56</v>
+        <v>-138.94</v>
       </c>
       <c r="L63" t="n">
-        <v>129.09</v>
+        <v>188.11</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:38:40</t>
+          <t>08:46:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.83</v>
+        <v>5.09</v>
       </c>
       <c r="F64" t="n">
-        <v>9.98</v>
+        <v>12.91</v>
       </c>
       <c r="G64" t="n">
-        <v>356.5</v>
+        <v>1.8</v>
       </c>
       <c r="H64" t="n">
-        <v>67.3</v>
+        <v>34</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>-134.64</v>
+        <v>-20.64</v>
       </c>
       <c r="K64" t="n">
-        <v>74.98</v>
+        <v>129.88</v>
       </c>
       <c r="L64" t="n">
-        <v>154.11</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:42:59</t>
+          <t>08:51:53</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.9</v>
+        <v>5.11</v>
       </c>
       <c r="F65" t="n">
-        <v>13.57</v>
+        <v>12.11</v>
       </c>
       <c r="G65" t="n">
-        <v>344.2</v>
+        <v>351.5</v>
       </c>
       <c r="H65" t="n">
-        <v>67.2</v>
+        <v>65</v>
       </c>
       <c r="I65" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>4.68</v>
+        <v>-73.42</v>
       </c>
       <c r="K65" t="n">
-        <v>284.3</v>
+        <v>129.88</v>
       </c>
       <c r="L65" t="n">
-        <v>284.33</v>
+        <v>149.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:44:16</t>
+          <t>08:53:08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.54</v>
+        <v>5.19</v>
       </c>
       <c r="F66" t="n">
-        <v>11.48</v>
+        <v>12.02</v>
       </c>
       <c r="G66" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="H66" t="n">
-        <v>45.9</v>
+        <v>37.4</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-148.43</v>
+        <v>-14.99</v>
       </c>
       <c r="K66" t="n">
-        <v>-41.05</v>
+        <v>-321.56</v>
       </c>
       <c r="L66" t="n">
-        <v>154.01</v>
+        <v>321.91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:45:23</t>
+          <t>08:54:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.88</v>
+        <v>6.29</v>
       </c>
       <c r="F67" t="n">
         <v>13.57</v>
       </c>
       <c r="G67" t="n">
-        <v>337.1</v>
+        <v>340</v>
       </c>
       <c r="H67" t="n">
-        <v>43.7</v>
+        <v>57.9</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>-158.54</v>
+        <v>-100.2</v>
       </c>
       <c r="K67" t="n">
-        <v>154.54</v>
+        <v>147.58</v>
       </c>
       <c r="L67" t="n">
-        <v>221.4</v>
+        <v>178.39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:51:13</t>
+          <t>08:58:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.33</v>
+        <v>5.49</v>
       </c>
       <c r="F68" t="n">
-        <v>11.95</v>
+        <v>13.22</v>
       </c>
       <c r="G68" t="n">
-        <v>356.2</v>
+        <v>353.7</v>
       </c>
       <c r="H68" t="n">
-        <v>49.6</v>
+        <v>90.7</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J68" t="n">
-        <v>-130.59</v>
+        <v>40.7</v>
       </c>
       <c r="K68" t="n">
-        <v>277.23</v>
+        <v>-258.87</v>
       </c>
       <c r="L68" t="n">
-        <v>306.45</v>
+        <v>262.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:52:35</t>
+          <t>09:00:29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.01</v>
+        <v>5.32</v>
       </c>
       <c r="F69" t="n">
-        <v>12.58</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>347.3</v>
+        <v>352.8</v>
       </c>
       <c r="H69" t="n">
-        <v>66.2</v>
+        <v>56.1</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J69" t="n">
-        <v>38.19</v>
+        <v>207.4</v>
       </c>
       <c r="K69" t="n">
-        <v>289.6</v>
+        <v>-39</v>
       </c>
       <c r="L69" t="n">
-        <v>292.11</v>
+        <v>211.03</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:53:54</t>
+          <t>09:01:44</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="F70" t="n">
-        <v>13.57</v>
+        <v>12.62</v>
       </c>
       <c r="G70" t="n">
-        <v>337.7</v>
+        <v>5</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>55.8</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>176.61</v>
+        <v>251.67</v>
       </c>
       <c r="K70" t="n">
-        <v>174.41</v>
+        <v>115.02</v>
       </c>
       <c r="L70" t="n">
-        <v>248.21</v>
+        <v>276.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:58:31</t>
+          <t>09:06:21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.1</v>
+        <v>5.12</v>
       </c>
       <c r="F71" t="n">
-        <v>12.7</v>
+        <v>13.57</v>
       </c>
       <c r="G71" t="n">
-        <v>342.1</v>
+        <v>350.8</v>
       </c>
       <c r="H71" t="n">
-        <v>35.6</v>
+        <v>52.8</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>125.69</v>
+        <v>-32.06</v>
       </c>
       <c r="K71" t="n">
-        <v>312.69</v>
+        <v>366.91</v>
       </c>
       <c r="L71" t="n">
-        <v>337.01</v>
+        <v>368.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:59:36</t>
+          <t>09:07:31</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.51</v>
+        <v>5.92</v>
       </c>
       <c r="F72" t="n">
-        <v>11.82</v>
+        <v>13.57</v>
       </c>
       <c r="G72" t="n">
-        <v>351.6</v>
+        <v>344.5</v>
       </c>
       <c r="H72" t="n">
-        <v>67.90000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>-125.86</v>
+        <v>228.52</v>
       </c>
       <c r="K72" t="n">
-        <v>-417.66</v>
+        <v>-425.25</v>
       </c>
       <c r="L72" t="n">
-        <v>436.21</v>
+        <v>482.77</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:00:14</t>
+          <t>09:08:15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.95</v>
+        <v>5.35</v>
       </c>
       <c r="F73" t="n">
-        <v>11.81</v>
+        <v>9.49</v>
       </c>
       <c r="G73" t="n">
-        <v>352</v>
+        <v>333.9</v>
       </c>
       <c r="H73" t="n">
-        <v>75</v>
+        <v>38.9</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-135.56</v>
+        <v>182.73</v>
       </c>
       <c r="K73" t="n">
-        <v>343.01</v>
+        <v>-316.11</v>
       </c>
       <c r="L73" t="n">
-        <v>368.83</v>
+        <v>365.12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:13:03</t>
+          <t>09:16:53</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.06</v>
+        <v>5.55</v>
       </c>
       <c r="F74" t="n">
-        <v>13.45</v>
+        <v>13.44</v>
       </c>
       <c r="G74" t="n">
-        <v>341.9</v>
+        <v>349.5</v>
       </c>
       <c r="H74" t="n">
-        <v>27</v>
+        <v>37.2</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J74" t="n">
-        <v>26.41</v>
+        <v>75.87</v>
       </c>
       <c r="K74" t="n">
-        <v>102.59</v>
+        <v>79.16</v>
       </c>
       <c r="L74" t="n">
-        <v>105.93</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:14:20</t>
+          <t>09:18:03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.53</v>
+        <v>5.27</v>
       </c>
       <c r="F75" t="n">
-        <v>13.57</v>
+        <v>12.49</v>
       </c>
       <c r="G75" t="n">
-        <v>351</v>
+        <v>0.1</v>
       </c>
       <c r="H75" t="n">
-        <v>48.5</v>
+        <v>27.9</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>159.16</v>
+        <v>-118.22</v>
       </c>
       <c r="K75" t="n">
-        <v>25.52</v>
+        <v>-4.87</v>
       </c>
       <c r="L75" t="n">
-        <v>161.19</v>
+        <v>118.32</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:15:14</t>
+          <t>09:19:28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.61</v>
+        <v>5.71</v>
       </c>
       <c r="F76" t="n">
-        <v>11.66</v>
+        <v>13.57</v>
       </c>
       <c r="G76" t="n">
-        <v>2.2</v>
+        <v>344.5</v>
       </c>
       <c r="H76" t="n">
-        <v>75.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>101.59</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-19.69</v>
+        <v>112.06</v>
       </c>
       <c r="L76" t="n">
-        <v>103.48</v>
+        <v>144.68</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:19:11</t>
+          <t>09:24:53</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.53</v>
+        <v>5.91</v>
       </c>
       <c r="F77" t="n">
-        <v>12.96</v>
+        <v>13.57</v>
       </c>
       <c r="G77" t="n">
-        <v>342.4</v>
+        <v>351.4</v>
       </c>
       <c r="H77" t="n">
-        <v>53.7</v>
+        <v>57.6</v>
       </c>
       <c r="I77" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-87.05</v>
+        <v>-198.4</v>
       </c>
       <c r="K77" t="n">
-        <v>167.06</v>
+        <v>-8.42</v>
       </c>
       <c r="L77" t="n">
-        <v>188.38</v>
+        <v>198.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:20:39</t>
+          <t>09:25:58</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.36</v>
+        <v>6.21</v>
       </c>
       <c r="F78" t="n">
         <v>13.57</v>
       </c>
       <c r="G78" t="n">
-        <v>357.3</v>
+        <v>343.2</v>
       </c>
       <c r="H78" t="n">
-        <v>39.1</v>
+        <v>73</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>-158</v>
+        <v>165.74</v>
       </c>
       <c r="K78" t="n">
-        <v>-22.73</v>
+        <v>-168.3</v>
       </c>
       <c r="L78" t="n">
-        <v>159.63</v>
+        <v>236.21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:21:56</t>
+          <t>09:27:29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
       <c r="F79" t="n">
-        <v>13.05</v>
+        <v>12.75</v>
       </c>
       <c r="G79" t="n">
-        <v>349.9</v>
+        <v>336.8</v>
       </c>
       <c r="H79" t="n">
-        <v>30.3</v>
+        <v>29.4</v>
       </c>
       <c r="I79" t="n">
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-21.46</v>
+        <v>-184.71</v>
       </c>
       <c r="K79" t="n">
-        <v>-152.81</v>
+        <v>42.07</v>
       </c>
       <c r="L79" t="n">
-        <v>154.31</v>
+        <v>189.45</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:27:25</t>
+          <t>09:32:41</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.39</v>
+        <v>4.7</v>
       </c>
       <c r="F80" t="n">
-        <v>13.57</v>
+        <v>10.8</v>
       </c>
       <c r="G80" t="n">
-        <v>339.3</v>
+        <v>4.8</v>
       </c>
       <c r="H80" t="n">
-        <v>34.5</v>
+        <v>37.1</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J80" t="n">
-        <v>-108.89</v>
+        <v>-51.9</v>
       </c>
       <c r="K80" t="n">
-        <v>177.04</v>
+        <v>-194.71</v>
       </c>
       <c r="L80" t="n">
-        <v>207.84</v>
+        <v>201.51</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:29:44</t>
+          <t>09:34:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="F81" t="n">
-        <v>10.32</v>
+        <v>12.85</v>
       </c>
       <c r="G81" t="n">
-        <v>346.3</v>
+        <v>353.3</v>
       </c>
       <c r="H81" t="n">
-        <v>90.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-56.16</v>
+        <v>-42.53</v>
       </c>
       <c r="K81" t="n">
-        <v>175.93</v>
+        <v>187.82</v>
       </c>
       <c r="L81" t="n">
-        <v>184.68</v>
+        <v>192.58</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:31:57</t>
+          <t>09:35:44</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.64</v>
+        <v>5.7</v>
       </c>
       <c r="F82" t="n">
         <v>13.57</v>
       </c>
       <c r="G82" t="n">
-        <v>4.7</v>
+        <v>335.3</v>
       </c>
       <c r="H82" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>203.57</v>
+        <v>160.1</v>
       </c>
       <c r="K82" t="n">
-        <v>86.59999999999999</v>
+        <v>102.41</v>
       </c>
       <c r="L82" t="n">
-        <v>221.22</v>
+        <v>190.06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:36:39</t>
+          <t>09:39:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.15</v>
+        <v>5.74</v>
       </c>
       <c r="F83" t="n">
-        <v>12.03</v>
+        <v>13.57</v>
       </c>
       <c r="G83" t="n">
-        <v>324.4</v>
+        <v>354.7</v>
       </c>
       <c r="H83" t="n">
-        <v>20</v>
+        <v>58.7</v>
       </c>
       <c r="I83" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>74.09999999999999</v>
+        <v>336.26</v>
       </c>
       <c r="K83" t="n">
-        <v>161.16</v>
+        <v>-64.19</v>
       </c>
       <c r="L83" t="n">
-        <v>177.38</v>
+        <v>342.34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:38:48</t>
+          <t>09:41:49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.86</v>
+        <v>5.73</v>
       </c>
       <c r="F84" t="n">
         <v>13.57</v>
       </c>
       <c r="G84" t="n">
-        <v>357.7</v>
+        <v>339.4</v>
       </c>
       <c r="H84" t="n">
-        <v>90.90000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.98</v>
+        <v>-170.07</v>
       </c>
       <c r="K84" t="n">
-        <v>340.26</v>
+        <v>301.1</v>
       </c>
       <c r="L84" t="n">
-        <v>340.3</v>
+        <v>345.81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:41:05</t>
+          <t>09:43:44</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>6.92</v>
+        <v>5.59</v>
       </c>
       <c r="F85" t="n">
-        <v>13.57</v>
+        <v>12.56</v>
       </c>
       <c r="G85" t="n">
-        <v>342.8</v>
+        <v>337.8</v>
       </c>
       <c r="H85" t="n">
-        <v>60.2</v>
+        <v>68.5</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>343.33</v>
+        <v>-116.44</v>
       </c>
       <c r="K85" t="n">
-        <v>-99.56999999999999</v>
+        <v>-377.01</v>
       </c>
       <c r="L85" t="n">
-        <v>357.47</v>
+        <v>394.58</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:46:17</t>
+          <t>09:49:49</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.93</v>
+        <v>5.42</v>
       </c>
       <c r="F86" t="n">
-        <v>11.15</v>
+        <v>12.55</v>
       </c>
       <c r="G86" t="n">
-        <v>357.7</v>
+        <v>349.9</v>
       </c>
       <c r="H86" t="n">
-        <v>89.59999999999999</v>
+        <v>46.5</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>-149.1</v>
+        <v>78.55</v>
       </c>
       <c r="K86" t="n">
-        <v>285.6</v>
+        <v>368.13</v>
       </c>
       <c r="L86" t="n">
-        <v>322.18</v>
+        <v>376.41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:47:49</t>
+          <t>09:52:05</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.62</v>
+        <v>5.53</v>
       </c>
       <c r="F87" t="n">
         <v>13.57</v>
       </c>
       <c r="G87" t="n">
-        <v>354.1</v>
+        <v>353</v>
       </c>
       <c r="H87" t="n">
-        <v>85.2</v>
+        <v>38.4</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>-295.71</v>
+        <v>-373.57</v>
       </c>
       <c r="K87" t="n">
-        <v>-276.33</v>
+        <v>-84.3</v>
       </c>
       <c r="L87" t="n">
-        <v>404.72</v>
+        <v>382.96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:49:18</t>
+          <t>09:54:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.58</v>
+        <v>5.51</v>
       </c>
       <c r="F88" t="n">
-        <v>12.07</v>
+        <v>12.31</v>
       </c>
       <c r="G88" t="n">
-        <v>353.3</v>
+        <v>346.5</v>
       </c>
       <c r="H88" t="n">
-        <v>50.5</v>
+        <v>89</v>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>127.64</v>
+        <v>-158.33</v>
       </c>
       <c r="K88" t="n">
-        <v>303.05</v>
+        <v>326.74</v>
       </c>
       <c r="L88" t="n">
-        <v>328.84</v>
+        <v>363.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>64.47</v>
+        <v>73.92</v>
       </c>
       <c r="K14" t="n">
-        <v>27.21</v>
+        <v>31.2</v>
       </c>
       <c r="L14" t="n">
-        <v>69.98</v>
+        <v>80.23</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-102.74</v>
+        <v>-104.68</v>
       </c>
       <c r="K15" t="n">
-        <v>-72.37</v>
+        <v>-73.73999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>125.67</v>
+        <v>128.04</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-24.27</v>
+        <v>-27.15</v>
       </c>
       <c r="K16" t="n">
-        <v>74.14</v>
+        <v>82.91</v>
       </c>
       <c r="L16" t="n">
-        <v>78.01000000000001</v>
+        <v>87.23999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>109.7</v>
+        <v>121.78</v>
       </c>
       <c r="K17" t="n">
-        <v>10.26</v>
+        <v>11.39</v>
       </c>
       <c r="L17" t="n">
-        <v>110.17</v>
+        <v>122.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>96.34999999999999</v>
+        <v>109.58</v>
       </c>
       <c r="K18" t="n">
-        <v>78.42</v>
+        <v>89.19</v>
       </c>
       <c r="L18" t="n">
-        <v>124.23</v>
+        <v>141.29</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.68</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>93.02</v>
+        <v>107.67</v>
       </c>
       <c r="L19" t="n">
-        <v>93.33</v>
+        <v>108.04</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-142.28</v>
+        <v>-175.51</v>
       </c>
       <c r="K20" t="n">
-        <v>24.55</v>
+        <v>30.28</v>
       </c>
       <c r="L20" t="n">
-        <v>144.38</v>
+        <v>178.1</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.27</v>
+        <v>-12.13</v>
       </c>
       <c r="K21" t="n">
-        <v>142.68</v>
+        <v>168.45</v>
       </c>
       <c r="L21" t="n">
-        <v>143.05</v>
+        <v>168.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-62.96</v>
+        <v>-73.8</v>
       </c>
       <c r="K22" t="n">
-        <v>136.28</v>
+        <v>159.74</v>
       </c>
       <c r="L22" t="n">
-        <v>150.12</v>
+        <v>175.96</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>244.27</v>
+        <v>322.32</v>
       </c>
       <c r="K23" t="n">
-        <v>55.11</v>
+        <v>72.73</v>
       </c>
       <c r="L23" t="n">
-        <v>250.41</v>
+        <v>330.42</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>213.55</v>
+        <v>274.77</v>
       </c>
       <c r="K24" t="n">
-        <v>-62.29</v>
+        <v>-80.15000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>222.45</v>
+        <v>286.22</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.97</v>
+        <v>-16.61</v>
       </c>
       <c r="K25" t="n">
-        <v>0.98</v>
+        <v>1.37</v>
       </c>
       <c r="L25" t="n">
-        <v>12.01</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-284.77</v>
+        <v>-349.19</v>
       </c>
       <c r="K26" t="n">
-        <v>243.08</v>
+        <v>298.07</v>
       </c>
       <c r="L26" t="n">
-        <v>374.41</v>
+        <v>459.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>156.82</v>
+        <v>215.28</v>
       </c>
       <c r="K27" t="n">
-        <v>272.14</v>
+        <v>373.59</v>
       </c>
       <c r="L27" t="n">
-        <v>314.09</v>
+        <v>431.18</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-531.54</v>
+        <v>-675.74</v>
       </c>
       <c r="K28" t="n">
-        <v>-45.86</v>
+        <v>-58.3</v>
       </c>
       <c r="L28" t="n">
-        <v>533.52</v>
+        <v>678.25</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.85</v>
+        <v>-27.89</v>
       </c>
       <c r="K29" t="n">
-        <v>-95.81</v>
+        <v>-103.37</v>
       </c>
       <c r="L29" t="n">
-        <v>99.23999999999999</v>
+        <v>107.07</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>89.68000000000001</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>9.470000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="L30" t="n">
-        <v>90.18000000000001</v>
+        <v>99.37</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-77.68000000000001</v>
+        <v>-82.63</v>
       </c>
       <c r="K31" t="n">
-        <v>-53.51</v>
+        <v>-56.92</v>
       </c>
       <c r="L31" t="n">
-        <v>94.33</v>
+        <v>100.34</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>24.7</v>
+        <v>27.33</v>
       </c>
       <c r="K32" t="n">
-        <v>118.58</v>
+        <v>131.17</v>
       </c>
       <c r="L32" t="n">
-        <v>121.13</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>62.91</v>
+        <v>75.87</v>
       </c>
       <c r="K33" t="n">
-        <v>45.28</v>
+        <v>54.6</v>
       </c>
       <c r="L33" t="n">
-        <v>77.51000000000001</v>
+        <v>93.48</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>11.27</v>
+        <v>12.49</v>
       </c>
       <c r="K34" t="n">
-        <v>-99.89</v>
+        <v>-110.71</v>
       </c>
       <c r="L34" t="n">
-        <v>100.53</v>
+        <v>111.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-119.4</v>
+        <v>-141.77</v>
       </c>
       <c r="K35" t="n">
-        <v>77.77</v>
+        <v>92.34</v>
       </c>
       <c r="L35" t="n">
-        <v>142.49</v>
+        <v>169.19</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.11</v>
+        <v>-1.43</v>
       </c>
       <c r="K36" t="n">
-        <v>135.31</v>
+        <v>175.48</v>
       </c>
       <c r="L36" t="n">
-        <v>135.32</v>
+        <v>175.49</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>-196.39</v>
+        <v>-237.82</v>
       </c>
       <c r="K37" t="n">
-        <v>31.58</v>
+        <v>38.24</v>
       </c>
       <c r="L37" t="n">
-        <v>198.91</v>
+        <v>240.87</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>224.37</v>
+        <v>290.34</v>
       </c>
       <c r="K38" t="n">
-        <v>229.86</v>
+        <v>297.44</v>
       </c>
       <c r="L38" t="n">
-        <v>321.21</v>
+        <v>415.65</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>-175.18</v>
+        <v>-221.11</v>
       </c>
       <c r="K39" t="n">
-        <v>131.71</v>
+        <v>166.25</v>
       </c>
       <c r="L39" t="n">
-        <v>219.17</v>
+        <v>276.64</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>179.72</v>
+        <v>224.03</v>
       </c>
       <c r="K40" t="n">
-        <v>168.03</v>
+        <v>209.45</v>
       </c>
       <c r="L40" t="n">
-        <v>246.04</v>
+        <v>306.69</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-32.93</v>
+        <v>-47.9</v>
       </c>
       <c r="K41" t="n">
-        <v>-280.6</v>
+        <v>-408.14</v>
       </c>
       <c r="L41" t="n">
-        <v>282.53</v>
+        <v>410.94</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-90.12</v>
+        <v>-119.6</v>
       </c>
       <c r="K42" t="n">
-        <v>266.71</v>
+        <v>353.96</v>
       </c>
       <c r="L42" t="n">
-        <v>281.52</v>
+        <v>373.62</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-112.16</v>
+        <v>-162.39</v>
       </c>
       <c r="K43" t="n">
-        <v>237.15</v>
+        <v>343.37</v>
       </c>
       <c r="L43" t="n">
-        <v>262.33</v>
+        <v>379.84</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>61.04</v>
+        <v>70.75</v>
       </c>
       <c r="K44" t="n">
-        <v>-53.98</v>
+        <v>-62.57</v>
       </c>
       <c r="L44" t="n">
-        <v>81.48999999999999</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>75.40000000000001</v>
+        <v>88.84</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.34</v>
+        <v>-8.65</v>
       </c>
       <c r="L45" t="n">
-        <v>75.76000000000001</v>
+        <v>89.26000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>73.93000000000001</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>70.95999999999999</v>
+        <v>75.81</v>
       </c>
       <c r="L46" t="n">
-        <v>102.47</v>
+        <v>109.49</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-78.88</v>
+        <v>-99.39</v>
       </c>
       <c r="K47" t="n">
-        <v>24.76</v>
+        <v>31.2</v>
       </c>
       <c r="L47" t="n">
-        <v>82.68000000000001</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-57.15</v>
+        <v>-65.76000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-106.13</v>
+        <v>-122.12</v>
       </c>
       <c r="L48" t="n">
-        <v>120.54</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-22.13</v>
+        <v>-26.15</v>
       </c>
       <c r="K49" t="n">
-        <v>-79.92</v>
+        <v>-94.45</v>
       </c>
       <c r="L49" t="n">
-        <v>82.92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>141.85</v>
+        <v>174.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-13.64</v>
+        <v>-16.75</v>
       </c>
       <c r="L50" t="n">
-        <v>142.51</v>
+        <v>174.95</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-154.08</v>
+        <v>-190.52</v>
       </c>
       <c r="K51" t="n">
-        <v>-19.3</v>
+        <v>-23.86</v>
       </c>
       <c r="L51" t="n">
-        <v>155.28</v>
+        <v>192.01</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-40.04</v>
+        <v>-50.96</v>
       </c>
       <c r="K52" t="n">
-        <v>135.22</v>
+        <v>172.09</v>
       </c>
       <c r="L52" t="n">
-        <v>141.02</v>
+        <v>179.47</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>324.29</v>
+        <v>404.41</v>
       </c>
       <c r="K53" t="n">
-        <v>91.95999999999999</v>
+        <v>114.68</v>
       </c>
       <c r="L53" t="n">
-        <v>337.08</v>
+        <v>420.35</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="n">
-        <v>-273.77</v>
+        <v>-356.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-102.45</v>
+        <v>-133.38</v>
       </c>
       <c r="L54" t="n">
-        <v>292.31</v>
+        <v>380.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-171.25</v>
+        <v>-229.77</v>
       </c>
       <c r="K55" t="n">
-        <v>-151.16</v>
+        <v>-202.81</v>
       </c>
       <c r="L55" t="n">
-        <v>228.42</v>
+        <v>306.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-328.06</v>
+        <v>-475.5</v>
       </c>
       <c r="K56" t="n">
-        <v>-219.05</v>
+        <v>-317.5</v>
       </c>
       <c r="L56" t="n">
-        <v>394.46</v>
+        <v>571.76</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-243.11</v>
+        <v>-318.68</v>
       </c>
       <c r="K57" t="n">
-        <v>-409.54</v>
+        <v>-536.84</v>
       </c>
       <c r="L57" t="n">
-        <v>476.26</v>
+        <v>624.3099999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>307.03</v>
+        <v>446.75</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.210000000000001</v>
+        <v>-11.95</v>
       </c>
       <c r="L58" t="n">
-        <v>307.14</v>
+        <v>446.91</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-58.96</v>
+        <v>-71.12</v>
       </c>
       <c r="K59" t="n">
-        <v>-12.78</v>
+        <v>-15.42</v>
       </c>
       <c r="L59" t="n">
-        <v>60.32</v>
+        <v>72.78</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-58.68</v>
+        <v>-68.81999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>-31.5</v>
+        <v>-36.94</v>
       </c>
       <c r="L60" t="n">
-        <v>66.59999999999999</v>
+        <v>78.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-73.05</v>
+        <v>-81.54000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>32.54</v>
+        <v>36.33</v>
       </c>
       <c r="L61" t="n">
-        <v>79.97</v>
+        <v>89.27</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-167.14</v>
+        <v>-177.43</v>
       </c>
       <c r="K62" t="n">
-        <v>-22.87</v>
+        <v>-24.28</v>
       </c>
       <c r="L62" t="n">
-        <v>168.7</v>
+        <v>179.08</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-77.31999999999999</v>
+        <v>-89.84999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-57.67</v>
+        <v>-67.02</v>
       </c>
       <c r="L63" t="n">
-        <v>96.45</v>
+        <v>112.1</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>77.40000000000001</v>
+        <v>95.75</v>
       </c>
       <c r="K64" t="n">
-        <v>-51.74</v>
+        <v>-64</v>
       </c>
       <c r="L64" t="n">
-        <v>93.09999999999999</v>
+        <v>115.17</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>65.45999999999999</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-83.26000000000001</v>
+        <v>-110.71</v>
       </c>
       <c r="L65" t="n">
-        <v>105.91</v>
+        <v>140.82</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>17</v>
       </c>
       <c r="J66" t="n">
-        <v>-153.53</v>
+        <v>-192.39</v>
       </c>
       <c r="K66" t="n">
-        <v>76.34999999999999</v>
+        <v>95.66</v>
       </c>
       <c r="L66" t="n">
-        <v>171.47</v>
+        <v>214.86</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-145.65</v>
+        <v>-183.59</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.96</v>
+        <v>-4.99</v>
       </c>
       <c r="L67" t="n">
-        <v>145.7</v>
+        <v>183.65</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>101.27</v>
+        <v>143.34</v>
       </c>
       <c r="K68" t="n">
-        <v>-172.33</v>
+        <v>-243.93</v>
       </c>
       <c r="L68" t="n">
-        <v>199.89</v>
+        <v>282.92</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>172.87</v>
+        <v>242.22</v>
       </c>
       <c r="K69" t="n">
-        <v>-87.88</v>
+        <v>-123.14</v>
       </c>
       <c r="L69" t="n">
-        <v>193.93</v>
+        <v>271.73</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-165.88</v>
+        <v>-228.92</v>
       </c>
       <c r="K70" t="n">
-        <v>-133.13</v>
+        <v>-183.72</v>
       </c>
       <c r="L70" t="n">
-        <v>212.7</v>
+        <v>293.53</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-256.41</v>
+        <v>-336.67</v>
       </c>
       <c r="K71" t="n">
-        <v>378.24</v>
+        <v>496.64</v>
       </c>
       <c r="L71" t="n">
-        <v>456.95</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-120.37</v>
+        <v>-160.46</v>
       </c>
       <c r="K72" t="n">
-        <v>427.33</v>
+        <v>569.6799999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>443.96</v>
+        <v>591.84</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.53</v>
+        <v>-9.41</v>
       </c>
       <c r="K73" t="n">
-        <v>-291.09</v>
+        <v>-419.32</v>
       </c>
       <c r="L73" t="n">
-        <v>291.16</v>
+        <v>419.42</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-61.87</v>
+        <v>-76.31999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>43.97</v>
+        <v>54.23</v>
       </c>
       <c r="L74" t="n">
-        <v>75.91</v>
+        <v>93.62</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-85.75</v>
+        <v>-98.45999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>18.5</v>
+        <v>21.25</v>
       </c>
       <c r="L75" t="n">
-        <v>87.72</v>
+        <v>100.73</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>26.49</v>
+        <v>33.25</v>
       </c>
       <c r="K76" t="n">
-        <v>61.66</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>67.11</v>
+        <v>84.23999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="K77" t="n">
-        <v>29.92</v>
+        <v>37.95</v>
       </c>
       <c r="L77" t="n">
-        <v>29.95</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>98.27</v>
+        <v>119.07</v>
       </c>
       <c r="K78" t="n">
-        <v>33.59</v>
+        <v>40.7</v>
       </c>
       <c r="L78" t="n">
-        <v>103.85</v>
+        <v>125.84</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>21.53</v>
+        <v>27.38</v>
       </c>
       <c r="K79" t="n">
-        <v>-44.96</v>
+        <v>-57.18</v>
       </c>
       <c r="L79" t="n">
-        <v>49.85</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>142.5</v>
+        <v>185.86</v>
       </c>
       <c r="K80" t="n">
-        <v>56.86</v>
+        <v>74.16</v>
       </c>
       <c r="L80" t="n">
-        <v>153.43</v>
+        <v>200.11</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-67.55</v>
+        <v>-83.81999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>180.39</v>
+        <v>223.85</v>
       </c>
       <c r="L81" t="n">
-        <v>192.62</v>
+        <v>239.03</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-24.13</v>
+        <v>-31.43</v>
       </c>
       <c r="K82" t="n">
-        <v>113.3</v>
+        <v>147.57</v>
       </c>
       <c r="L82" t="n">
-        <v>115.84</v>
+        <v>150.88</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>149.09</v>
+        <v>206.56</v>
       </c>
       <c r="K83" t="n">
-        <v>-159.92</v>
+        <v>-221.56</v>
       </c>
       <c r="L83" t="n">
-        <v>218.64</v>
+        <v>302.91</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>162.81</v>
+        <v>211.9</v>
       </c>
       <c r="K84" t="n">
-        <v>226.09</v>
+        <v>294.26</v>
       </c>
       <c r="L84" t="n">
-        <v>278.61</v>
+        <v>362.61</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.45</v>
+        <v>-7.74</v>
       </c>
       <c r="K85" t="n">
-        <v>-191.78</v>
+        <v>-272.34</v>
       </c>
       <c r="L85" t="n">
-        <v>191.86</v>
+        <v>272.45</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-338.79</v>
+        <v>-466.74</v>
       </c>
       <c r="K86" t="n">
-        <v>-297.82</v>
+        <v>-410.29</v>
       </c>
       <c r="L86" t="n">
-        <v>451.09</v>
+        <v>621.4400000000001</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>282.88</v>
+        <v>386.89</v>
       </c>
       <c r="K87" t="n">
-        <v>-403.53</v>
+        <v>-551.92</v>
       </c>
       <c r="L87" t="n">
-        <v>492.81</v>
+        <v>674.02</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-581.8</v>
+        <v>-754.4</v>
       </c>
       <c r="K88" t="n">
-        <v>153.74</v>
+        <v>199.35</v>
       </c>
       <c r="L88" t="n">
-        <v>601.77</v>
+        <v>780.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-09-02.xlsx
+++ b/output/2025-09-02.xlsx
@@ -640,13 +640,13 @@
         <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>73.92</v>
+        <v>100.25</v>
       </c>
       <c r="K14" t="n">
-        <v>31.2</v>
+        <v>42.32</v>
       </c>
       <c r="L14" t="n">
-        <v>80.23</v>
+        <v>108.82</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-104.68</v>
+        <v>-130.42</v>
       </c>
       <c r="K15" t="n">
-        <v>-73.73999999999999</v>
+        <v>-91.87</v>
       </c>
       <c r="L15" t="n">
-        <v>128.04</v>
+        <v>159.53</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-27.15</v>
+        <v>-35.3</v>
       </c>
       <c r="K16" t="n">
-        <v>82.91</v>
+        <v>107.8</v>
       </c>
       <c r="L16" t="n">
-        <v>87.23999999999999</v>
+        <v>113.43</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>121.78</v>
+        <v>158.02</v>
       </c>
       <c r="K17" t="n">
-        <v>11.39</v>
+        <v>14.79</v>
       </c>
       <c r="L17" t="n">
-        <v>122.31</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>109.58</v>
+        <v>155.64</v>
       </c>
       <c r="K18" t="n">
-        <v>89.19</v>
+        <v>126.68</v>
       </c>
       <c r="L18" t="n">
-        <v>141.29</v>
+        <v>200.68</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.890000000000001</v>
+        <v>-12.13</v>
       </c>
       <c r="K19" t="n">
-        <v>107.67</v>
+        <v>146.89</v>
       </c>
       <c r="L19" t="n">
-        <v>108.04</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.89</v>
+        <v>-38.13</v>
       </c>
       <c r="K29" t="n">
-        <v>-103.37</v>
+        <v>-141.32</v>
       </c>
       <c r="L29" t="n">
-        <v>107.07</v>
+        <v>146.38</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>98.81999999999999</v>
+        <v>143.87</v>
       </c>
       <c r="K30" t="n">
-        <v>10.43</v>
+        <v>15.19</v>
       </c>
       <c r="L30" t="n">
-        <v>99.37</v>
+        <v>144.67</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-82.63</v>
+        <v>-115.92</v>
       </c>
       <c r="K31" t="n">
-        <v>-56.92</v>
+        <v>-79.84999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>100.34</v>
+        <v>140.76</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>27.33</v>
+        <v>35.03</v>
       </c>
       <c r="K32" t="n">
-        <v>131.17</v>
+        <v>168.14</v>
       </c>
       <c r="L32" t="n">
-        <v>133.99</v>
+        <v>171.75</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>75.87</v>
+        <v>100.42</v>
       </c>
       <c r="K33" t="n">
-        <v>54.6</v>
+        <v>72.27</v>
       </c>
       <c r="L33" t="n">
-        <v>93.48</v>
+        <v>123.72</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>12.49</v>
+        <v>15.41</v>
       </c>
       <c r="K34" t="n">
-        <v>-110.71</v>
+        <v>-136.54</v>
       </c>
       <c r="L34" t="n">
-        <v>111.41</v>
+        <v>137.41</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>70.75</v>
+        <v>111.75</v>
       </c>
       <c r="K44" t="n">
-        <v>-62.57</v>
+        <v>-98.84</v>
       </c>
       <c r="L44" t="n">
-        <v>94.45</v>
+        <v>149.19</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>88.84</v>
+        <v>139.29</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.65</v>
+        <v>-13.56</v>
       </c>
       <c r="L45" t="n">
-        <v>89.26000000000001</v>
+        <v>139.95</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>78.98999999999999</v>
+        <v>110.38</v>
       </c>
       <c r="K46" t="n">
-        <v>75.81</v>
+        <v>105.93</v>
       </c>
       <c r="L46" t="n">
-        <v>109.49</v>
+        <v>152.99</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-99.39</v>
+        <v>-145.8</v>
       </c>
       <c r="K47" t="n">
-        <v>31.2</v>
+        <v>45.77</v>
       </c>
       <c r="L47" t="n">
-        <v>104.17</v>
+        <v>152.81</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-65.76000000000001</v>
+        <v>-92.44</v>
       </c>
       <c r="K48" t="n">
-        <v>-122.12</v>
+        <v>-171.66</v>
       </c>
       <c r="L48" t="n">
-        <v>138.7</v>
+        <v>194.97</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.15</v>
+        <v>-35.51</v>
       </c>
       <c r="K49" t="n">
-        <v>-94.45</v>
+        <v>-128.27</v>
       </c>
       <c r="L49" t="n">
-        <v>98</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-71.12</v>
+        <v>-101.95</v>
       </c>
       <c r="K59" t="n">
-        <v>-15.42</v>
+        <v>-22.1</v>
       </c>
       <c r="L59" t="n">
-        <v>72.78</v>
+        <v>104.32</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-68.81999999999999</v>
+        <v>-114.43</v>
       </c>
       <c r="K60" t="n">
-        <v>-36.94</v>
+        <v>-61.42</v>
       </c>
       <c r="L60" t="n">
-        <v>78.11</v>
+        <v>129.87</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-81.54000000000001</v>
+        <v>-126.66</v>
       </c>
       <c r="K61" t="n">
-        <v>36.33</v>
+        <v>56.42</v>
       </c>
       <c r="L61" t="n">
-        <v>89.27</v>
+        <v>138.66</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-177.43</v>
+        <v>-254.25</v>
       </c>
       <c r="K62" t="n">
-        <v>-24.28</v>
+        <v>-34.79</v>
       </c>
       <c r="L62" t="n">
-        <v>179.08</v>
+        <v>256.62</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-89.84999999999999</v>
+        <v>-116.24</v>
       </c>
       <c r="K63" t="n">
-        <v>-67.02</v>
+        <v>-86.7</v>
       </c>
       <c r="L63" t="n">
-        <v>112.1</v>
+        <v>145.01</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>95.75</v>
+        <v>141.7</v>
       </c>
       <c r="K64" t="n">
-        <v>-64</v>
+        <v>-94.72</v>
       </c>
       <c r="L64" t="n">
-        <v>115.17</v>
+        <v>170.44</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-76.31999999999999</v>
+        <v>-131.51</v>
       </c>
       <c r="K74" t="n">
-        <v>54.23</v>
+        <v>93.45</v>
       </c>
       <c r="L74" t="n">
-        <v>93.62</v>
+        <v>161.33</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-98.45999999999999</v>
+        <v>-165.49</v>
       </c>
       <c r="K75" t="n">
-        <v>21.25</v>
+        <v>35.71</v>
       </c>
       <c r="L75" t="n">
-        <v>100.73</v>
+        <v>169.3</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>33.25</v>
+        <v>56.79</v>
       </c>
       <c r="K76" t="n">
-        <v>77.40000000000001</v>
+        <v>132.2</v>
       </c>
       <c r="L76" t="n">
-        <v>84.23999999999999</v>
+        <v>143.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="K77" t="n">
-        <v>37.95</v>
+        <v>52.4</v>
       </c>
       <c r="L77" t="n">
-        <v>38</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>119.07</v>
+        <v>188.43</v>
       </c>
       <c r="K78" t="n">
-        <v>40.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>125.84</v>
+        <v>199.14</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>27.38</v>
+        <v>37.64</v>
       </c>
       <c r="K79" t="n">
-        <v>-57.18</v>
+        <v>-78.59</v>
       </c>
       <c r="L79" t="n">
-        <v>63.4</v>
+        <v>87.14</v>
       </c>
     </row>
     <row r="80">
